--- a/input/FEC_VoiceAgent_BRD.xlsx
+++ b/input/FEC_VoiceAgent_BRD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hieunguyen/Downloads/cursor_project/Auto_gen_TC/input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hieunguyen/cursor_project/auto_generate_test_cases/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C163E5-2557-F64D-9A71-6B4EEBB25AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D47EE846-4A84-734E-BA87-8D6F630323B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="29400" windowHeight="17000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7824,66 +7824,6 @@
     <xf numFmtId="0" fontId="77" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7908,6 +7848,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -7920,13 +7866,61 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7938,10 +7932,28 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="75" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7953,19 +7965,7 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="66" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -8025,9 +8025,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -8040,11 +8037,38 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -8086,30 +8110,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -8199,14 +8199,14 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -8216,6 +8216,18 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -8232,19 +8244,7 @@
     <xf numFmtId="0" fontId="17" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -9309,8 +9309,8 @@
       <c r="F1" s="188"/>
       <c r="G1" s="188"/>
       <c r="H1" s="105"/>
-      <c r="I1" s="422"/>
-      <c r="J1" s="422"/>
+      <c r="I1" s="402"/>
+      <c r="J1" s="402"/>
       <c r="L1" s="30"/>
       <c r="M1" s="30"/>
     </row>
@@ -9351,13 +9351,13 @@
       </c>
     </row>
     <row r="3" spans="1:138" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="490">
+      <c r="A3" s="476">
         <v>1</v>
       </c>
-      <c r="B3" s="425" t="s">
+      <c r="B3" s="405" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="492" t="s">
+      <c r="C3" s="478" t="s">
         <v>325</v>
       </c>
       <c r="D3" s="73" t="s">
@@ -9385,9 +9385,9 @@
       </c>
     </row>
     <row r="4" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A4" s="491"/>
-      <c r="B4" s="426"/>
-      <c r="C4" s="493"/>
+      <c r="A4" s="477"/>
+      <c r="B4" s="406"/>
+      <c r="C4" s="479"/>
       <c r="D4" s="73" t="s">
         <v>56</v>
       </c>
@@ -9409,9 +9409,9 @@
       <c r="M4" s="76"/>
     </row>
     <row r="5" spans="1:138" ht="75" x14ac:dyDescent="0.2">
-      <c r="A5" s="491"/>
-      <c r="B5" s="426"/>
-      <c r="C5" s="493"/>
+      <c r="A5" s="477"/>
+      <c r="B5" s="406"/>
+      <c r="C5" s="479"/>
       <c r="D5" s="73" t="s">
         <v>55</v>
       </c>
@@ -9436,9 +9436,9 @@
       </c>
     </row>
     <row r="6" spans="1:138" ht="225" x14ac:dyDescent="0.2">
-      <c r="A6" s="491"/>
-      <c r="B6" s="426"/>
-      <c r="C6" s="493"/>
+      <c r="A6" s="477"/>
+      <c r="B6" s="406"/>
+      <c r="C6" s="479"/>
       <c r="D6" s="73" t="s">
         <v>63</v>
       </c>
@@ -9461,9 +9461,9 @@
       <c r="M6" s="76"/>
     </row>
     <row r="7" spans="1:138" ht="165" x14ac:dyDescent="0.2">
-      <c r="A7" s="491"/>
-      <c r="B7" s="426"/>
-      <c r="C7" s="493"/>
+      <c r="A7" s="477"/>
+      <c r="B7" s="406"/>
+      <c r="C7" s="479"/>
       <c r="D7" s="73" t="s">
         <v>68</v>
       </c>
@@ -9485,9 +9485,9 @@
       <c r="M7" s="76"/>
     </row>
     <row r="8" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A8" s="491"/>
-      <c r="B8" s="426"/>
-      <c r="C8" s="493"/>
+      <c r="A8" s="477"/>
+      <c r="B8" s="406"/>
+      <c r="C8" s="479"/>
       <c r="D8" s="73" t="s">
         <v>72</v>
       </c>
@@ -9509,9 +9509,9 @@
       <c r="M8" s="76"/>
     </row>
     <row r="9" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A9" s="491"/>
-      <c r="B9" s="426"/>
-      <c r="C9" s="493"/>
+      <c r="A9" s="477"/>
+      <c r="B9" s="406"/>
+      <c r="C9" s="479"/>
       <c r="D9" s="73" t="s">
         <v>86</v>
       </c>
@@ -9535,9 +9535,9 @@
       <c r="M9" s="76"/>
     </row>
     <row r="10" spans="1:138" s="42" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="491"/>
-      <c r="B10" s="426"/>
-      <c r="C10" s="493"/>
+      <c r="A10" s="477"/>
+      <c r="B10" s="406"/>
+      <c r="C10" s="479"/>
       <c r="D10" s="73" t="s">
         <v>92</v>
       </c>
@@ -9687,9 +9687,9 @@
       <c r="EH10" s="41"/>
     </row>
     <row r="11" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A11" s="491"/>
-      <c r="B11" s="426"/>
-      <c r="C11" s="494"/>
+      <c r="A11" s="477"/>
+      <c r="B11" s="406"/>
+      <c r="C11" s="480"/>
       <c r="D11" s="73" t="s">
         <v>282</v>
       </c>
@@ -9711,13 +9711,13 @@
       <c r="M11" s="76"/>
     </row>
     <row r="12" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="495">
+      <c r="A12" s="481">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B12" s="496" t="s">
+      <c r="B12" s="482" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="430" t="s">
+      <c r="C12" s="412" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="73" t="s">
@@ -9743,9 +9743,9 @@
       <c r="M12" s="76"/>
     </row>
     <row r="13" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A13" s="495"/>
-      <c r="B13" s="496"/>
-      <c r="C13" s="431"/>
+      <c r="A13" s="481"/>
+      <c r="B13" s="482"/>
+      <c r="C13" s="413"/>
       <c r="D13" s="73" t="s">
         <v>56</v>
       </c>
@@ -9771,9 +9771,9 @@
       <c r="M13" s="76"/>
     </row>
     <row r="14" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A14" s="495"/>
-      <c r="B14" s="496"/>
-      <c r="C14" s="431"/>
+      <c r="A14" s="481"/>
+      <c r="B14" s="482"/>
+      <c r="C14" s="413"/>
       <c r="D14" s="237" t="s">
         <v>284</v>
       </c>
@@ -9820,9 +9820,9 @@
       <c r="M14" s="76"/>
     </row>
     <row r="15" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="495"/>
-      <c r="B15" s="496"/>
-      <c r="C15" s="431"/>
+      <c r="A15" s="481"/>
+      <c r="B15" s="482"/>
+      <c r="C15" s="413"/>
       <c r="D15" s="237" t="s">
         <v>286</v>
       </c>
@@ -9841,9 +9841,9 @@
       <c r="M15" s="76"/>
     </row>
     <row r="16" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A16" s="495"/>
-      <c r="B16" s="496"/>
-      <c r="C16" s="431"/>
+      <c r="A16" s="481"/>
+      <c r="B16" s="482"/>
+      <c r="C16" s="413"/>
       <c r="D16" s="76" t="s">
         <v>106</v>
       </c>
@@ -10004,9 +10004,9 @@
       <c r="EH16" s="36"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A17" s="495"/>
-      <c r="B17" s="496"/>
-      <c r="C17" s="431"/>
+      <c r="A17" s="481"/>
+      <c r="B17" s="482"/>
+      <c r="C17" s="413"/>
       <c r="D17" s="76" t="s">
         <v>92</v>
       </c>
@@ -10167,9 +10167,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A18" s="490"/>
-      <c r="B18" s="497"/>
-      <c r="C18" s="431"/>
+      <c r="A18" s="476"/>
+      <c r="B18" s="483"/>
+      <c r="C18" s="413"/>
       <c r="D18" s="78" t="s">
         <v>282</v>
       </c>
@@ -10191,13 +10191,13 @@
       <c r="M18" s="76"/>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="476">
+      <c r="A19" s="484">
         <v>2</v>
       </c>
-      <c r="B19" s="477" t="s">
+      <c r="B19" s="485" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="478" t="s">
+      <c r="C19" s="486" t="s">
         <v>326</v>
       </c>
       <c r="D19" s="73" t="s">
@@ -10223,9 +10223,9 @@
       <c r="M19" s="76"/>
     </row>
     <row r="20" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A20" s="476"/>
-      <c r="B20" s="477"/>
-      <c r="C20" s="479"/>
+      <c r="A20" s="484"/>
+      <c r="B20" s="485"/>
+      <c r="C20" s="487"/>
       <c r="D20" s="73" t="s">
         <v>56</v>
       </c>
@@ -10251,9 +10251,9 @@
       <c r="M20" s="76"/>
     </row>
     <row r="21" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A21" s="476"/>
-      <c r="B21" s="477"/>
-      <c r="C21" s="479"/>
+      <c r="A21" s="484"/>
+      <c r="B21" s="485"/>
+      <c r="C21" s="487"/>
       <c r="D21" s="240" t="s">
         <v>284</v>
       </c>
@@ -10284,9 +10284,9 @@
       <c r="M21" s="76"/>
     </row>
     <row r="22" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A22" s="476"/>
-      <c r="B22" s="477"/>
-      <c r="C22" s="480"/>
+      <c r="A22" s="484"/>
+      <c r="B22" s="485"/>
+      <c r="C22" s="488"/>
       <c r="D22" s="237" t="s">
         <v>286</v>
       </c>
@@ -10304,9 +10304,9 @@
       <c r="M22" s="76"/>
     </row>
     <row r="23" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A23" s="476"/>
-      <c r="B23" s="477"/>
-      <c r="C23" s="479"/>
+      <c r="A23" s="484"/>
+      <c r="B23" s="485"/>
+      <c r="C23" s="487"/>
       <c r="D23" s="88" t="s">
         <v>114</v>
       </c>
@@ -10463,9 +10463,9 @@
       <c r="EH23" s="36"/>
     </row>
     <row r="24" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A24" s="476"/>
-      <c r="B24" s="477"/>
-      <c r="C24" s="479"/>
+      <c r="A24" s="484"/>
+      <c r="B24" s="485"/>
+      <c r="C24" s="487"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
       </c>
@@ -10622,9 +10622,9 @@
       <c r="EH24" s="36"/>
     </row>
     <row r="25" spans="1:138" ht="196.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="476"/>
-      <c r="B25" s="477"/>
-      <c r="C25" s="480"/>
+      <c r="A25" s="484"/>
+      <c r="B25" s="485"/>
+      <c r="C25" s="488"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
       </c>
@@ -10646,13 +10646,13 @@
       <c r="M25" s="76"/>
     </row>
     <row r="26" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A26" s="481">
+      <c r="A26" s="489">
         <v>2.1</v>
       </c>
-      <c r="B26" s="484" t="s">
+      <c r="B26" s="492" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="487" t="s">
+      <c r="C26" s="495" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="237" t="s">
@@ -10678,9 +10678,9 @@
       <c r="M26" s="76"/>
     </row>
     <row r="27" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A27" s="482"/>
-      <c r="B27" s="485"/>
-      <c r="C27" s="488"/>
+      <c r="A27" s="490"/>
+      <c r="B27" s="493"/>
+      <c r="C27" s="496"/>
       <c r="D27" s="237" t="s">
         <v>122</v>
       </c>
@@ -10700,9 +10700,9 @@
       <c r="M27" s="76"/>
     </row>
     <row r="28" spans="1:138" ht="135" x14ac:dyDescent="0.2">
-      <c r="A28" s="482"/>
-      <c r="B28" s="485"/>
-      <c r="C28" s="488"/>
+      <c r="A28" s="490"/>
+      <c r="B28" s="493"/>
+      <c r="C28" s="496"/>
       <c r="D28" s="76" t="s">
         <v>130</v>
       </c>
@@ -10726,9 +10726,9 @@
       <c r="M28" s="76"/>
     </row>
     <row r="29" spans="1:138" ht="75" x14ac:dyDescent="0.2">
-      <c r="A29" s="482"/>
-      <c r="B29" s="485"/>
-      <c r="C29" s="488"/>
+      <c r="A29" s="490"/>
+      <c r="B29" s="493"/>
+      <c r="C29" s="496"/>
       <c r="D29" s="189" t="s">
         <v>55</v>
       </c>
@@ -10752,9 +10752,9 @@
       <c r="M29" s="76"/>
     </row>
     <row r="30" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A30" s="482"/>
-      <c r="B30" s="485"/>
-      <c r="C30" s="488"/>
+      <c r="A30" s="490"/>
+      <c r="B30" s="493"/>
+      <c r="C30" s="496"/>
       <c r="D30" s="37" t="s">
         <v>134</v>
       </c>
@@ -10778,9 +10778,9 @@
       </c>
     </row>
     <row r="31" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A31" s="482"/>
-      <c r="B31" s="485"/>
-      <c r="C31" s="488"/>
+      <c r="A31" s="490"/>
+      <c r="B31" s="493"/>
+      <c r="C31" s="496"/>
       <c r="D31" s="88" t="s">
         <v>114</v>
       </c>
@@ -10804,9 +10804,9 @@
       <c r="M31" s="76"/>
     </row>
     <row r="32" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="482"/>
-      <c r="B32" s="485"/>
-      <c r="C32" s="488"/>
+      <c r="A32" s="490"/>
+      <c r="B32" s="493"/>
+      <c r="C32" s="496"/>
       <c r="D32" s="86" t="s">
         <v>92</v>
       </c>
@@ -10830,9 +10830,9 @@
       <c r="M32" s="76"/>
     </row>
     <row r="33" spans="1:13" ht="45" x14ac:dyDescent="0.2">
-      <c r="A33" s="483"/>
-      <c r="B33" s="486"/>
-      <c r="C33" s="489"/>
+      <c r="A33" s="491"/>
+      <c r="B33" s="494"/>
+      <c r="C33" s="497"/>
       <c r="D33" s="76" t="s">
         <v>94</v>
       </c>
@@ -10859,6 +10859,12 @@
   </sheetData>
   <autoFilter ref="A2:EH33" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="13">
+    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="B19:B25"/>
+    <mergeCell ref="C19:C25"/>
+    <mergeCell ref="A26:A33"/>
+    <mergeCell ref="B26:B33"/>
+    <mergeCell ref="C26:C33"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="A3:A11"/>
     <mergeCell ref="B3:B11"/>
@@ -10866,12 +10872,6 @@
     <mergeCell ref="A12:A18"/>
     <mergeCell ref="B12:B18"/>
     <mergeCell ref="C12:C18"/>
-    <mergeCell ref="A19:A25"/>
-    <mergeCell ref="B19:B25"/>
-    <mergeCell ref="C19:C25"/>
-    <mergeCell ref="A26:A33"/>
-    <mergeCell ref="B26:B33"/>
-    <mergeCell ref="C26:C33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -11670,8 +11670,8 @@
       <c r="F1" s="188"/>
       <c r="G1" s="188"/>
       <c r="H1" s="105"/>
-      <c r="I1" s="422"/>
-      <c r="J1" s="422"/>
+      <c r="I1" s="402"/>
+      <c r="J1" s="402"/>
       <c r="L1" s="30"/>
       <c r="M1" s="30"/>
     </row>
@@ -11712,13 +11712,13 @@
       </c>
     </row>
     <row r="3" spans="1:138" ht="44.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="490">
+      <c r="A3" s="476">
         <v>1</v>
       </c>
-      <c r="B3" s="425" t="s">
+      <c r="B3" s="405" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="492" t="s">
+      <c r="C3" s="478" t="s">
         <v>340</v>
       </c>
       <c r="D3" s="73" t="s">
@@ -11746,9 +11746,9 @@
       </c>
     </row>
     <row r="4" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A4" s="491"/>
-      <c r="B4" s="426"/>
-      <c r="C4" s="493"/>
+      <c r="A4" s="477"/>
+      <c r="B4" s="406"/>
+      <c r="C4" s="479"/>
       <c r="D4" s="73" t="s">
         <v>56</v>
       </c>
@@ -11770,9 +11770,9 @@
       <c r="M4" s="76"/>
     </row>
     <row r="5" spans="1:138" ht="75" x14ac:dyDescent="0.2">
-      <c r="A5" s="491"/>
-      <c r="B5" s="426"/>
-      <c r="C5" s="493"/>
+      <c r="A5" s="477"/>
+      <c r="B5" s="406"/>
+      <c r="C5" s="479"/>
       <c r="D5" s="73" t="s">
         <v>55</v>
       </c>
@@ -11794,9 +11794,9 @@
       <c r="M5" s="76"/>
     </row>
     <row r="6" spans="1:138" ht="240" x14ac:dyDescent="0.2">
-      <c r="A6" s="491"/>
-      <c r="B6" s="426"/>
-      <c r="C6" s="493"/>
+      <c r="A6" s="477"/>
+      <c r="B6" s="406"/>
+      <c r="C6" s="479"/>
       <c r="D6" s="73" t="s">
         <v>63</v>
       </c>
@@ -11819,9 +11819,9 @@
       <c r="M6" s="76"/>
     </row>
     <row r="7" spans="1:138" ht="180" x14ac:dyDescent="0.2">
-      <c r="A7" s="491"/>
-      <c r="B7" s="426"/>
-      <c r="C7" s="493"/>
+      <c r="A7" s="477"/>
+      <c r="B7" s="406"/>
+      <c r="C7" s="479"/>
       <c r="D7" s="73" t="s">
         <v>68</v>
       </c>
@@ -11843,9 +11843,9 @@
       <c r="M7" s="76"/>
     </row>
     <row r="8" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A8" s="491"/>
-      <c r="B8" s="426"/>
-      <c r="C8" s="493"/>
+      <c r="A8" s="477"/>
+      <c r="B8" s="406"/>
+      <c r="C8" s="479"/>
       <c r="D8" s="73" t="s">
         <v>72</v>
       </c>
@@ -11867,9 +11867,9 @@
       <c r="M8" s="76"/>
     </row>
     <row r="9" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A9" s="491"/>
-      <c r="B9" s="426"/>
-      <c r="C9" s="493"/>
+      <c r="A9" s="477"/>
+      <c r="B9" s="406"/>
+      <c r="C9" s="479"/>
       <c r="D9" s="73" t="s">
         <v>86</v>
       </c>
@@ -11893,9 +11893,9 @@
       <c r="M9" s="76"/>
     </row>
     <row r="10" spans="1:138" s="42" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="491"/>
-      <c r="B10" s="426"/>
-      <c r="C10" s="493"/>
+      <c r="A10" s="477"/>
+      <c r="B10" s="406"/>
+      <c r="C10" s="479"/>
       <c r="D10" s="73" t="s">
         <v>92</v>
       </c>
@@ -12045,9 +12045,9 @@
       <c r="EH10" s="41"/>
     </row>
     <row r="11" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A11" s="491"/>
-      <c r="B11" s="426"/>
-      <c r="C11" s="494"/>
+      <c r="A11" s="477"/>
+      <c r="B11" s="406"/>
+      <c r="C11" s="480"/>
       <c r="D11" s="73" t="s">
         <v>282</v>
       </c>
@@ -12069,13 +12069,13 @@
       <c r="M11" s="76"/>
     </row>
     <row r="12" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="495">
+      <c r="A12" s="481">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B12" s="496" t="s">
+      <c r="B12" s="482" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="430" t="s">
+      <c r="C12" s="412" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="73" t="s">
@@ -12101,9 +12101,9 @@
       <c r="M12" s="76"/>
     </row>
     <row r="13" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A13" s="495"/>
-      <c r="B13" s="496"/>
-      <c r="C13" s="431"/>
+      <c r="A13" s="481"/>
+      <c r="B13" s="482"/>
+      <c r="C13" s="413"/>
       <c r="D13" s="73" t="s">
         <v>56</v>
       </c>
@@ -12129,9 +12129,9 @@
       <c r="M13" s="76"/>
     </row>
     <row r="14" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A14" s="495"/>
-      <c r="B14" s="496"/>
-      <c r="C14" s="431"/>
+      <c r="A14" s="481"/>
+      <c r="B14" s="482"/>
+      <c r="C14" s="413"/>
       <c r="D14" s="237" t="s">
         <v>284</v>
       </c>
@@ -12167,9 +12167,9 @@
       <c r="M14" s="76"/>
     </row>
     <row r="15" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="495"/>
-      <c r="B15" s="496"/>
-      <c r="C15" s="431"/>
+      <c r="A15" s="481"/>
+      <c r="B15" s="482"/>
+      <c r="C15" s="413"/>
       <c r="D15" s="237" t="s">
         <v>286</v>
       </c>
@@ -12188,9 +12188,9 @@
       <c r="M15" s="76"/>
     </row>
     <row r="16" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A16" s="495"/>
-      <c r="B16" s="496"/>
-      <c r="C16" s="431"/>
+      <c r="A16" s="481"/>
+      <c r="B16" s="482"/>
+      <c r="C16" s="413"/>
       <c r="D16" s="76" t="s">
         <v>106</v>
       </c>
@@ -12351,9 +12351,9 @@
       <c r="EH16" s="36"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A17" s="495"/>
-      <c r="B17" s="496"/>
-      <c r="C17" s="431"/>
+      <c r="A17" s="481"/>
+      <c r="B17" s="482"/>
+      <c r="C17" s="413"/>
       <c r="D17" s="76" t="s">
         <v>92</v>
       </c>
@@ -12514,9 +12514,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A18" s="490"/>
-      <c r="B18" s="497"/>
-      <c r="C18" s="431"/>
+      <c r="A18" s="476"/>
+      <c r="B18" s="483"/>
+      <c r="C18" s="413"/>
       <c r="D18" s="78" t="s">
         <v>282</v>
       </c>
@@ -12538,13 +12538,13 @@
       <c r="M18" s="76"/>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="476">
+      <c r="A19" s="484">
         <v>2</v>
       </c>
-      <c r="B19" s="477" t="s">
+      <c r="B19" s="485" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="478" t="s">
+      <c r="C19" s="486" t="s">
         <v>326</v>
       </c>
       <c r="D19" s="73" t="s">
@@ -12570,9 +12570,9 @@
       <c r="M19" s="76"/>
     </row>
     <row r="20" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A20" s="476"/>
-      <c r="B20" s="477"/>
-      <c r="C20" s="479"/>
+      <c r="A20" s="484"/>
+      <c r="B20" s="485"/>
+      <c r="C20" s="487"/>
       <c r="D20" s="73" t="s">
         <v>56</v>
       </c>
@@ -12598,9 +12598,9 @@
       <c r="M20" s="76"/>
     </row>
     <row r="21" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A21" s="476"/>
-      <c r="B21" s="477"/>
-      <c r="C21" s="479"/>
+      <c r="A21" s="484"/>
+      <c r="B21" s="485"/>
+      <c r="C21" s="487"/>
       <c r="D21" s="240" t="s">
         <v>284</v>
       </c>
@@ -12631,9 +12631,9 @@
       <c r="M21" s="76"/>
     </row>
     <row r="22" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A22" s="476"/>
-      <c r="B22" s="477"/>
-      <c r="C22" s="480"/>
+      <c r="A22" s="484"/>
+      <c r="B22" s="485"/>
+      <c r="C22" s="488"/>
       <c r="D22" s="237" t="s">
         <v>286</v>
       </c>
@@ -12651,9 +12651,9 @@
       <c r="M22" s="76"/>
     </row>
     <row r="23" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A23" s="476"/>
-      <c r="B23" s="477"/>
-      <c r="C23" s="479"/>
+      <c r="A23" s="484"/>
+      <c r="B23" s="485"/>
+      <c r="C23" s="487"/>
       <c r="D23" s="88" t="s">
         <v>114</v>
       </c>
@@ -12810,9 +12810,9 @@
       <c r="EH23" s="36"/>
     </row>
     <row r="24" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A24" s="476"/>
-      <c r="B24" s="477"/>
-      <c r="C24" s="479"/>
+      <c r="A24" s="484"/>
+      <c r="B24" s="485"/>
+      <c r="C24" s="487"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
       </c>
@@ -12969,9 +12969,9 @@
       <c r="EH24" s="36"/>
     </row>
     <row r="25" spans="1:138" ht="196.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="476"/>
-      <c r="B25" s="477"/>
-      <c r="C25" s="480"/>
+      <c r="A25" s="484"/>
+      <c r="B25" s="485"/>
+      <c r="C25" s="488"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
       </c>
@@ -12993,13 +12993,13 @@
       <c r="M25" s="76"/>
     </row>
     <row r="26" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A26" s="481">
+      <c r="A26" s="489">
         <v>2.1</v>
       </c>
-      <c r="B26" s="484" t="s">
+      <c r="B26" s="492" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="487" t="s">
+      <c r="C26" s="495" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="237" t="s">
@@ -13025,9 +13025,9 @@
       <c r="M26" s="76"/>
     </row>
     <row r="27" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A27" s="482"/>
-      <c r="B27" s="485"/>
-      <c r="C27" s="488"/>
+      <c r="A27" s="490"/>
+      <c r="B27" s="493"/>
+      <c r="C27" s="496"/>
       <c r="D27" s="237" t="s">
         <v>122</v>
       </c>
@@ -13047,9 +13047,9 @@
       <c r="M27" s="76"/>
     </row>
     <row r="28" spans="1:138" ht="135" x14ac:dyDescent="0.2">
-      <c r="A28" s="482"/>
-      <c r="B28" s="485"/>
-      <c r="C28" s="488"/>
+      <c r="A28" s="490"/>
+      <c r="B28" s="493"/>
+      <c r="C28" s="496"/>
       <c r="D28" s="76" t="s">
         <v>130</v>
       </c>
@@ -13073,9 +13073,9 @@
       <c r="M28" s="76"/>
     </row>
     <row r="29" spans="1:138" ht="75" x14ac:dyDescent="0.2">
-      <c r="A29" s="482"/>
-      <c r="B29" s="485"/>
-      <c r="C29" s="488"/>
+      <c r="A29" s="490"/>
+      <c r="B29" s="493"/>
+      <c r="C29" s="496"/>
       <c r="D29" s="189" t="s">
         <v>55</v>
       </c>
@@ -13099,9 +13099,9 @@
       <c r="M29" s="76"/>
     </row>
     <row r="30" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A30" s="482"/>
-      <c r="B30" s="485"/>
-      <c r="C30" s="488"/>
+      <c r="A30" s="490"/>
+      <c r="B30" s="493"/>
+      <c r="C30" s="496"/>
       <c r="D30" s="37" t="s">
         <v>134</v>
       </c>
@@ -13125,9 +13125,9 @@
       </c>
     </row>
     <row r="31" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A31" s="482"/>
-      <c r="B31" s="485"/>
-      <c r="C31" s="488"/>
+      <c r="A31" s="490"/>
+      <c r="B31" s="493"/>
+      <c r="C31" s="496"/>
       <c r="D31" s="88" t="s">
         <v>114</v>
       </c>
@@ -13151,9 +13151,9 @@
       <c r="M31" s="76"/>
     </row>
     <row r="32" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A32" s="482"/>
-      <c r="B32" s="485"/>
-      <c r="C32" s="488"/>
+      <c r="A32" s="490"/>
+      <c r="B32" s="493"/>
+      <c r="C32" s="496"/>
       <c r="D32" s="86" t="s">
         <v>92</v>
       </c>
@@ -13177,9 +13177,9 @@
       <c r="M32" s="76"/>
     </row>
     <row r="33" spans="1:13" ht="45" x14ac:dyDescent="0.2">
-      <c r="A33" s="483"/>
-      <c r="B33" s="486"/>
-      <c r="C33" s="489"/>
+      <c r="A33" s="491"/>
+      <c r="B33" s="494"/>
+      <c r="C33" s="497"/>
       <c r="D33" s="76" t="s">
         <v>94</v>
       </c>
@@ -13338,13 +13338,6 @@
   </sheetData>
   <autoFilter ref="A2:EH34" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="16">
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A3:A11"/>
-    <mergeCell ref="B3:B11"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="A12:A18"/>
-    <mergeCell ref="B12:B18"/>
-    <mergeCell ref="C12:C18"/>
     <mergeCell ref="A34:A38"/>
     <mergeCell ref="B34:B38"/>
     <mergeCell ref="C34:C38"/>
@@ -13354,6 +13347,13 @@
     <mergeCell ref="A26:A33"/>
     <mergeCell ref="B26:B33"/>
     <mergeCell ref="C26:C33"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A3:A11"/>
+    <mergeCell ref="B3:B11"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="A12:A18"/>
+    <mergeCell ref="B12:B18"/>
+    <mergeCell ref="C12:C18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -13392,8 +13392,8 @@
       <c r="F1" s="188"/>
       <c r="G1" s="188"/>
       <c r="H1" s="105"/>
-      <c r="I1" s="422"/>
-      <c r="J1" s="422"/>
+      <c r="I1" s="402"/>
+      <c r="J1" s="402"/>
       <c r="L1" s="30"/>
       <c r="M1" s="30"/>
     </row>
@@ -13434,10 +13434,10 @@
       </c>
     </row>
     <row r="3" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A3" s="490">
+      <c r="A3" s="476">
         <v>1</v>
       </c>
-      <c r="B3" s="425" t="s">
+      <c r="B3" s="405" t="s">
         <v>50</v>
       </c>
       <c r="C3" s="509" t="s">
@@ -13468,9 +13468,9 @@
       </c>
     </row>
     <row r="4" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A4" s="491"/>
-      <c r="B4" s="426"/>
-      <c r="C4" s="473"/>
+      <c r="A4" s="477"/>
+      <c r="B4" s="406"/>
+      <c r="C4" s="472"/>
       <c r="D4" s="73" t="s">
         <v>56</v>
       </c>
@@ -13492,9 +13492,9 @@
       <c r="M4" s="76"/>
     </row>
     <row r="5" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A5" s="491"/>
-      <c r="B5" s="426"/>
-      <c r="C5" s="473"/>
+      <c r="A5" s="477"/>
+      <c r="B5" s="406"/>
+      <c r="C5" s="472"/>
       <c r="D5" s="73" t="s">
         <v>55</v>
       </c>
@@ -13516,9 +13516,9 @@
       <c r="M5" s="76"/>
     </row>
     <row r="6" spans="1:138" ht="210" x14ac:dyDescent="0.2">
-      <c r="A6" s="491"/>
-      <c r="B6" s="426"/>
-      <c r="C6" s="473"/>
+      <c r="A6" s="477"/>
+      <c r="B6" s="406"/>
+      <c r="C6" s="472"/>
       <c r="D6" s="73" t="s">
         <v>63</v>
       </c>
@@ -13541,9 +13541,9 @@
       <c r="M6" s="76"/>
     </row>
     <row r="7" spans="1:138" ht="150" x14ac:dyDescent="0.2">
-      <c r="A7" s="491"/>
-      <c r="B7" s="426"/>
-      <c r="C7" s="473"/>
+      <c r="A7" s="477"/>
+      <c r="B7" s="406"/>
+      <c r="C7" s="472"/>
       <c r="D7" s="73" t="s">
         <v>68</v>
       </c>
@@ -13565,9 +13565,9 @@
       <c r="M7" s="76"/>
     </row>
     <row r="8" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A8" s="491"/>
-      <c r="B8" s="426"/>
-      <c r="C8" s="473"/>
+      <c r="A8" s="477"/>
+      <c r="B8" s="406"/>
+      <c r="C8" s="472"/>
       <c r="D8" s="73" t="s">
         <v>72</v>
       </c>
@@ -13589,9 +13589,9 @@
       <c r="M8" s="76"/>
     </row>
     <row r="9" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A9" s="491"/>
-      <c r="B9" s="426"/>
-      <c r="C9" s="473"/>
+      <c r="A9" s="477"/>
+      <c r="B9" s="406"/>
+      <c r="C9" s="472"/>
       <c r="D9" s="73" t="s">
         <v>86</v>
       </c>
@@ -13629,9 +13629,9 @@
       <c r="M9" s="76"/>
     </row>
     <row r="10" spans="1:138" s="42" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A10" s="491"/>
-      <c r="B10" s="426"/>
-      <c r="C10" s="473"/>
+      <c r="A10" s="477"/>
+      <c r="B10" s="406"/>
+      <c r="C10" s="472"/>
       <c r="D10" s="73" t="s">
         <v>92</v>
       </c>
@@ -13795,9 +13795,9 @@
       <c r="EH10" s="41"/>
     </row>
     <row r="11" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A11" s="491"/>
-      <c r="B11" s="426"/>
-      <c r="C11" s="473"/>
+      <c r="A11" s="477"/>
+      <c r="B11" s="406"/>
+      <c r="C11" s="472"/>
       <c r="D11" s="73" t="s">
         <v>282</v>
       </c>
@@ -13819,13 +13819,13 @@
       <c r="M11" s="76"/>
     </row>
     <row r="12" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="495">
+      <c r="A12" s="481">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B12" s="496" t="s">
+      <c r="B12" s="482" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="430" t="s">
+      <c r="C12" s="412" t="s">
         <v>99</v>
       </c>
       <c r="D12" s="73" t="s">
@@ -13851,9 +13851,9 @@
       <c r="M12" s="76"/>
     </row>
     <row r="13" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A13" s="495"/>
-      <c r="B13" s="496"/>
-      <c r="C13" s="431"/>
+      <c r="A13" s="481"/>
+      <c r="B13" s="482"/>
+      <c r="C13" s="413"/>
       <c r="D13" s="73" t="s">
         <v>56</v>
       </c>
@@ -13879,9 +13879,9 @@
       <c r="M13" s="76"/>
     </row>
     <row r="14" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A14" s="495"/>
-      <c r="B14" s="496"/>
-      <c r="C14" s="431"/>
+      <c r="A14" s="481"/>
+      <c r="B14" s="482"/>
+      <c r="C14" s="413"/>
       <c r="D14" s="73" t="s">
         <v>55</v>
       </c>
@@ -13917,9 +13917,9 @@
       <c r="M14" s="76"/>
     </row>
     <row r="15" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A15" s="495"/>
-      <c r="B15" s="496"/>
-      <c r="C15" s="431"/>
+      <c r="A15" s="481"/>
+      <c r="B15" s="482"/>
+      <c r="C15" s="413"/>
       <c r="D15" s="76" t="s">
         <v>106</v>
       </c>
@@ -14080,9 +14080,9 @@
       <c r="EH15" s="36"/>
     </row>
     <row r="16" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A16" s="495"/>
-      <c r="B16" s="496"/>
-      <c r="C16" s="431"/>
+      <c r="A16" s="481"/>
+      <c r="B16" s="482"/>
+      <c r="C16" s="413"/>
       <c r="D16" s="76" t="s">
         <v>92</v>
       </c>
@@ -14243,9 +14243,9 @@
       <c r="EH16" s="36"/>
     </row>
     <row r="17" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A17" s="490"/>
-      <c r="B17" s="497"/>
-      <c r="C17" s="431"/>
+      <c r="A17" s="476"/>
+      <c r="B17" s="483"/>
+      <c r="C17" s="413"/>
       <c r="D17" s="78" t="s">
         <v>282</v>
       </c>
@@ -14267,13 +14267,13 @@
       <c r="M17" s="76"/>
     </row>
     <row r="18" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A18" s="476">
+      <c r="A18" s="484">
         <v>2</v>
       </c>
-      <c r="B18" s="477" t="s">
+      <c r="B18" s="485" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="478" t="s">
+      <c r="C18" s="486" t="s">
         <v>352</v>
       </c>
       <c r="D18" s="73" t="s">
@@ -14299,9 +14299,9 @@
       <c r="M18" s="76"/>
     </row>
     <row r="19" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A19" s="476"/>
-      <c r="B19" s="477"/>
-      <c r="C19" s="479"/>
+      <c r="A19" s="484"/>
+      <c r="B19" s="485"/>
+      <c r="C19" s="487"/>
       <c r="D19" s="73" t="s">
         <v>56</v>
       </c>
@@ -14327,9 +14327,9 @@
       <c r="M19" s="76"/>
     </row>
     <row r="20" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A20" s="476"/>
-      <c r="B20" s="477"/>
-      <c r="C20" s="479"/>
+      <c r="A20" s="484"/>
+      <c r="B20" s="485"/>
+      <c r="C20" s="487"/>
       <c r="D20" s="73" t="s">
         <v>55</v>
       </c>
@@ -14360,9 +14360,9 @@
       <c r="M20" s="76"/>
     </row>
     <row r="21" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A21" s="476"/>
-      <c r="B21" s="477"/>
-      <c r="C21" s="479"/>
+      <c r="A21" s="484"/>
+      <c r="B21" s="485"/>
+      <c r="C21" s="487"/>
       <c r="D21" s="61" t="s">
         <v>114</v>
       </c>
@@ -14519,9 +14519,9 @@
       <c r="EH21" s="36"/>
     </row>
     <row r="22" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A22" s="476"/>
-      <c r="B22" s="477"/>
-      <c r="C22" s="479"/>
+      <c r="A22" s="484"/>
+      <c r="B22" s="485"/>
+      <c r="C22" s="487"/>
       <c r="D22" s="86" t="s">
         <v>92</v>
       </c>
@@ -14678,9 +14678,9 @@
       <c r="EH22" s="36"/>
     </row>
     <row r="23" spans="1:138" ht="196.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="476"/>
-      <c r="B23" s="477"/>
-      <c r="C23" s="480"/>
+      <c r="A23" s="484"/>
+      <c r="B23" s="485"/>
+      <c r="C23" s="488"/>
       <c r="D23" s="76" t="s">
         <v>94</v>
       </c>
@@ -14702,13 +14702,13 @@
       <c r="M23" s="76"/>
     </row>
     <row r="24" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A24" s="481">
+      <c r="A24" s="489">
         <v>2.1</v>
       </c>
-      <c r="B24" s="484" t="s">
+      <c r="B24" s="492" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="487" t="s">
+      <c r="C24" s="495" t="s">
         <v>117</v>
       </c>
       <c r="D24" s="76" t="s">
@@ -14734,9 +14734,9 @@
       <c r="M24" s="76"/>
     </row>
     <row r="25" spans="1:138" ht="105" x14ac:dyDescent="0.2">
-      <c r="A25" s="482"/>
-      <c r="B25" s="485"/>
-      <c r="C25" s="488"/>
+      <c r="A25" s="490"/>
+      <c r="B25" s="493"/>
+      <c r="C25" s="496"/>
       <c r="D25" s="76" t="s">
         <v>130</v>
       </c>
@@ -14760,9 +14760,9 @@
       <c r="M25" s="76"/>
     </row>
     <row r="26" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A26" s="482"/>
-      <c r="B26" s="485"/>
-      <c r="C26" s="488"/>
+      <c r="A26" s="490"/>
+      <c r="B26" s="493"/>
+      <c r="C26" s="496"/>
       <c r="D26" s="189" t="s">
         <v>55</v>
       </c>
@@ -14786,9 +14786,9 @@
       <c r="M26" s="76"/>
     </row>
     <row r="27" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A27" s="482"/>
-      <c r="B27" s="485"/>
-      <c r="C27" s="488"/>
+      <c r="A27" s="490"/>
+      <c r="B27" s="493"/>
+      <c r="C27" s="496"/>
       <c r="D27" s="37" t="s">
         <v>134</v>
       </c>
@@ -14812,9 +14812,9 @@
       </c>
     </row>
     <row r="28" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A28" s="482"/>
-      <c r="B28" s="485"/>
-      <c r="C28" s="488"/>
+      <c r="A28" s="490"/>
+      <c r="B28" s="493"/>
+      <c r="C28" s="496"/>
       <c r="D28" s="88" t="s">
         <v>114</v>
       </c>
@@ -14838,9 +14838,9 @@
       <c r="M28" s="76"/>
     </row>
     <row r="29" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" s="482"/>
-      <c r="B29" s="485"/>
-      <c r="C29" s="488"/>
+      <c r="A29" s="490"/>
+      <c r="B29" s="493"/>
+      <c r="C29" s="496"/>
       <c r="D29" s="86" t="s">
         <v>92</v>
       </c>
@@ -14864,9 +14864,9 @@
       <c r="M29" s="76"/>
     </row>
     <row r="30" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="483"/>
-      <c r="B30" s="486"/>
-      <c r="C30" s="489"/>
+      <c r="A30" s="491"/>
+      <c r="B30" s="494"/>
+      <c r="C30" s="497"/>
       <c r="D30" s="76" t="s">
         <v>94</v>
       </c>
@@ -15025,13 +15025,6 @@
   </sheetData>
   <autoFilter ref="A2:EH31" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="16">
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A3:A11"/>
-    <mergeCell ref="B3:B11"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="B12:B17"/>
-    <mergeCell ref="C12:C17"/>
     <mergeCell ref="A31:A35"/>
     <mergeCell ref="B31:B35"/>
     <mergeCell ref="C31:C35"/>
@@ -15041,6 +15034,13 @@
     <mergeCell ref="A24:A30"/>
     <mergeCell ref="B24:B30"/>
     <mergeCell ref="C24:C30"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A3:A11"/>
+    <mergeCell ref="B3:B11"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="B12:B17"/>
+    <mergeCell ref="C12:C17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -15902,10 +15902,10 @@
       <c r="F1" s="188"/>
       <c r="G1" s="188"/>
       <c r="H1" s="105"/>
-      <c r="I1" s="422" t="s">
+      <c r="I1" s="402" t="s">
         <v>381</v>
       </c>
-      <c r="J1" s="422"/>
+      <c r="J1" s="402"/>
     </row>
     <row r="2" spans="1:138" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="26" t="s">
@@ -15938,13 +15938,13 @@
       </c>
     </row>
     <row r="3" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A3" s="490">
+      <c r="A3" s="476">
         <v>1</v>
       </c>
-      <c r="B3" s="425" t="s">
+      <c r="B3" s="405" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="430" t="s">
+      <c r="C3" s="412" t="s">
         <v>382</v>
       </c>
       <c r="D3" s="73" t="s">
@@ -15966,9 +15966,9 @@
       </c>
     </row>
     <row r="4" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A4" s="491"/>
-      <c r="B4" s="426"/>
-      <c r="C4" s="431"/>
+      <c r="A4" s="477"/>
+      <c r="B4" s="406"/>
+      <c r="C4" s="413"/>
       <c r="D4" s="73" t="s">
         <v>56</v>
       </c>
@@ -15988,9 +15988,9 @@
       </c>
     </row>
     <row r="5" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A5" s="491"/>
-      <c r="B5" s="426"/>
-      <c r="C5" s="431"/>
+      <c r="A5" s="477"/>
+      <c r="B5" s="406"/>
+      <c r="C5" s="413"/>
       <c r="D5" s="73" t="s">
         <v>55</v>
       </c>
@@ -16010,9 +16010,9 @@
       </c>
     </row>
     <row r="6" spans="1:138" ht="210" x14ac:dyDescent="0.2">
-      <c r="A6" s="491"/>
-      <c r="B6" s="426"/>
-      <c r="C6" s="431"/>
+      <c r="A6" s="477"/>
+      <c r="B6" s="406"/>
+      <c r="C6" s="413"/>
       <c r="D6" s="73" t="s">
         <v>63</v>
       </c>
@@ -16033,9 +16033,9 @@
       <c r="K6" s="38"/>
     </row>
     <row r="7" spans="1:138" ht="150" x14ac:dyDescent="0.2">
-      <c r="A7" s="491"/>
-      <c r="B7" s="426"/>
-      <c r="C7" s="431"/>
+      <c r="A7" s="477"/>
+      <c r="B7" s="406"/>
+      <c r="C7" s="413"/>
       <c r="D7" s="73" t="s">
         <v>68</v>
       </c>
@@ -16055,9 +16055,9 @@
       </c>
     </row>
     <row r="8" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A8" s="491"/>
-      <c r="B8" s="426"/>
-      <c r="C8" s="431"/>
+      <c r="A8" s="477"/>
+      <c r="B8" s="406"/>
+      <c r="C8" s="413"/>
       <c r="D8" s="73" t="s">
         <v>72</v>
       </c>
@@ -16077,9 +16077,9 @@
       </c>
     </row>
     <row r="9" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A9" s="491"/>
-      <c r="B9" s="426"/>
-      <c r="C9" s="431"/>
+      <c r="A9" s="477"/>
+      <c r="B9" s="406"/>
+      <c r="C9" s="413"/>
       <c r="D9" s="73" t="s">
         <v>86</v>
       </c>
@@ -16113,9 +16113,9 @@
       </c>
     </row>
     <row r="10" spans="1:138" s="42" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A10" s="491"/>
-      <c r="B10" s="426"/>
-      <c r="C10" s="431"/>
+      <c r="A10" s="477"/>
+      <c r="B10" s="406"/>
+      <c r="C10" s="413"/>
       <c r="D10" s="73" t="s">
         <v>92</v>
       </c>
@@ -16277,9 +16277,9 @@
       <c r="EH10" s="41"/>
     </row>
     <row r="11" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A11" s="491"/>
-      <c r="B11" s="426"/>
-      <c r="C11" s="431"/>
+      <c r="A11" s="477"/>
+      <c r="B11" s="406"/>
+      <c r="C11" s="413"/>
       <c r="D11" s="73" t="s">
         <v>282</v>
       </c>
@@ -16299,13 +16299,13 @@
       </c>
     </row>
     <row r="12" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A12" s="495">
+      <c r="A12" s="481">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B12" s="496" t="s">
+      <c r="B12" s="482" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="430" t="s">
+      <c r="C12" s="412" t="s">
         <v>383</v>
       </c>
       <c r="D12" s="73" t="s">
@@ -16327,9 +16327,9 @@
       </c>
     </row>
     <row r="13" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="495"/>
-      <c r="B13" s="496"/>
-      <c r="C13" s="431"/>
+      <c r="A13" s="481"/>
+      <c r="B13" s="482"/>
+      <c r="C13" s="413"/>
       <c r="D13" s="73" t="s">
         <v>56</v>
       </c>
@@ -16351,9 +16351,9 @@
       </c>
     </row>
     <row r="14" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A14" s="495"/>
-      <c r="B14" s="496"/>
-      <c r="C14" s="431"/>
+      <c r="A14" s="481"/>
+      <c r="B14" s="482"/>
+      <c r="C14" s="413"/>
       <c r="D14" s="73" t="s">
         <v>55</v>
       </c>
@@ -16388,9 +16388,9 @@
       <c r="K14" s="38"/>
     </row>
     <row r="15" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A15" s="495"/>
-      <c r="B15" s="496"/>
-      <c r="C15" s="431"/>
+      <c r="A15" s="481"/>
+      <c r="B15" s="482"/>
+      <c r="C15" s="413"/>
       <c r="D15" s="76" t="s">
         <v>106</v>
       </c>
@@ -16552,9 +16552,9 @@
       <c r="EH15" s="36"/>
     </row>
     <row r="16" spans="1:138" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A16" s="495"/>
-      <c r="B16" s="496"/>
-      <c r="C16" s="431"/>
+      <c r="A16" s="481"/>
+      <c r="B16" s="482"/>
+      <c r="C16" s="413"/>
       <c r="D16" s="76" t="s">
         <v>92</v>
       </c>
@@ -16716,9 +16716,9 @@
       <c r="EH16" s="36"/>
     </row>
     <row r="17" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A17" s="490"/>
-      <c r="B17" s="497"/>
-      <c r="C17" s="431"/>
+      <c r="A17" s="476"/>
+      <c r="B17" s="483"/>
+      <c r="C17" s="413"/>
       <c r="D17" s="78" t="s">
         <v>282</v>
       </c>
@@ -16738,13 +16738,13 @@
       </c>
     </row>
     <row r="18" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A18" s="476">
+      <c r="A18" s="484">
         <v>2</v>
       </c>
-      <c r="B18" s="477" t="s">
+      <c r="B18" s="485" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="470" t="s">
+      <c r="C18" s="469" t="s">
         <v>384</v>
       </c>
       <c r="D18" s="73" t="s">
@@ -16766,8 +16766,8 @@
       </c>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="476"/>
-      <c r="B19" s="477"/>
+      <c r="A19" s="484"/>
+      <c r="B19" s="485"/>
       <c r="C19" s="519"/>
       <c r="D19" s="73" t="s">
         <v>56</v>
@@ -16790,8 +16790,8 @@
       </c>
     </row>
     <row r="20" spans="1:138" ht="90" x14ac:dyDescent="0.2">
-      <c r="A20" s="476"/>
-      <c r="B20" s="477"/>
+      <c r="A20" s="484"/>
+      <c r="B20" s="485"/>
       <c r="C20" s="519"/>
       <c r="D20" s="73" t="s">
         <v>55</v>
@@ -16814,8 +16814,8 @@
       </c>
     </row>
     <row r="21" spans="1:138" s="47" customFormat="1" ht="90" x14ac:dyDescent="0.2">
-      <c r="A21" s="476"/>
-      <c r="B21" s="477"/>
+      <c r="A21" s="484"/>
+      <c r="B21" s="485"/>
       <c r="C21" s="519"/>
       <c r="D21" s="61" t="s">
         <v>114</v>
@@ -16966,8 +16966,8 @@
       <c r="EH21" s="36"/>
     </row>
     <row r="22" spans="1:138" s="47" customFormat="1" ht="90" x14ac:dyDescent="0.2">
-      <c r="A22" s="476"/>
-      <c r="B22" s="477"/>
+      <c r="A22" s="484"/>
+      <c r="B22" s="485"/>
       <c r="C22" s="519"/>
       <c r="D22" s="86" t="s">
         <v>92</v>
@@ -17118,8 +17118,8 @@
       <c r="EH22" s="36"/>
     </row>
     <row r="23" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A23" s="476"/>
-      <c r="B23" s="477"/>
+      <c r="A23" s="484"/>
+      <c r="B23" s="485"/>
       <c r="C23" s="520"/>
       <c r="D23" s="76" t="s">
         <v>94</v>
@@ -17140,13 +17140,13 @@
       </c>
     </row>
     <row r="24" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A24" s="481">
+      <c r="A24" s="489">
         <v>2.1</v>
       </c>
-      <c r="B24" s="484" t="s">
+      <c r="B24" s="492" t="s">
         <v>116</v>
       </c>
-      <c r="C24" s="487" t="s">
+      <c r="C24" s="495" t="s">
         <v>117</v>
       </c>
       <c r="D24" s="83" t="s">
@@ -17171,9 +17171,9 @@
       </c>
     </row>
     <row r="25" spans="1:138" ht="105" x14ac:dyDescent="0.2">
-      <c r="A25" s="482"/>
-      <c r="B25" s="485"/>
-      <c r="C25" s="488"/>
+      <c r="A25" s="490"/>
+      <c r="B25" s="493"/>
+      <c r="C25" s="496"/>
       <c r="D25" s="83" t="s">
         <v>130</v>
       </c>
@@ -17196,9 +17196,9 @@
       </c>
     </row>
     <row r="26" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A26" s="482"/>
-      <c r="B26" s="485"/>
-      <c r="C26" s="488"/>
+      <c r="A26" s="490"/>
+      <c r="B26" s="493"/>
+      <c r="C26" s="496"/>
       <c r="D26" s="73" t="s">
         <v>55</v>
       </c>
@@ -17223,9 +17223,9 @@
       </c>
     </row>
     <row r="27" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A27" s="482"/>
-      <c r="B27" s="485"/>
-      <c r="C27" s="488"/>
+      <c r="A27" s="490"/>
+      <c r="B27" s="493"/>
+      <c r="C27" s="496"/>
       <c r="D27" s="61" t="s">
         <v>114</v>
       </c>
@@ -17247,9 +17247,9 @@
       </c>
     </row>
     <row r="28" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A28" s="482"/>
-      <c r="B28" s="485"/>
-      <c r="C28" s="488"/>
+      <c r="A28" s="490"/>
+      <c r="B28" s="493"/>
+      <c r="C28" s="496"/>
       <c r="D28" s="86" t="s">
         <v>92</v>
       </c>
@@ -17271,9 +17271,9 @@
       </c>
     </row>
     <row r="29" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" s="483"/>
-      <c r="B29" s="486"/>
-      <c r="C29" s="489"/>
+      <c r="A29" s="491"/>
+      <c r="B29" s="494"/>
+      <c r="C29" s="497"/>
       <c r="D29" s="76" t="s">
         <v>94</v>
       </c>
@@ -17415,6 +17415,13 @@
   </sheetData>
   <autoFilter ref="A2:EH30" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="16">
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A3:A11"/>
+    <mergeCell ref="B3:B11"/>
+    <mergeCell ref="C3:C11"/>
+    <mergeCell ref="A12:A17"/>
+    <mergeCell ref="B12:B17"/>
+    <mergeCell ref="C12:C17"/>
     <mergeCell ref="C30:C34"/>
     <mergeCell ref="B30:B34"/>
     <mergeCell ref="A30:A34"/>
@@ -17424,13 +17431,6 @@
     <mergeCell ref="A24:A29"/>
     <mergeCell ref="B24:B29"/>
     <mergeCell ref="C24:C29"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A3:A11"/>
-    <mergeCell ref="B3:B11"/>
-    <mergeCell ref="C3:C11"/>
-    <mergeCell ref="A12:A17"/>
-    <mergeCell ref="B12:B17"/>
-    <mergeCell ref="C12:C17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -17456,18 +17456,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:133" s="31" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="434" t="s">
+      <c r="A1" s="418" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="434"/>
-      <c r="C1" s="434"/>
-      <c r="D1" s="434"/>
-      <c r="E1" s="434"/>
-      <c r="F1" s="434"/>
-      <c r="G1" s="434"/>
+      <c r="B1" s="418"/>
+      <c r="C1" s="418"/>
+      <c r="D1" s="418"/>
+      <c r="E1" s="418"/>
+      <c r="F1" s="418"/>
+      <c r="G1" s="418"/>
       <c r="H1" s="310"/>
-      <c r="I1" s="422"/>
-      <c r="J1" s="422"/>
+      <c r="I1" s="402"/>
+      <c r="J1" s="402"/>
     </row>
     <row r="2" spans="1:133" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -17639,13 +17639,13 @@
       <c r="EC3" s="36"/>
     </row>
     <row r="4" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A4" s="423">
+      <c r="A4" s="403">
         <v>1</v>
       </c>
-      <c r="B4" s="425" t="s">
+      <c r="B4" s="405" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="427" t="s">
+      <c r="C4" s="407" t="s">
         <v>51</v>
       </c>
       <c r="D4" s="73" t="s">
@@ -17667,9 +17667,9 @@
       </c>
     </row>
     <row r="5" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A5" s="424"/>
-      <c r="B5" s="426"/>
-      <c r="C5" s="428"/>
+      <c r="A5" s="404"/>
+      <c r="B5" s="406"/>
+      <c r="C5" s="408"/>
       <c r="D5" s="73" t="s">
         <v>56</v>
       </c>
@@ -17689,9 +17689,9 @@
       </c>
     </row>
     <row r="6" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A6" s="424"/>
-      <c r="B6" s="426"/>
-      <c r="C6" s="428"/>
+      <c r="A6" s="404"/>
+      <c r="B6" s="406"/>
+      <c r="C6" s="408"/>
       <c r="D6" s="237" t="s">
         <v>61</v>
       </c>
@@ -17711,9 +17711,9 @@
       </c>
     </row>
     <row r="7" spans="1:133" ht="144" x14ac:dyDescent="0.2">
-      <c r="A7" s="424"/>
-      <c r="B7" s="426"/>
-      <c r="C7" s="428"/>
+      <c r="A7" s="404"/>
+      <c r="B7" s="406"/>
+      <c r="C7" s="408"/>
       <c r="D7" s="73" t="s">
         <v>63</v>
       </c>
@@ -17733,9 +17733,9 @@
       </c>
     </row>
     <row r="8" spans="1:133" ht="108" x14ac:dyDescent="0.2">
-      <c r="A8" s="424"/>
-      <c r="B8" s="426"/>
-      <c r="C8" s="428"/>
+      <c r="A8" s="404"/>
+      <c r="B8" s="406"/>
+      <c r="C8" s="408"/>
       <c r="D8" s="73" t="s">
         <v>68</v>
       </c>
@@ -17755,9 +17755,9 @@
       </c>
     </row>
     <row r="9" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A9" s="424"/>
-      <c r="B9" s="426"/>
-      <c r="C9" s="428"/>
+      <c r="A9" s="404"/>
+      <c r="B9" s="406"/>
+      <c r="C9" s="408"/>
       <c r="D9" s="73" t="s">
         <v>72</v>
       </c>
@@ -17777,9 +17777,9 @@
       </c>
     </row>
     <row r="10" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="424"/>
-      <c r="B10" s="426"/>
-      <c r="C10" s="428"/>
+      <c r="A10" s="404"/>
+      <c r="B10" s="406"/>
+      <c r="C10" s="408"/>
       <c r="D10" s="237" t="s">
         <v>76</v>
       </c>
@@ -17799,9 +17799,9 @@
       </c>
     </row>
     <row r="11" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A11" s="424"/>
-      <c r="B11" s="426"/>
-      <c r="C11" s="428"/>
+      <c r="A11" s="404"/>
+      <c r="B11" s="406"/>
+      <c r="C11" s="408"/>
       <c r="D11" s="237" t="s">
         <v>79</v>
       </c>
@@ -17823,9 +17823,9 @@
       </c>
     </row>
     <row r="12" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A12" s="424"/>
-      <c r="B12" s="426"/>
-      <c r="C12" s="428"/>
+      <c r="A12" s="404"/>
+      <c r="B12" s="406"/>
+      <c r="C12" s="408"/>
       <c r="D12" s="237" t="s">
         <v>83</v>
       </c>
@@ -17847,9 +17847,9 @@
       </c>
     </row>
     <row r="13" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A13" s="424"/>
-      <c r="B13" s="426"/>
-      <c r="C13" s="428"/>
+      <c r="A13" s="404"/>
+      <c r="B13" s="406"/>
+      <c r="C13" s="408"/>
       <c r="D13" s="73" t="s">
         <v>86</v>
       </c>
@@ -17871,9 +17871,9 @@
       </c>
     </row>
     <row r="14" spans="1:133" s="42" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A14" s="424"/>
-      <c r="B14" s="426"/>
-      <c r="C14" s="428"/>
+      <c r="A14" s="404"/>
+      <c r="B14" s="406"/>
+      <c r="C14" s="408"/>
       <c r="D14" s="73" t="s">
         <v>92</v>
       </c>
@@ -18018,9 +18018,9 @@
       <c r="EC14" s="41"/>
     </row>
     <row r="15" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A15" s="424"/>
-      <c r="B15" s="426"/>
-      <c r="C15" s="429"/>
+      <c r="A15" s="404"/>
+      <c r="B15" s="406"/>
+      <c r="C15" s="409"/>
       <c r="D15" s="73" t="s">
         <v>94</v>
       </c>
@@ -18040,13 +18040,13 @@
       </c>
     </row>
     <row r="16" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A16" s="415" t="s">
+      <c r="A16" s="410" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="416" t="s">
+      <c r="B16" s="411" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="430" t="s">
+      <c r="C16" s="412" t="s">
         <v>99</v>
       </c>
       <c r="D16" s="73" t="s">
@@ -18068,9 +18068,9 @@
       </c>
     </row>
     <row r="17" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="415"/>
-      <c r="B17" s="416"/>
-      <c r="C17" s="431"/>
+      <c r="A17" s="410"/>
+      <c r="B17" s="411"/>
+      <c r="C17" s="413"/>
       <c r="D17" s="73" t="s">
         <v>56</v>
       </c>
@@ -18092,9 +18092,9 @@
       </c>
     </row>
     <row r="18" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A18" s="415"/>
-      <c r="B18" s="416"/>
-      <c r="C18" s="431"/>
+      <c r="A18" s="410"/>
+      <c r="B18" s="411"/>
+      <c r="C18" s="413"/>
       <c r="D18" s="237" t="s">
         <v>61</v>
       </c>
@@ -18114,13 +18114,13 @@
       </c>
     </row>
     <row r="19" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="415"/>
-      <c r="B19" s="416"/>
-      <c r="C19" s="431"/>
-      <c r="D19" s="432" t="s">
+      <c r="A19" s="410"/>
+      <c r="B19" s="411"/>
+      <c r="C19" s="413"/>
+      <c r="D19" s="414" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="413" t="s">
+      <c r="E19" s="416" t="s">
         <v>77</v>
       </c>
       <c r="F19" s="73" t="s">
@@ -18136,11 +18136,11 @@
       </c>
     </row>
     <row r="20" spans="1:133" s="47" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="415"/>
-      <c r="B20" s="416"/>
-      <c r="C20" s="431"/>
-      <c r="D20" s="433"/>
-      <c r="E20" s="414"/>
+      <c r="A20" s="410"/>
+      <c r="B20" s="411"/>
+      <c r="C20" s="413"/>
+      <c r="D20" s="415"/>
+      <c r="E20" s="417"/>
       <c r="F20" s="73" t="s">
         <v>103</v>
       </c>
@@ -18277,9 +18277,9 @@
       <c r="EC20" s="36"/>
     </row>
     <row r="21" spans="1:133" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A21" s="415"/>
-      <c r="B21" s="416"/>
-      <c r="C21" s="431"/>
+      <c r="A21" s="410"/>
+      <c r="B21" s="411"/>
+      <c r="C21" s="413"/>
       <c r="D21" s="237" t="s">
         <v>79</v>
       </c>
@@ -18424,9 +18424,9 @@
       <c r="EC21" s="36"/>
     </row>
     <row r="22" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A22" s="415"/>
-      <c r="B22" s="416"/>
-      <c r="C22" s="431"/>
+      <c r="A22" s="410"/>
+      <c r="B22" s="411"/>
+      <c r="C22" s="413"/>
       <c r="D22" s="237" t="s">
         <v>83</v>
       </c>
@@ -18448,9 +18448,9 @@
       </c>
     </row>
     <row r="23" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A23" s="415"/>
-      <c r="B23" s="416"/>
-      <c r="C23" s="431"/>
+      <c r="A23" s="410"/>
+      <c r="B23" s="411"/>
+      <c r="C23" s="413"/>
       <c r="D23" s="73" t="s">
         <v>106</v>
       </c>
@@ -18472,9 +18472,9 @@
       </c>
     </row>
     <row r="24" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A24" s="415"/>
-      <c r="B24" s="416"/>
-      <c r="C24" s="431"/>
+      <c r="A24" s="410"/>
+      <c r="B24" s="411"/>
+      <c r="C24" s="413"/>
       <c r="D24" s="73" t="s">
         <v>92</v>
       </c>
@@ -18496,9 +18496,9 @@
       </c>
     </row>
     <row r="25" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A25" s="423"/>
-      <c r="B25" s="425"/>
-      <c r="C25" s="431"/>
+      <c r="A25" s="403"/>
+      <c r="B25" s="405"/>
+      <c r="C25" s="413"/>
       <c r="D25" s="73" t="s">
         <v>94</v>
       </c>
@@ -18518,13 +18518,13 @@
       </c>
     </row>
     <row r="26" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A26" s="402" t="s">
+      <c r="A26" s="421" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="405" t="s">
+      <c r="B26" s="424" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="408" t="s">
+      <c r="C26" s="430" t="s">
         <v>110</v>
       </c>
       <c r="D26" s="73" t="s">
@@ -18546,9 +18546,9 @@
       </c>
     </row>
     <row r="27" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A27" s="403"/>
-      <c r="B27" s="406"/>
-      <c r="C27" s="409"/>
+      <c r="A27" s="422"/>
+      <c r="B27" s="425"/>
+      <c r="C27" s="431"/>
       <c r="D27" s="73" t="s">
         <v>56</v>
       </c>
@@ -18570,9 +18570,9 @@
       </c>
     </row>
     <row r="28" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A28" s="403"/>
-      <c r="B28" s="406"/>
-      <c r="C28" s="409"/>
+      <c r="A28" s="422"/>
+      <c r="B28" s="425"/>
+      <c r="C28" s="431"/>
       <c r="D28" s="237" t="s">
         <v>61</v>
       </c>
@@ -18594,13 +18594,13 @@
       </c>
     </row>
     <row r="29" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29" s="403"/>
-      <c r="B29" s="406"/>
-      <c r="C29" s="409"/>
-      <c r="D29" s="411" t="s">
+      <c r="A29" s="422"/>
+      <c r="B29" s="425"/>
+      <c r="C29" s="431"/>
+      <c r="D29" s="433" t="s">
         <v>76</v>
       </c>
-      <c r="E29" s="413" t="s">
+      <c r="E29" s="416" t="s">
         <v>77</v>
       </c>
       <c r="F29" s="73" t="s">
@@ -18616,11 +18616,11 @@
       </c>
     </row>
     <row r="30" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="403"/>
-      <c r="B30" s="406"/>
-      <c r="C30" s="409"/>
-      <c r="D30" s="412"/>
-      <c r="E30" s="414"/>
+      <c r="A30" s="422"/>
+      <c r="B30" s="425"/>
+      <c r="C30" s="431"/>
+      <c r="D30" s="434"/>
+      <c r="E30" s="417"/>
       <c r="F30" s="73" t="s">
         <v>113</v>
       </c>
@@ -18636,9 +18636,9 @@
       </c>
     </row>
     <row r="31" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A31" s="403"/>
-      <c r="B31" s="406"/>
-      <c r="C31" s="409"/>
+      <c r="A31" s="422"/>
+      <c r="B31" s="425"/>
+      <c r="C31" s="431"/>
       <c r="D31" s="237" t="s">
         <v>79</v>
       </c>
@@ -18660,9 +18660,9 @@
       </c>
     </row>
     <row r="32" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A32" s="403"/>
-      <c r="B32" s="406"/>
-      <c r="C32" s="409"/>
+      <c r="A32" s="422"/>
+      <c r="B32" s="425"/>
+      <c r="C32" s="431"/>
       <c r="D32" s="237" t="s">
         <v>83</v>
       </c>
@@ -18684,9 +18684,9 @@
       </c>
     </row>
     <row r="33" spans="1:133" s="47" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A33" s="403"/>
-      <c r="B33" s="406"/>
-      <c r="C33" s="409"/>
+      <c r="A33" s="422"/>
+      <c r="B33" s="425"/>
+      <c r="C33" s="431"/>
       <c r="D33" s="264" t="s">
         <v>114</v>
       </c>
@@ -18831,9 +18831,9 @@
       <c r="EC33" s="36"/>
     </row>
     <row r="34" spans="1:133" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A34" s="403"/>
-      <c r="B34" s="406"/>
-      <c r="C34" s="409"/>
+      <c r="A34" s="422"/>
+      <c r="B34" s="425"/>
+      <c r="C34" s="431"/>
       <c r="D34" s="272" t="s">
         <v>92</v>
       </c>
@@ -18978,9 +18978,9 @@
       <c r="EC34" s="36"/>
     </row>
     <row r="35" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A35" s="404"/>
-      <c r="B35" s="407"/>
-      <c r="C35" s="410"/>
+      <c r="A35" s="423"/>
+      <c r="B35" s="426"/>
+      <c r="C35" s="432"/>
       <c r="D35" s="73" t="s">
         <v>94</v>
       </c>
@@ -19000,13 +19000,13 @@
       </c>
     </row>
     <row r="36" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A36" s="402" t="s">
+      <c r="A36" s="421" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="405" t="s">
+      <c r="B36" s="424" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="419" t="s">
+      <c r="C36" s="427" t="s">
         <v>117</v>
       </c>
       <c r="D36" s="37" t="s">
@@ -19030,9 +19030,9 @@
       </c>
     </row>
     <row r="37" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A37" s="403"/>
-      <c r="B37" s="406"/>
-      <c r="C37" s="420"/>
+      <c r="A37" s="422"/>
+      <c r="B37" s="425"/>
+      <c r="C37" s="428"/>
       <c r="D37" s="189" t="s">
         <v>122</v>
       </c>
@@ -19054,9 +19054,9 @@
       </c>
     </row>
     <row r="38" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A38" s="403"/>
-      <c r="B38" s="406"/>
-      <c r="C38" s="420"/>
+      <c r="A38" s="422"/>
+      <c r="B38" s="425"/>
+      <c r="C38" s="428"/>
       <c r="D38" s="37" t="s">
         <v>126</v>
       </c>
@@ -19078,9 +19078,9 @@
       </c>
     </row>
     <row r="39" spans="1:133" ht="84" x14ac:dyDescent="0.2">
-      <c r="A39" s="403"/>
-      <c r="B39" s="406"/>
-      <c r="C39" s="420"/>
+      <c r="A39" s="422"/>
+      <c r="B39" s="425"/>
+      <c r="C39" s="428"/>
       <c r="D39" s="73" t="s">
         <v>130</v>
       </c>
@@ -19102,9 +19102,9 @@
       </c>
     </row>
     <row r="40" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A40" s="403"/>
-      <c r="B40" s="406"/>
-      <c r="C40" s="420"/>
+      <c r="A40" s="422"/>
+      <c r="B40" s="425"/>
+      <c r="C40" s="428"/>
       <c r="D40" s="189" t="s">
         <v>134</v>
       </c>
@@ -19124,9 +19124,9 @@
       </c>
     </row>
     <row r="41" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A41" s="403"/>
-      <c r="B41" s="406"/>
-      <c r="C41" s="420"/>
+      <c r="A41" s="422"/>
+      <c r="B41" s="425"/>
+      <c r="C41" s="428"/>
       <c r="D41" s="237" t="s">
         <v>61</v>
       </c>
@@ -19148,9 +19148,9 @@
       </c>
     </row>
     <row r="42" spans="1:133" ht="72" x14ac:dyDescent="0.2">
-      <c r="A42" s="403"/>
-      <c r="B42" s="406"/>
-      <c r="C42" s="420"/>
+      <c r="A42" s="422"/>
+      <c r="B42" s="425"/>
+      <c r="C42" s="428"/>
       <c r="D42" s="73" t="s">
         <v>76</v>
       </c>
@@ -19172,9 +19172,9 @@
       </c>
     </row>
     <row r="43" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A43" s="403"/>
-      <c r="B43" s="406"/>
-      <c r="C43" s="420"/>
+      <c r="A43" s="422"/>
+      <c r="B43" s="425"/>
+      <c r="C43" s="428"/>
       <c r="D43" s="73" t="s">
         <v>138</v>
       </c>
@@ -19196,9 +19196,9 @@
       </c>
     </row>
     <row r="44" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A44" s="403"/>
-      <c r="B44" s="406"/>
-      <c r="C44" s="420"/>
+      <c r="A44" s="422"/>
+      <c r="B44" s="425"/>
+      <c r="C44" s="428"/>
       <c r="D44" s="332" t="s">
         <v>92</v>
       </c>
@@ -19220,9 +19220,9 @@
       </c>
     </row>
     <row r="45" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A45" s="404"/>
-      <c r="B45" s="407"/>
-      <c r="C45" s="421"/>
+      <c r="A45" s="423"/>
+      <c r="B45" s="426"/>
+      <c r="C45" s="429"/>
       <c r="D45" s="73" t="s">
         <v>94</v>
       </c>
@@ -19258,13 +19258,13 @@
       <c r="J46" s="71"/>
     </row>
     <row r="47" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A47" s="415" t="s">
+      <c r="A47" s="410" t="s">
         <v>141</v>
       </c>
-      <c r="B47" s="416" t="s">
+      <c r="B47" s="411" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="417" t="s">
+      <c r="C47" s="419" t="s">
         <v>142</v>
       </c>
       <c r="D47" s="73" t="s">
@@ -19286,9 +19286,9 @@
       </c>
     </row>
     <row r="48" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A48" s="415"/>
-      <c r="B48" s="416"/>
-      <c r="C48" s="418"/>
+      <c r="A48" s="410"/>
+      <c r="B48" s="411"/>
+      <c r="C48" s="420"/>
       <c r="D48" s="73" t="s">
         <v>56</v>
       </c>
@@ -19308,9 +19308,9 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="24" x14ac:dyDescent="0.2">
-      <c r="A49" s="415"/>
-      <c r="B49" s="416"/>
-      <c r="C49" s="418"/>
+      <c r="A49" s="410"/>
+      <c r="B49" s="411"/>
+      <c r="C49" s="420"/>
       <c r="D49" s="237" t="s">
         <v>61</v>
       </c>
@@ -19330,9 +19330,9 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="117.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="415"/>
-      <c r="B50" s="416"/>
-      <c r="C50" s="418"/>
+      <c r="A50" s="410"/>
+      <c r="B50" s="411"/>
+      <c r="C50" s="420"/>
       <c r="D50" s="73" t="s">
         <v>63</v>
       </c>
@@ -19352,9 +19352,9 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="108" x14ac:dyDescent="0.2">
-      <c r="A51" s="415"/>
-      <c r="B51" s="416"/>
-      <c r="C51" s="418"/>
+      <c r="A51" s="410"/>
+      <c r="B51" s="411"/>
+      <c r="C51" s="420"/>
       <c r="D51" s="73" t="s">
         <v>68</v>
       </c>
@@ -19374,9 +19374,9 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A52" s="415"/>
-      <c r="B52" s="416"/>
-      <c r="C52" s="418"/>
+      <c r="A52" s="410"/>
+      <c r="B52" s="411"/>
+      <c r="C52" s="420"/>
       <c r="D52" s="73" t="s">
         <v>143</v>
       </c>
@@ -19396,9 +19396,9 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A53" s="415"/>
-      <c r="B53" s="416"/>
-      <c r="C53" s="418"/>
+      <c r="A53" s="410"/>
+      <c r="B53" s="411"/>
+      <c r="C53" s="420"/>
       <c r="D53" s="237" t="s">
         <v>76</v>
       </c>
@@ -19418,9 +19418,9 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="75" x14ac:dyDescent="0.2">
-      <c r="A54" s="415"/>
-      <c r="B54" s="416"/>
-      <c r="C54" s="418"/>
+      <c r="A54" s="410"/>
+      <c r="B54" s="411"/>
+      <c r="C54" s="420"/>
       <c r="D54" s="237" t="s">
         <v>79</v>
       </c>
@@ -19442,9 +19442,9 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A55" s="415"/>
-      <c r="B55" s="416"/>
-      <c r="C55" s="418"/>
+      <c r="A55" s="410"/>
+      <c r="B55" s="411"/>
+      <c r="C55" s="420"/>
       <c r="D55" s="237" t="s">
         <v>83</v>
       </c>
@@ -19466,9 +19466,9 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A56" s="415"/>
-      <c r="B56" s="416"/>
-      <c r="C56" s="418"/>
+      <c r="A56" s="410"/>
+      <c r="B56" s="411"/>
+      <c r="C56" s="420"/>
       <c r="D56" s="73" t="s">
         <v>106</v>
       </c>
@@ -19490,9 +19490,9 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A57" s="415"/>
-      <c r="B57" s="416"/>
-      <c r="C57" s="418"/>
+      <c r="A57" s="410"/>
+      <c r="B57" s="411"/>
+      <c r="C57" s="420"/>
       <c r="D57" s="73" t="s">
         <v>92</v>
       </c>
@@ -19514,9 +19514,9 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="45" x14ac:dyDescent="0.2">
-      <c r="A58" s="415"/>
-      <c r="B58" s="416"/>
-      <c r="C58" s="418"/>
+      <c r="A58" s="410"/>
+      <c r="B58" s="411"/>
+      <c r="C58" s="420"/>
       <c r="D58" s="73" t="s">
         <v>94</v>
       </c>
@@ -19538,6 +19538,17 @@
   </sheetData>
   <autoFilter ref="A2:EC43" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="21">
+    <mergeCell ref="A26:A35"/>
+    <mergeCell ref="B26:B35"/>
+    <mergeCell ref="C26:C35"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A47:A58"/>
+    <mergeCell ref="B47:B58"/>
+    <mergeCell ref="C47:C58"/>
+    <mergeCell ref="A36:A45"/>
+    <mergeCell ref="B36:B45"/>
+    <mergeCell ref="C36:C45"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="A4:A15"/>
     <mergeCell ref="B4:B15"/>
@@ -19548,17 +19559,6 @@
     <mergeCell ref="D19:D20"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A47:A58"/>
-    <mergeCell ref="B47:B58"/>
-    <mergeCell ref="C47:C58"/>
-    <mergeCell ref="A36:A45"/>
-    <mergeCell ref="B36:B45"/>
-    <mergeCell ref="C36:C45"/>
-    <mergeCell ref="A26:A35"/>
-    <mergeCell ref="B26:B35"/>
-    <mergeCell ref="C26:C35"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -20018,32 +20018,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:138" s="31" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="527"/>
-      <c r="B1" s="527"/>
-      <c r="C1" s="527"/>
-      <c r="D1" s="527"/>
-      <c r="E1" s="527"/>
-      <c r="F1" s="527"/>
-      <c r="G1" s="527"/>
+      <c r="A1" s="528"/>
+      <c r="B1" s="528"/>
+      <c r="C1" s="528"/>
+      <c r="D1" s="528"/>
+      <c r="E1" s="528"/>
+      <c r="F1" s="528"/>
+      <c r="G1" s="528"/>
       <c r="H1" s="104"/>
       <c r="I1" s="101"/>
       <c r="J1" s="102"/>
     </row>
     <row r="2" spans="1:138" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="528" t="s">
+      <c r="A2" s="529" t="s">
         <v>398</v>
       </c>
-      <c r="B2" s="528"/>
-      <c r="C2" s="528"/>
-      <c r="D2" s="528"/>
-      <c r="E2" s="528"/>
-      <c r="F2" s="528"/>
-      <c r="G2" s="528"/>
+      <c r="B2" s="529"/>
+      <c r="C2" s="529"/>
+      <c r="D2" s="529"/>
+      <c r="E2" s="529"/>
+      <c r="F2" s="529"/>
+      <c r="G2" s="529"/>
       <c r="H2" s="105"/>
-      <c r="I2" s="422" t="s">
+      <c r="I2" s="402" t="s">
         <v>381</v>
       </c>
-      <c r="J2" s="422"/>
+      <c r="J2" s="402"/>
     </row>
     <row r="3" spans="1:138" s="31" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="64"/>
@@ -20087,13 +20087,13 @@
       </c>
     </row>
     <row r="5" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="490">
+      <c r="A5" s="476">
         <v>1</v>
       </c>
-      <c r="B5" s="425" t="s">
+      <c r="B5" s="405" t="s">
         <v>399</v>
       </c>
-      <c r="C5" s="430" t="s">
+      <c r="C5" s="412" t="s">
         <v>400</v>
       </c>
       <c r="D5" s="73" t="s">
@@ -20115,9 +20115,9 @@
       </c>
     </row>
     <row r="6" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="491"/>
-      <c r="B6" s="426"/>
-      <c r="C6" s="431"/>
+      <c r="A6" s="477"/>
+      <c r="B6" s="406"/>
+      <c r="C6" s="413"/>
       <c r="D6" s="73" t="s">
         <v>56</v>
       </c>
@@ -20137,9 +20137,9 @@
       </c>
     </row>
     <row r="7" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="491"/>
-      <c r="B7" s="426"/>
-      <c r="C7" s="431"/>
+      <c r="A7" s="477"/>
+      <c r="B7" s="406"/>
+      <c r="C7" s="413"/>
       <c r="D7" s="73" t="s">
         <v>55</v>
       </c>
@@ -20159,9 +20159,9 @@
       </c>
     </row>
     <row r="8" spans="1:138" ht="210" x14ac:dyDescent="0.2">
-      <c r="A8" s="491"/>
-      <c r="B8" s="426"/>
-      <c r="C8" s="431"/>
+      <c r="A8" s="477"/>
+      <c r="B8" s="406"/>
+      <c r="C8" s="413"/>
       <c r="D8" s="73" t="s">
         <v>63</v>
       </c>
@@ -20182,9 +20182,9 @@
       <c r="K8" s="38"/>
     </row>
     <row r="9" spans="1:138" ht="150" x14ac:dyDescent="0.2">
-      <c r="A9" s="491"/>
-      <c r="B9" s="426"/>
-      <c r="C9" s="431"/>
+      <c r="A9" s="477"/>
+      <c r="B9" s="406"/>
+      <c r="C9" s="413"/>
       <c r="D9" s="73" t="s">
         <v>68</v>
       </c>
@@ -20204,9 +20204,9 @@
       </c>
     </row>
     <row r="10" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A10" s="491"/>
-      <c r="B10" s="426"/>
-      <c r="C10" s="431"/>
+      <c r="A10" s="477"/>
+      <c r="B10" s="406"/>
+      <c r="C10" s="413"/>
       <c r="D10" s="73" t="s">
         <v>72</v>
       </c>
@@ -20226,9 +20226,9 @@
       </c>
     </row>
     <row r="11" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="491"/>
-      <c r="B11" s="426"/>
-      <c r="C11" s="431"/>
+      <c r="A11" s="477"/>
+      <c r="B11" s="406"/>
+      <c r="C11" s="413"/>
       <c r="D11" s="73" t="s">
         <v>86</v>
       </c>
@@ -20250,9 +20250,9 @@
       </c>
     </row>
     <row r="12" spans="1:138" s="42" customFormat="1" ht="347.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="491"/>
-      <c r="B12" s="426"/>
-      <c r="C12" s="431"/>
+      <c r="A12" s="477"/>
+      <c r="B12" s="406"/>
+      <c r="C12" s="413"/>
       <c r="D12" s="73" t="s">
         <v>92</v>
       </c>
@@ -20402,9 +20402,9 @@
       <c r="EH12" s="41"/>
     </row>
     <row r="13" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="491"/>
-      <c r="B13" s="426"/>
-      <c r="C13" s="431"/>
+      <c r="A13" s="477"/>
+      <c r="B13" s="406"/>
+      <c r="C13" s="413"/>
       <c r="D13" s="73" t="s">
         <v>282</v>
       </c>
@@ -20424,13 +20424,13 @@
       </c>
     </row>
     <row r="14" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="495">
+      <c r="A14" s="481">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="496" t="s">
+      <c r="B14" s="482" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="430" t="s">
+      <c r="C14" s="412" t="s">
         <v>401</v>
       </c>
       <c r="D14" s="73" t="s">
@@ -20452,9 +20452,9 @@
       </c>
     </row>
     <row r="15" spans="1:138" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="495"/>
-      <c r="B15" s="496"/>
-      <c r="C15" s="529"/>
+      <c r="A15" s="481"/>
+      <c r="B15" s="482"/>
+      <c r="C15" s="527"/>
       <c r="D15" s="73" t="s">
         <v>56</v>
       </c>
@@ -20476,9 +20476,9 @@
       </c>
     </row>
     <row r="16" spans="1:138" ht="140.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="495"/>
-      <c r="B16" s="496"/>
-      <c r="C16" s="529"/>
+      <c r="A16" s="481"/>
+      <c r="B16" s="482"/>
+      <c r="C16" s="527"/>
       <c r="D16" s="73" t="s">
         <v>55</v>
       </c>
@@ -20501,9 +20501,9 @@
       <c r="K16" s="38"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="495"/>
-      <c r="B17" s="496"/>
-      <c r="C17" s="529"/>
+      <c r="A17" s="481"/>
+      <c r="B17" s="482"/>
+      <c r="C17" s="527"/>
       <c r="D17" s="76" t="s">
         <v>106</v>
       </c>
@@ -20653,9 +20653,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" s="47" customFormat="1" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="495"/>
-      <c r="B18" s="496"/>
-      <c r="C18" s="529"/>
+      <c r="A18" s="481"/>
+      <c r="B18" s="482"/>
+      <c r="C18" s="527"/>
       <c r="D18" s="76" t="s">
         <v>92</v>
       </c>
@@ -20805,9 +20805,9 @@
       <c r="EH18" s="36"/>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="490"/>
-      <c r="B19" s="497"/>
-      <c r="C19" s="529"/>
+      <c r="A19" s="476"/>
+      <c r="B19" s="483"/>
+      <c r="C19" s="527"/>
       <c r="D19" s="78" t="s">
         <v>282</v>
       </c>
@@ -20827,13 +20827,13 @@
       </c>
     </row>
     <row r="20" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="476">
+      <c r="A20" s="484">
         <v>2</v>
       </c>
-      <c r="B20" s="477" t="s">
+      <c r="B20" s="485" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="470" t="s">
+      <c r="C20" s="469" t="s">
         <v>384</v>
       </c>
       <c r="D20" s="73" t="s">
@@ -20855,8 +20855,8 @@
       </c>
     </row>
     <row r="21" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="476"/>
-      <c r="B21" s="477"/>
+      <c r="A21" s="484"/>
+      <c r="B21" s="485"/>
       <c r="C21" s="519"/>
       <c r="D21" s="73" t="s">
         <v>56</v>
@@ -20879,8 +20879,8 @@
       </c>
     </row>
     <row r="22" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A22" s="476"/>
-      <c r="B22" s="477"/>
+      <c r="A22" s="484"/>
+      <c r="B22" s="485"/>
       <c r="C22" s="519"/>
       <c r="D22" s="73" t="s">
         <v>55</v>
@@ -20903,8 +20903,8 @@
       </c>
     </row>
     <row r="23" spans="1:138" s="47" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A23" s="476"/>
-      <c r="B23" s="477"/>
+      <c r="A23" s="484"/>
+      <c r="B23" s="485"/>
       <c r="C23" s="519"/>
       <c r="D23" s="61" t="s">
         <v>114</v>
@@ -21055,8 +21055,8 @@
       <c r="EH23" s="36"/>
     </row>
     <row r="24" spans="1:138" s="47" customFormat="1" ht="60" x14ac:dyDescent="0.2">
-      <c r="A24" s="476"/>
-      <c r="B24" s="477"/>
+      <c r="A24" s="484"/>
+      <c r="B24" s="485"/>
       <c r="C24" s="519"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
@@ -21207,8 +21207,8 @@
       <c r="EH24" s="36"/>
     </row>
     <row r="25" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="476"/>
-      <c r="B25" s="477"/>
+      <c r="A25" s="484"/>
+      <c r="B25" s="485"/>
       <c r="C25" s="520"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
@@ -21229,13 +21229,13 @@
       </c>
     </row>
     <row r="26" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A26" s="481">
+      <c r="A26" s="489">
         <v>2.1</v>
       </c>
-      <c r="B26" s="484" t="s">
+      <c r="B26" s="492" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="487" t="s">
+      <c r="C26" s="495" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="83" t="s">
@@ -21257,9 +21257,9 @@
       </c>
     </row>
     <row r="27" spans="1:138" ht="105" x14ac:dyDescent="0.2">
-      <c r="A27" s="482"/>
-      <c r="B27" s="485"/>
-      <c r="C27" s="488"/>
+      <c r="A27" s="490"/>
+      <c r="B27" s="493"/>
+      <c r="C27" s="496"/>
       <c r="D27" s="83" t="s">
         <v>130</v>
       </c>
@@ -21279,9 +21279,9 @@
       </c>
     </row>
     <row r="28" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A28" s="482"/>
-      <c r="B28" s="485"/>
-      <c r="C28" s="488"/>
+      <c r="A28" s="490"/>
+      <c r="B28" s="493"/>
+      <c r="C28" s="496"/>
       <c r="D28" s="73" t="s">
         <v>55</v>
       </c>
@@ -21303,9 +21303,9 @@
       </c>
     </row>
     <row r="29" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A29" s="482"/>
-      <c r="B29" s="485"/>
-      <c r="C29" s="488"/>
+      <c r="A29" s="490"/>
+      <c r="B29" s="493"/>
+      <c r="C29" s="496"/>
       <c r="D29" s="61" t="s">
         <v>114</v>
       </c>
@@ -21327,9 +21327,9 @@
       </c>
     </row>
     <row r="30" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="482"/>
-      <c r="B30" s="485"/>
-      <c r="C30" s="488"/>
+      <c r="A30" s="490"/>
+      <c r="B30" s="493"/>
+      <c r="C30" s="496"/>
       <c r="D30" s="86" t="s">
         <v>92</v>
       </c>
@@ -21351,9 +21351,9 @@
       </c>
     </row>
     <row r="31" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A31" s="483"/>
-      <c r="B31" s="486"/>
-      <c r="C31" s="489"/>
+      <c r="A31" s="491"/>
+      <c r="B31" s="494"/>
+      <c r="C31" s="497"/>
       <c r="D31" s="76" t="s">
         <v>94</v>
       </c>
@@ -21495,24 +21495,24 @@
   </sheetData>
   <autoFilter ref="A4:EH32" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="18">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="B5:B13"/>
+    <mergeCell ref="C5:C13"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="C14:C19"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="B20:B25"/>
+    <mergeCell ref="C20:C25"/>
     <mergeCell ref="A26:A31"/>
     <mergeCell ref="B26:B31"/>
     <mergeCell ref="C26:C31"/>
     <mergeCell ref="A32:A36"/>
     <mergeCell ref="B32:B36"/>
     <mergeCell ref="C32:C36"/>
-    <mergeCell ref="A14:A19"/>
-    <mergeCell ref="B14:B19"/>
-    <mergeCell ref="C14:C19"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="B20:B25"/>
-    <mergeCell ref="C20:C25"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="B5:B13"/>
-    <mergeCell ref="C5:C13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -21540,33 +21540,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:139" s="31" customFormat="1" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="527"/>
-      <c r="B1" s="527"/>
-      <c r="C1" s="527"/>
-      <c r="D1" s="527"/>
-      <c r="E1" s="527"/>
-      <c r="F1" s="527"/>
-      <c r="G1" s="527"/>
+      <c r="A1" s="528"/>
+      <c r="B1" s="528"/>
+      <c r="C1" s="528"/>
+      <c r="D1" s="528"/>
+      <c r="E1" s="528"/>
+      <c r="F1" s="528"/>
+      <c r="G1" s="528"/>
       <c r="H1" s="104"/>
       <c r="I1" s="101"/>
       <c r="J1" s="102"/>
       <c r="K1" s="102"/>
     </row>
     <row r="2" spans="1:139" s="31" customFormat="1" ht="25" x14ac:dyDescent="0.2">
-      <c r="A2" s="528" t="s">
+      <c r="A2" s="529" t="s">
         <v>380</v>
       </c>
-      <c r="B2" s="528"/>
-      <c r="C2" s="528"/>
-      <c r="D2" s="528"/>
-      <c r="E2" s="528"/>
-      <c r="F2" s="528"/>
-      <c r="G2" s="528"/>
+      <c r="B2" s="529"/>
+      <c r="C2" s="529"/>
+      <c r="D2" s="529"/>
+      <c r="E2" s="529"/>
+      <c r="F2" s="529"/>
+      <c r="G2" s="529"/>
       <c r="H2" s="105"/>
-      <c r="I2" s="422" t="s">
+      <c r="I2" s="402" t="s">
         <v>381</v>
       </c>
-      <c r="J2" s="422"/>
+      <c r="J2" s="402"/>
       <c r="K2" s="103"/>
     </row>
     <row r="3" spans="1:139" s="31" customFormat="1" ht="20" x14ac:dyDescent="0.2">
@@ -21615,10 +21615,10 @@
       </c>
     </row>
     <row r="5" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A5" s="490">
+      <c r="A5" s="476">
         <v>1</v>
       </c>
-      <c r="B5" s="425" t="s">
+      <c r="B5" s="405" t="s">
         <v>399</v>
       </c>
       <c r="C5" s="509" t="s">
@@ -21646,9 +21646,9 @@
       </c>
     </row>
     <row r="6" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A6" s="491"/>
-      <c r="B6" s="426"/>
-      <c r="C6" s="473"/>
+      <c r="A6" s="477"/>
+      <c r="B6" s="406"/>
+      <c r="C6" s="472"/>
       <c r="D6" s="73" t="s">
         <v>56</v>
       </c>
@@ -21669,9 +21669,9 @@
       <c r="K6" s="35"/>
     </row>
     <row r="7" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="491"/>
-      <c r="B7" s="426"/>
-      <c r="C7" s="473"/>
+      <c r="A7" s="477"/>
+      <c r="B7" s="406"/>
+      <c r="C7" s="472"/>
       <c r="D7" s="73" t="s">
         <v>55</v>
       </c>
@@ -21692,9 +21692,9 @@
       <c r="K7" s="35"/>
     </row>
     <row r="8" spans="1:139" ht="210" x14ac:dyDescent="0.2">
-      <c r="A8" s="491"/>
-      <c r="B8" s="426"/>
-      <c r="C8" s="473"/>
+      <c r="A8" s="477"/>
+      <c r="B8" s="406"/>
+      <c r="C8" s="472"/>
       <c r="D8" s="73" t="s">
         <v>63</v>
       </c>
@@ -21716,9 +21716,9 @@
       <c r="L8" s="38"/>
     </row>
     <row r="9" spans="1:139" ht="150" x14ac:dyDescent="0.2">
-      <c r="A9" s="491"/>
-      <c r="B9" s="426"/>
-      <c r="C9" s="473"/>
+      <c r="A9" s="477"/>
+      <c r="B9" s="406"/>
+      <c r="C9" s="472"/>
       <c r="D9" s="73" t="s">
         <v>68</v>
       </c>
@@ -21739,9 +21739,9 @@
       <c r="K9" s="35"/>
     </row>
     <row r="10" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A10" s="491"/>
-      <c r="B10" s="426"/>
-      <c r="C10" s="473"/>
+      <c r="A10" s="477"/>
+      <c r="B10" s="406"/>
+      <c r="C10" s="472"/>
       <c r="D10" s="73" t="s">
         <v>72</v>
       </c>
@@ -21762,9 +21762,9 @@
       <c r="K10" s="35"/>
     </row>
     <row r="11" spans="1:139" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="491"/>
-      <c r="B11" s="426"/>
-      <c r="C11" s="473"/>
+      <c r="A11" s="477"/>
+      <c r="B11" s="406"/>
+      <c r="C11" s="472"/>
       <c r="D11" s="73" t="s">
         <v>86</v>
       </c>
@@ -21801,9 +21801,9 @@
       </c>
     </row>
     <row r="12" spans="1:139" s="42" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A12" s="491"/>
-      <c r="B12" s="426"/>
-      <c r="C12" s="473"/>
+      <c r="A12" s="477"/>
+      <c r="B12" s="406"/>
+      <c r="C12" s="472"/>
       <c r="D12" s="73" t="s">
         <v>92</v>
       </c>
@@ -21968,9 +21968,9 @@
       <c r="EI12" s="41"/>
     </row>
     <row r="13" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="491"/>
-      <c r="B13" s="426"/>
-      <c r="C13" s="473"/>
+      <c r="A13" s="477"/>
+      <c r="B13" s="406"/>
+      <c r="C13" s="472"/>
       <c r="D13" s="73" t="s">
         <v>282</v>
       </c>
@@ -21993,10 +21993,10 @@
       </c>
     </row>
     <row r="14" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="495">
+      <c r="A14" s="481">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="496" t="s">
+      <c r="B14" s="482" t="s">
         <v>98</v>
       </c>
       <c r="C14" s="509" t="s">
@@ -22024,8 +22024,8 @@
       </c>
     </row>
     <row r="15" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A15" s="495"/>
-      <c r="B15" s="496"/>
+      <c r="A15" s="481"/>
+      <c r="B15" s="482"/>
       <c r="C15" s="530"/>
       <c r="D15" s="73" t="s">
         <v>56</v>
@@ -22049,8 +22049,8 @@
       <c r="K15" s="35"/>
     </row>
     <row r="16" spans="1:139" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A16" s="495"/>
-      <c r="B16" s="496"/>
+      <c r="A16" s="481"/>
+      <c r="B16" s="482"/>
       <c r="C16" s="530"/>
       <c r="D16" s="73" t="s">
         <v>55</v>
@@ -22089,8 +22089,8 @@
       <c r="L16" s="38"/>
     </row>
     <row r="17" spans="1:139" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A17" s="495"/>
-      <c r="B17" s="496"/>
+      <c r="A17" s="481"/>
+      <c r="B17" s="482"/>
       <c r="C17" s="530"/>
       <c r="D17" s="76" t="s">
         <v>106</v>
@@ -22256,8 +22256,8 @@
       <c r="EI17" s="36"/>
     </row>
     <row r="18" spans="1:139" s="47" customFormat="1" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A18" s="495"/>
-      <c r="B18" s="496"/>
+      <c r="A18" s="481"/>
+      <c r="B18" s="482"/>
       <c r="C18" s="530"/>
       <c r="D18" s="76" t="s">
         <v>92</v>
@@ -22421,8 +22421,8 @@
       <c r="EI18" s="36"/>
     </row>
     <row r="19" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="490"/>
-      <c r="B19" s="497"/>
+      <c r="A19" s="476"/>
+      <c r="B19" s="483"/>
       <c r="C19" s="530"/>
       <c r="D19" s="78" t="s">
         <v>282</v>
@@ -22446,13 +22446,13 @@
       </c>
     </row>
     <row r="20" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="476">
+      <c r="A20" s="484">
         <v>2</v>
       </c>
-      <c r="B20" s="477" t="s">
+      <c r="B20" s="485" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="470" t="s">
+      <c r="C20" s="469" t="s">
         <v>408</v>
       </c>
       <c r="D20" s="73" t="s">
@@ -22475,8 +22475,8 @@
       <c r="K20" s="54"/>
     </row>
     <row r="21" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="476"/>
-      <c r="B21" s="477"/>
+      <c r="A21" s="484"/>
+      <c r="B21" s="485"/>
       <c r="C21" s="519"/>
       <c r="D21" s="73" t="s">
         <v>56</v>
@@ -22500,8 +22500,8 @@
       <c r="K21" s="54"/>
     </row>
     <row r="22" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A22" s="476"/>
-      <c r="B22" s="477"/>
+      <c r="A22" s="484"/>
+      <c r="B22" s="485"/>
       <c r="C22" s="519"/>
       <c r="D22" s="73" t="s">
         <v>55</v>
@@ -22527,8 +22527,8 @@
       </c>
     </row>
     <row r="23" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A23" s="476"/>
-      <c r="B23" s="477"/>
+      <c r="A23" s="484"/>
+      <c r="B23" s="485"/>
       <c r="C23" s="519"/>
       <c r="D23" s="61" t="s">
         <v>114</v>
@@ -22682,8 +22682,8 @@
       <c r="EI23" s="36"/>
     </row>
     <row r="24" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A24" s="476"/>
-      <c r="B24" s="477"/>
+      <c r="A24" s="484"/>
+      <c r="B24" s="485"/>
       <c r="C24" s="519"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
@@ -22837,8 +22837,8 @@
       <c r="EI24" s="36"/>
     </row>
     <row r="25" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="476"/>
-      <c r="B25" s="477"/>
+      <c r="A25" s="484"/>
+      <c r="B25" s="485"/>
       <c r="C25" s="520"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
@@ -22862,13 +22862,13 @@
       </c>
     </row>
     <row r="26" spans="1:139" ht="90" x14ac:dyDescent="0.2">
-      <c r="A26" s="481">
+      <c r="A26" s="489">
         <v>2.1</v>
       </c>
-      <c r="B26" s="484" t="s">
+      <c r="B26" s="492" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="487" t="s">
+      <c r="C26" s="495" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="76" t="s">
@@ -22891,9 +22891,9 @@
       <c r="K26" s="35"/>
     </row>
     <row r="27" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A27" s="482"/>
-      <c r="B27" s="485"/>
-      <c r="C27" s="488"/>
+      <c r="A27" s="490"/>
+      <c r="B27" s="493"/>
+      <c r="C27" s="496"/>
       <c r="D27" s="73" t="s">
         <v>55</v>
       </c>
@@ -22916,9 +22916,9 @@
       <c r="K27" s="35"/>
     </row>
     <row r="28" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A28" s="482"/>
-      <c r="B28" s="485"/>
-      <c r="C28" s="488"/>
+      <c r="A28" s="490"/>
+      <c r="B28" s="493"/>
+      <c r="C28" s="496"/>
       <c r="D28" s="61" t="s">
         <v>114</v>
       </c>
@@ -22941,9 +22941,9 @@
       <c r="K28" s="35"/>
     </row>
     <row r="29" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A29" s="482"/>
-      <c r="B29" s="485"/>
-      <c r="C29" s="488"/>
+      <c r="A29" s="490"/>
+      <c r="B29" s="493"/>
+      <c r="C29" s="496"/>
       <c r="D29" s="86" t="s">
         <v>92</v>
       </c>
@@ -22966,9 +22966,9 @@
       <c r="K29" s="35"/>
     </row>
     <row r="30" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="483"/>
-      <c r="B30" s="486"/>
-      <c r="C30" s="489"/>
+      <c r="A30" s="491"/>
+      <c r="B30" s="494"/>
+      <c r="C30" s="497"/>
       <c r="D30" s="76" t="s">
         <v>94</v>
       </c>
@@ -24181,6 +24181,12 @@
   </sheetData>
   <autoFilter ref="A4:EI31" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="15">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="B5:B13"/>
+    <mergeCell ref="C5:C13"/>
     <mergeCell ref="A26:A30"/>
     <mergeCell ref="B26:B30"/>
     <mergeCell ref="C26:C30"/>
@@ -24190,12 +24196,6 @@
     <mergeCell ref="A20:A25"/>
     <mergeCell ref="B20:B25"/>
     <mergeCell ref="C20:C25"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="B5:B13"/>
-    <mergeCell ref="C5:C13"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K6:K7 K26" xr:uid="{71B7DFEE-6548-4738-BBF7-B2A60C74FD01}"/>
@@ -24805,33 +24805,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:139" s="31" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="527"/>
-      <c r="B1" s="527"/>
-      <c r="C1" s="527"/>
-      <c r="D1" s="527"/>
-      <c r="E1" s="527"/>
-      <c r="F1" s="527"/>
-      <c r="G1" s="527"/>
+      <c r="A1" s="528"/>
+      <c r="B1" s="528"/>
+      <c r="C1" s="528"/>
+      <c r="D1" s="528"/>
+      <c r="E1" s="528"/>
+      <c r="F1" s="528"/>
+      <c r="G1" s="528"/>
       <c r="H1" s="104"/>
       <c r="I1" s="101"/>
       <c r="J1" s="102"/>
       <c r="K1" s="102"/>
     </row>
     <row r="2" spans="1:139" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="528" t="s">
+      <c r="A2" s="529" t="s">
         <v>398</v>
       </c>
-      <c r="B2" s="528"/>
-      <c r="C2" s="528"/>
-      <c r="D2" s="528"/>
-      <c r="E2" s="528"/>
-      <c r="F2" s="528"/>
-      <c r="G2" s="528"/>
+      <c r="B2" s="529"/>
+      <c r="C2" s="529"/>
+      <c r="D2" s="529"/>
+      <c r="E2" s="529"/>
+      <c r="F2" s="529"/>
+      <c r="G2" s="529"/>
       <c r="H2" s="105"/>
-      <c r="I2" s="422" t="s">
+      <c r="I2" s="402" t="s">
         <v>381</v>
       </c>
-      <c r="J2" s="422"/>
+      <c r="J2" s="402"/>
       <c r="K2" s="103"/>
     </row>
     <row r="3" spans="1:139" s="31" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -24880,13 +24880,13 @@
       </c>
     </row>
     <row r="5" spans="1:139" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="490">
+      <c r="A5" s="476">
         <v>1</v>
       </c>
-      <c r="B5" s="425" t="s">
+      <c r="B5" s="405" t="s">
         <v>399</v>
       </c>
-      <c r="C5" s="430" t="s">
+      <c r="C5" s="412" t="s">
         <v>400</v>
       </c>
       <c r="D5" s="73" t="s">
@@ -24911,9 +24911,9 @@
       </c>
     </row>
     <row r="6" spans="1:139" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="491"/>
-      <c r="B6" s="426"/>
-      <c r="C6" s="431"/>
+      <c r="A6" s="477"/>
+      <c r="B6" s="406"/>
+      <c r="C6" s="413"/>
       <c r="D6" s="73" t="s">
         <v>56</v>
       </c>
@@ -24934,9 +24934,9 @@
       <c r="K6" s="35"/>
     </row>
     <row r="7" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="491"/>
-      <c r="B7" s="426"/>
-      <c r="C7" s="431"/>
+      <c r="A7" s="477"/>
+      <c r="B7" s="406"/>
+      <c r="C7" s="413"/>
       <c r="D7" s="73" t="s">
         <v>55</v>
       </c>
@@ -24957,9 +24957,9 @@
       <c r="K7" s="35"/>
     </row>
     <row r="8" spans="1:139" ht="210" x14ac:dyDescent="0.2">
-      <c r="A8" s="491"/>
-      <c r="B8" s="426"/>
-      <c r="C8" s="431"/>
+      <c r="A8" s="477"/>
+      <c r="B8" s="406"/>
+      <c r="C8" s="413"/>
       <c r="D8" s="73" t="s">
         <v>63</v>
       </c>
@@ -24981,9 +24981,9 @@
       <c r="L8" s="38"/>
     </row>
     <row r="9" spans="1:139" ht="150" x14ac:dyDescent="0.2">
-      <c r="A9" s="491"/>
-      <c r="B9" s="426"/>
-      <c r="C9" s="431"/>
+      <c r="A9" s="477"/>
+      <c r="B9" s="406"/>
+      <c r="C9" s="413"/>
       <c r="D9" s="73" t="s">
         <v>68</v>
       </c>
@@ -25004,9 +25004,9 @@
       <c r="K9" s="35"/>
     </row>
     <row r="10" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A10" s="491"/>
-      <c r="B10" s="426"/>
-      <c r="C10" s="431"/>
+      <c r="A10" s="477"/>
+      <c r="B10" s="406"/>
+      <c r="C10" s="413"/>
       <c r="D10" s="73" t="s">
         <v>72</v>
       </c>
@@ -25027,9 +25027,9 @@
       <c r="K10" s="35"/>
     </row>
     <row r="11" spans="1:139" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="491"/>
-      <c r="B11" s="426"/>
-      <c r="C11" s="431"/>
+      <c r="A11" s="477"/>
+      <c r="B11" s="406"/>
+      <c r="C11" s="413"/>
       <c r="D11" s="73" t="s">
         <v>86</v>
       </c>
@@ -25054,9 +25054,9 @@
       </c>
     </row>
     <row r="12" spans="1:139" s="42" customFormat="1" ht="347.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="491"/>
-      <c r="B12" s="426"/>
-      <c r="C12" s="431"/>
+      <c r="A12" s="477"/>
+      <c r="B12" s="406"/>
+      <c r="C12" s="413"/>
       <c r="D12" s="73" t="s">
         <v>92</v>
       </c>
@@ -25209,9 +25209,9 @@
       <c r="EI12" s="41"/>
     </row>
     <row r="13" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="491"/>
-      <c r="B13" s="426"/>
-      <c r="C13" s="431"/>
+      <c r="A13" s="477"/>
+      <c r="B13" s="406"/>
+      <c r="C13" s="413"/>
       <c r="D13" s="73" t="s">
         <v>282</v>
       </c>
@@ -25234,13 +25234,13 @@
       </c>
     </row>
     <row r="14" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="495">
+      <c r="A14" s="481">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="496" t="s">
+      <c r="B14" s="482" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="430" t="s">
+      <c r="C14" s="412" t="s">
         <v>401</v>
       </c>
       <c r="D14" s="73" t="s">
@@ -25265,9 +25265,9 @@
       </c>
     </row>
     <row r="15" spans="1:139" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="495"/>
-      <c r="B15" s="496"/>
-      <c r="C15" s="529"/>
+      <c r="A15" s="481"/>
+      <c r="B15" s="482"/>
+      <c r="C15" s="527"/>
       <c r="D15" s="73" t="s">
         <v>56</v>
       </c>
@@ -25290,9 +25290,9 @@
       <c r="K15" s="35"/>
     </row>
     <row r="16" spans="1:139" ht="140.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="495"/>
-      <c r="B16" s="496"/>
-      <c r="C16" s="529"/>
+      <c r="A16" s="481"/>
+      <c r="B16" s="482"/>
+      <c r="C16" s="527"/>
       <c r="D16" s="73" t="s">
         <v>55</v>
       </c>
@@ -25318,9 +25318,9 @@
       <c r="L16" s="38"/>
     </row>
     <row r="17" spans="1:139" s="47" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="495"/>
-      <c r="B17" s="496"/>
-      <c r="C17" s="529"/>
+      <c r="A17" s="481"/>
+      <c r="B17" s="482"/>
+      <c r="C17" s="527"/>
       <c r="D17" s="76" t="s">
         <v>106</v>
       </c>
@@ -25473,9 +25473,9 @@
       <c r="EI17" s="36"/>
     </row>
     <row r="18" spans="1:139" s="47" customFormat="1" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="495"/>
-      <c r="B18" s="496"/>
-      <c r="C18" s="529"/>
+      <c r="A18" s="481"/>
+      <c r="B18" s="482"/>
+      <c r="C18" s="527"/>
       <c r="D18" s="76" t="s">
         <v>92</v>
       </c>
@@ -25626,9 +25626,9 @@
       <c r="EI18" s="36"/>
     </row>
     <row r="19" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="490"/>
-      <c r="B19" s="497"/>
-      <c r="C19" s="529"/>
+      <c r="A19" s="476"/>
+      <c r="B19" s="483"/>
+      <c r="C19" s="527"/>
       <c r="D19" s="78" t="s">
         <v>282</v>
       </c>
@@ -25651,13 +25651,13 @@
       </c>
     </row>
     <row r="20" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="476">
+      <c r="A20" s="484">
         <v>2</v>
       </c>
-      <c r="B20" s="477" t="s">
+      <c r="B20" s="485" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="470" t="s">
+      <c r="C20" s="469" t="s">
         <v>408</v>
       </c>
       <c r="D20" s="73" t="s">
@@ -25680,8 +25680,8 @@
       <c r="K20" s="54"/>
     </row>
     <row r="21" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="476"/>
-      <c r="B21" s="477"/>
+      <c r="A21" s="484"/>
+      <c r="B21" s="485"/>
       <c r="C21" s="519"/>
       <c r="D21" s="73" t="s">
         <v>56</v>
@@ -25705,8 +25705,8 @@
       <c r="K21" s="54"/>
     </row>
     <row r="22" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A22" s="476"/>
-      <c r="B22" s="477"/>
+      <c r="A22" s="484"/>
+      <c r="B22" s="485"/>
       <c r="C22" s="519"/>
       <c r="D22" s="73" t="s">
         <v>55</v>
@@ -25732,8 +25732,8 @@
       </c>
     </row>
     <row r="23" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A23" s="476"/>
-      <c r="B23" s="477"/>
+      <c r="A23" s="484"/>
+      <c r="B23" s="485"/>
       <c r="C23" s="519"/>
       <c r="D23" s="61" t="s">
         <v>114</v>
@@ -25887,8 +25887,8 @@
       <c r="EI23" s="36"/>
     </row>
     <row r="24" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A24" s="476"/>
-      <c r="B24" s="477"/>
+      <c r="A24" s="484"/>
+      <c r="B24" s="485"/>
       <c r="C24" s="519"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
@@ -26042,8 +26042,8 @@
       <c r="EI24" s="36"/>
     </row>
     <row r="25" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="476"/>
-      <c r="B25" s="477"/>
+      <c r="A25" s="484"/>
+      <c r="B25" s="485"/>
       <c r="C25" s="520"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
@@ -26067,13 +26067,13 @@
       </c>
     </row>
     <row r="26" spans="1:139" ht="90" x14ac:dyDescent="0.2">
-      <c r="A26" s="481">
+      <c r="A26" s="489">
         <v>2.1</v>
       </c>
-      <c r="B26" s="484" t="s">
+      <c r="B26" s="492" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="487" t="s">
+      <c r="C26" s="495" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="76" t="s">
@@ -26096,9 +26096,9 @@
       <c r="K26" s="35"/>
     </row>
     <row r="27" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A27" s="482"/>
-      <c r="B27" s="485"/>
-      <c r="C27" s="488"/>
+      <c r="A27" s="490"/>
+      <c r="B27" s="493"/>
+      <c r="C27" s="496"/>
       <c r="D27" s="73" t="s">
         <v>55</v>
       </c>
@@ -26121,9 +26121,9 @@
       <c r="K27" s="35"/>
     </row>
     <row r="28" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A28" s="482"/>
-      <c r="B28" s="485"/>
-      <c r="C28" s="488"/>
+      <c r="A28" s="490"/>
+      <c r="B28" s="493"/>
+      <c r="C28" s="496"/>
       <c r="D28" s="61" t="s">
         <v>114</v>
       </c>
@@ -26146,9 +26146,9 @@
       <c r="K28" s="35"/>
     </row>
     <row r="29" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A29" s="482"/>
-      <c r="B29" s="485"/>
-      <c r="C29" s="488"/>
+      <c r="A29" s="490"/>
+      <c r="B29" s="493"/>
+      <c r="C29" s="496"/>
       <c r="D29" s="86" t="s">
         <v>92</v>
       </c>
@@ -26171,9 +26171,9 @@
       <c r="K29" s="35"/>
     </row>
     <row r="30" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="483"/>
-      <c r="B30" s="486"/>
-      <c r="C30" s="489"/>
+      <c r="A30" s="491"/>
+      <c r="B30" s="494"/>
+      <c r="C30" s="497"/>
       <c r="D30" s="76" t="s">
         <v>94</v>
       </c>
@@ -27386,6 +27386,12 @@
   </sheetData>
   <autoFilter ref="A4:EI31" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="15">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="B5:B13"/>
+    <mergeCell ref="C5:C13"/>
     <mergeCell ref="A26:A30"/>
     <mergeCell ref="B26:B30"/>
     <mergeCell ref="C26:C30"/>
@@ -27395,12 +27401,6 @@
     <mergeCell ref="A20:A25"/>
     <mergeCell ref="B20:B25"/>
     <mergeCell ref="C20:C25"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="B5:B13"/>
-    <mergeCell ref="C5:C13"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K6:K7 K26" xr:uid="{EC1EB0C9-7584-409C-B7C9-CE8A33BC2994}"/>
@@ -27990,33 +27990,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:139" s="31" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="527"/>
-      <c r="B1" s="527"/>
-      <c r="C1" s="527"/>
-      <c r="D1" s="527"/>
-      <c r="E1" s="527"/>
-      <c r="F1" s="527"/>
-      <c r="G1" s="527"/>
+      <c r="A1" s="528"/>
+      <c r="B1" s="528"/>
+      <c r="C1" s="528"/>
+      <c r="D1" s="528"/>
+      <c r="E1" s="528"/>
+      <c r="F1" s="528"/>
+      <c r="G1" s="528"/>
       <c r="H1" s="104"/>
       <c r="I1" s="101"/>
       <c r="J1" s="102"/>
       <c r="K1" s="102"/>
     </row>
     <row r="2" spans="1:139" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="528" t="s">
+      <c r="A2" s="529" t="s">
         <v>434</v>
       </c>
-      <c r="B2" s="528"/>
-      <c r="C2" s="528"/>
-      <c r="D2" s="528"/>
-      <c r="E2" s="528"/>
-      <c r="F2" s="528"/>
-      <c r="G2" s="528"/>
+      <c r="B2" s="529"/>
+      <c r="C2" s="529"/>
+      <c r="D2" s="529"/>
+      <c r="E2" s="529"/>
+      <c r="F2" s="529"/>
+      <c r="G2" s="529"/>
       <c r="H2" s="105"/>
-      <c r="I2" s="422" t="s">
+      <c r="I2" s="402" t="s">
         <v>381</v>
       </c>
-      <c r="J2" s="422"/>
+      <c r="J2" s="402"/>
       <c r="K2" s="103"/>
     </row>
     <row r="3" spans="1:139" s="31" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -28065,10 +28065,10 @@
       </c>
     </row>
     <row r="5" spans="1:139" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="490">
+      <c r="A5" s="476">
         <v>1</v>
       </c>
-      <c r="B5" s="425" t="s">
+      <c r="B5" s="405" t="s">
         <v>399</v>
       </c>
       <c r="C5" s="509" t="s">
@@ -28096,9 +28096,9 @@
       </c>
     </row>
     <row r="6" spans="1:139" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="491"/>
-      <c r="B6" s="426"/>
-      <c r="C6" s="473"/>
+      <c r="A6" s="477"/>
+      <c r="B6" s="406"/>
+      <c r="C6" s="472"/>
       <c r="D6" s="73" t="s">
         <v>56</v>
       </c>
@@ -28119,9 +28119,9 @@
       <c r="K6" s="35"/>
     </row>
     <row r="7" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="491"/>
-      <c r="B7" s="426"/>
-      <c r="C7" s="473"/>
+      <c r="A7" s="477"/>
+      <c r="B7" s="406"/>
+      <c r="C7" s="472"/>
       <c r="D7" s="73" t="s">
         <v>55</v>
       </c>
@@ -28142,9 +28142,9 @@
       <c r="K7" s="35"/>
     </row>
     <row r="8" spans="1:139" ht="210" x14ac:dyDescent="0.2">
-      <c r="A8" s="491"/>
-      <c r="B8" s="426"/>
-      <c r="C8" s="473"/>
+      <c r="A8" s="477"/>
+      <c r="B8" s="406"/>
+      <c r="C8" s="472"/>
       <c r="D8" s="73" t="s">
         <v>63</v>
       </c>
@@ -28166,9 +28166,9 @@
       <c r="L8" s="38"/>
     </row>
     <row r="9" spans="1:139" ht="150" x14ac:dyDescent="0.2">
-      <c r="A9" s="491"/>
-      <c r="B9" s="426"/>
-      <c r="C9" s="473"/>
+      <c r="A9" s="477"/>
+      <c r="B9" s="406"/>
+      <c r="C9" s="472"/>
       <c r="D9" s="73" t="s">
         <v>68</v>
       </c>
@@ -28189,9 +28189,9 @@
       <c r="K9" s="35"/>
     </row>
     <row r="10" spans="1:139" ht="60" x14ac:dyDescent="0.2">
-      <c r="A10" s="491"/>
-      <c r="B10" s="426"/>
-      <c r="C10" s="473"/>
+      <c r="A10" s="477"/>
+      <c r="B10" s="406"/>
+      <c r="C10" s="472"/>
       <c r="D10" s="73" t="s">
         <v>72</v>
       </c>
@@ -28212,9 +28212,9 @@
       <c r="K10" s="35"/>
     </row>
     <row r="11" spans="1:139" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="491"/>
-      <c r="B11" s="426"/>
-      <c r="C11" s="473"/>
+      <c r="A11" s="477"/>
+      <c r="B11" s="406"/>
+      <c r="C11" s="472"/>
       <c r="D11" s="73" t="s">
         <v>86</v>
       </c>
@@ -28239,9 +28239,9 @@
       </c>
     </row>
     <row r="12" spans="1:139" s="42" customFormat="1" ht="347.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="491"/>
-      <c r="B12" s="426"/>
-      <c r="C12" s="473"/>
+      <c r="A12" s="477"/>
+      <c r="B12" s="406"/>
+      <c r="C12" s="472"/>
       <c r="D12" s="73" t="s">
         <v>92</v>
       </c>
@@ -28394,9 +28394,9 @@
       <c r="EI12" s="41"/>
     </row>
     <row r="13" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A13" s="491"/>
-      <c r="B13" s="426"/>
-      <c r="C13" s="473"/>
+      <c r="A13" s="477"/>
+      <c r="B13" s="406"/>
+      <c r="C13" s="472"/>
       <c r="D13" s="73" t="s">
         <v>282</v>
       </c>
@@ -28419,10 +28419,10 @@
       </c>
     </row>
     <row r="14" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="495">
+      <c r="A14" s="481">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="496" t="s">
+      <c r="B14" s="482" t="s">
         <v>98</v>
       </c>
       <c r="C14" s="509" t="s">
@@ -28450,8 +28450,8 @@
       </c>
     </row>
     <row r="15" spans="1:139" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="495"/>
-      <c r="B15" s="496"/>
+      <c r="A15" s="481"/>
+      <c r="B15" s="482"/>
       <c r="C15" s="530"/>
       <c r="D15" s="73" t="s">
         <v>56</v>
@@ -28475,8 +28475,8 @@
       <c r="K15" s="35"/>
     </row>
     <row r="16" spans="1:139" ht="140.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="495"/>
-      <c r="B16" s="496"/>
+      <c r="A16" s="481"/>
+      <c r="B16" s="482"/>
       <c r="C16" s="530"/>
       <c r="D16" s="73" t="s">
         <v>55</v>
@@ -28503,8 +28503,8 @@
       <c r="L16" s="38"/>
     </row>
     <row r="17" spans="1:139" s="47" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="495"/>
-      <c r="B17" s="496"/>
+      <c r="A17" s="481"/>
+      <c r="B17" s="482"/>
       <c r="C17" s="530"/>
       <c r="D17" s="76" t="s">
         <v>106</v>
@@ -28658,8 +28658,8 @@
       <c r="EI17" s="36"/>
     </row>
     <row r="18" spans="1:139" s="47" customFormat="1" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="495"/>
-      <c r="B18" s="496"/>
+      <c r="A18" s="481"/>
+      <c r="B18" s="482"/>
       <c r="C18" s="530"/>
       <c r="D18" s="76" t="s">
         <v>92</v>
@@ -28811,8 +28811,8 @@
       <c r="EI18" s="36"/>
     </row>
     <row r="19" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="490"/>
-      <c r="B19" s="497"/>
+      <c r="A19" s="476"/>
+      <c r="B19" s="483"/>
       <c r="C19" s="530"/>
       <c r="D19" s="78" t="s">
         <v>282</v>
@@ -28836,13 +28836,13 @@
       </c>
     </row>
     <row r="20" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="476">
+      <c r="A20" s="484">
         <v>2</v>
       </c>
-      <c r="B20" s="477" t="s">
+      <c r="B20" s="485" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="470" t="s">
+      <c r="C20" s="469" t="s">
         <v>408</v>
       </c>
       <c r="D20" s="73" t="s">
@@ -28865,8 +28865,8 @@
       <c r="K20" s="54"/>
     </row>
     <row r="21" spans="1:139" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="476"/>
-      <c r="B21" s="477"/>
+      <c r="A21" s="484"/>
+      <c r="B21" s="485"/>
       <c r="C21" s="519"/>
       <c r="D21" s="73" t="s">
         <v>56</v>
@@ -28890,8 +28890,8 @@
       <c r="K21" s="54"/>
     </row>
     <row r="22" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A22" s="476"/>
-      <c r="B22" s="477"/>
+      <c r="A22" s="484"/>
+      <c r="B22" s="485"/>
       <c r="C22" s="519"/>
       <c r="D22" s="73" t="s">
         <v>55</v>
@@ -28917,8 +28917,8 @@
       </c>
     </row>
     <row r="23" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A23" s="476"/>
-      <c r="B23" s="477"/>
+      <c r="A23" s="484"/>
+      <c r="B23" s="485"/>
       <c r="C23" s="519"/>
       <c r="D23" s="61" t="s">
         <v>114</v>
@@ -29072,8 +29072,8 @@
       <c r="EI23" s="36"/>
     </row>
     <row r="24" spans="1:139" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A24" s="476"/>
-      <c r="B24" s="477"/>
+      <c r="A24" s="484"/>
+      <c r="B24" s="485"/>
       <c r="C24" s="519"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
@@ -29227,8 +29227,8 @@
       <c r="EI24" s="36"/>
     </row>
     <row r="25" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="476"/>
-      <c r="B25" s="477"/>
+      <c r="A25" s="484"/>
+      <c r="B25" s="485"/>
       <c r="C25" s="520"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
@@ -29252,13 +29252,13 @@
       </c>
     </row>
     <row r="26" spans="1:139" ht="90" x14ac:dyDescent="0.2">
-      <c r="A26" s="481">
+      <c r="A26" s="489">
         <v>2.1</v>
       </c>
-      <c r="B26" s="484" t="s">
+      <c r="B26" s="492" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="487" t="s">
+      <c r="C26" s="495" t="s">
         <v>117</v>
       </c>
       <c r="D26" s="76" t="s">
@@ -29281,9 +29281,9 @@
       <c r="K26" s="35"/>
     </row>
     <row r="27" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A27" s="482"/>
-      <c r="B27" s="485"/>
-      <c r="C27" s="488"/>
+      <c r="A27" s="490"/>
+      <c r="B27" s="493"/>
+      <c r="C27" s="496"/>
       <c r="D27" s="73" t="s">
         <v>55</v>
       </c>
@@ -29306,9 +29306,9 @@
       <c r="K27" s="35"/>
     </row>
     <row r="28" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A28" s="482"/>
-      <c r="B28" s="485"/>
-      <c r="C28" s="488"/>
+      <c r="A28" s="490"/>
+      <c r="B28" s="493"/>
+      <c r="C28" s="496"/>
       <c r="D28" s="61" t="s">
         <v>114</v>
       </c>
@@ -29331,9 +29331,9 @@
       <c r="K28" s="35"/>
     </row>
     <row r="29" spans="1:139" ht="75" x14ac:dyDescent="0.2">
-      <c r="A29" s="482"/>
-      <c r="B29" s="485"/>
-      <c r="C29" s="488"/>
+      <c r="A29" s="490"/>
+      <c r="B29" s="493"/>
+      <c r="C29" s="496"/>
       <c r="D29" s="86" t="s">
         <v>92</v>
       </c>
@@ -29356,9 +29356,9 @@
       <c r="K29" s="35"/>
     </row>
     <row r="30" spans="1:139" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="483"/>
-      <c r="B30" s="486"/>
-      <c r="C30" s="489"/>
+      <c r="A30" s="491"/>
+      <c r="B30" s="494"/>
+      <c r="C30" s="497"/>
       <c r="D30" s="76" t="s">
         <v>94</v>
       </c>
@@ -30571,6 +30571,12 @@
   </sheetData>
   <autoFilter ref="A4:EI31" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="15">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="B5:B13"/>
+    <mergeCell ref="C5:C13"/>
     <mergeCell ref="A26:A30"/>
     <mergeCell ref="B26:B30"/>
     <mergeCell ref="C26:C30"/>
@@ -30580,12 +30586,6 @@
     <mergeCell ref="A20:A25"/>
     <mergeCell ref="B20:B25"/>
     <mergeCell ref="C20:C25"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="B5:B13"/>
-    <mergeCell ref="C5:C13"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K6:K7 K26" xr:uid="{F4C3080E-55C9-4ABE-B0CD-E6276EC6EDFB}"/>
@@ -42708,27 +42708,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:138" s="31" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="527"/>
-      <c r="B1" s="527"/>
-      <c r="C1" s="527"/>
-      <c r="D1" s="527"/>
-      <c r="E1" s="527"/>
-      <c r="F1" s="527"/>
-      <c r="G1" s="527"/>
+      <c r="A1" s="528"/>
+      <c r="B1" s="528"/>
+      <c r="C1" s="528"/>
+      <c r="D1" s="528"/>
+      <c r="E1" s="528"/>
+      <c r="F1" s="528"/>
+      <c r="G1" s="528"/>
       <c r="H1" s="24"/>
       <c r="I1" s="25"/>
       <c r="J1" s="25"/>
     </row>
     <row r="2" spans="1:138" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="528" t="s">
+      <c r="A2" s="529" t="s">
         <v>439</v>
       </c>
-      <c r="B2" s="528"/>
-      <c r="C2" s="528"/>
-      <c r="D2" s="528"/>
-      <c r="E2" s="528"/>
-      <c r="F2" s="528"/>
-      <c r="G2" s="528"/>
+      <c r="B2" s="529"/>
+      <c r="C2" s="529"/>
+      <c r="D2" s="529"/>
+      <c r="E2" s="529"/>
+      <c r="F2" s="529"/>
+      <c r="G2" s="529"/>
       <c r="H2" s="24"/>
       <c r="I2" s="25"/>
       <c r="J2" s="25"/>
@@ -42777,13 +42777,13 @@
       </c>
     </row>
     <row r="5" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="490">
+      <c r="A5" s="476">
         <v>1</v>
       </c>
-      <c r="B5" s="425" t="s">
+      <c r="B5" s="405" t="s">
         <v>399</v>
       </c>
-      <c r="C5" s="430" t="s">
+      <c r="C5" s="412" t="s">
         <v>440</v>
       </c>
       <c r="D5" s="73" t="s">
@@ -42807,9 +42807,9 @@
       </c>
     </row>
     <row r="6" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="491"/>
-      <c r="B6" s="426"/>
-      <c r="C6" s="431"/>
+      <c r="A6" s="477"/>
+      <c r="B6" s="406"/>
+      <c r="C6" s="413"/>
       <c r="D6" s="73" t="s">
         <v>56</v>
       </c>
@@ -42829,9 +42829,9 @@
       <c r="J6" s="35"/>
     </row>
     <row r="7" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="491"/>
-      <c r="B7" s="426"/>
-      <c r="C7" s="431"/>
+      <c r="A7" s="477"/>
+      <c r="B7" s="406"/>
+      <c r="C7" s="413"/>
       <c r="D7" s="73" t="s">
         <v>55</v>
       </c>
@@ -42851,9 +42851,9 @@
       <c r="J7" s="35"/>
     </row>
     <row r="8" spans="1:138" ht="210" x14ac:dyDescent="0.2">
-      <c r="A8" s="491"/>
-      <c r="B8" s="426"/>
-      <c r="C8" s="431"/>
+      <c r="A8" s="477"/>
+      <c r="B8" s="406"/>
+      <c r="C8" s="413"/>
       <c r="D8" s="73" t="s">
         <v>63</v>
       </c>
@@ -42874,9 +42874,9 @@
       <c r="K8" s="38"/>
     </row>
     <row r="9" spans="1:138" ht="150" x14ac:dyDescent="0.2">
-      <c r="A9" s="491"/>
-      <c r="B9" s="426"/>
-      <c r="C9" s="431"/>
+      <c r="A9" s="477"/>
+      <c r="B9" s="406"/>
+      <c r="C9" s="413"/>
       <c r="D9" s="73" t="s">
         <v>68</v>
       </c>
@@ -42896,9 +42896,9 @@
       <c r="J9" s="35"/>
     </row>
     <row r="10" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A10" s="491"/>
-      <c r="B10" s="426"/>
-      <c r="C10" s="431"/>
+      <c r="A10" s="477"/>
+      <c r="B10" s="406"/>
+      <c r="C10" s="413"/>
       <c r="D10" s="73" t="s">
         <v>72</v>
       </c>
@@ -42918,9 +42918,9 @@
       <c r="J10" s="35"/>
     </row>
     <row r="11" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="491"/>
-      <c r="B11" s="426"/>
-      <c r="C11" s="431"/>
+      <c r="A11" s="477"/>
+      <c r="B11" s="406"/>
+      <c r="C11" s="413"/>
       <c r="D11" s="73" t="s">
         <v>86</v>
       </c>
@@ -42944,9 +42944,9 @@
       </c>
     </row>
     <row r="12" spans="1:138" s="42" customFormat="1" ht="347.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="491"/>
-      <c r="B12" s="426"/>
-      <c r="C12" s="431"/>
+      <c r="A12" s="477"/>
+      <c r="B12" s="406"/>
+      <c r="C12" s="413"/>
       <c r="D12" s="73" t="s">
         <v>92</v>
       </c>
@@ -43096,9 +43096,9 @@
       <c r="EH12" s="41"/>
     </row>
     <row r="13" spans="1:138" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="491"/>
-      <c r="B13" s="426"/>
-      <c r="C13" s="431"/>
+      <c r="A13" s="477"/>
+      <c r="B13" s="406"/>
+      <c r="C13" s="413"/>
       <c r="D13" s="73" t="s">
         <v>282</v>
       </c>
@@ -43118,13 +43118,13 @@
       </c>
     </row>
     <row r="14" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A14" s="495">
+      <c r="A14" s="481">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="496" t="s">
+      <c r="B14" s="482" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="430" t="s">
+      <c r="C14" s="412" t="s">
         <v>441</v>
       </c>
       <c r="D14" s="73" t="s">
@@ -43148,9 +43148,9 @@
       </c>
     </row>
     <row r="15" spans="1:138" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="495"/>
-      <c r="B15" s="496"/>
-      <c r="C15" s="529"/>
+      <c r="A15" s="481"/>
+      <c r="B15" s="482"/>
+      <c r="C15" s="527"/>
       <c r="D15" s="73" t="s">
         <v>56</v>
       </c>
@@ -43172,9 +43172,9 @@
       <c r="J15" s="35"/>
     </row>
     <row r="16" spans="1:138" ht="140.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="495"/>
-      <c r="B16" s="496"/>
-      <c r="C16" s="529"/>
+      <c r="A16" s="481"/>
+      <c r="B16" s="482"/>
+      <c r="C16" s="527"/>
       <c r="D16" s="73" t="s">
         <v>55</v>
       </c>
@@ -43199,9 +43199,9 @@
       <c r="K16" s="38"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="495"/>
-      <c r="B17" s="496"/>
-      <c r="C17" s="529"/>
+      <c r="A17" s="481"/>
+      <c r="B17" s="482"/>
+      <c r="C17" s="527"/>
       <c r="D17" s="76" t="s">
         <v>106</v>
       </c>
@@ -43353,9 +43353,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" s="47" customFormat="1" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="495"/>
-      <c r="B18" s="496"/>
-      <c r="C18" s="529"/>
+      <c r="A18" s="481"/>
+      <c r="B18" s="482"/>
+      <c r="C18" s="527"/>
       <c r="D18" s="76" t="s">
         <v>92</v>
       </c>
@@ -43503,9 +43503,9 @@
       <c r="EH18" s="36"/>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="490"/>
-      <c r="B19" s="497"/>
-      <c r="C19" s="529"/>
+      <c r="A19" s="476"/>
+      <c r="B19" s="483"/>
+      <c r="C19" s="527"/>
       <c r="D19" s="78" t="s">
         <v>282</v>
       </c>
@@ -43525,13 +43525,13 @@
       </c>
     </row>
     <row r="20" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="476">
+      <c r="A20" s="484">
         <v>2</v>
       </c>
-      <c r="B20" s="477" t="s">
+      <c r="B20" s="485" t="s">
         <v>442</v>
       </c>
-      <c r="C20" s="470" t="s">
+      <c r="C20" s="469" t="s">
         <v>443</v>
       </c>
       <c r="D20" s="73" t="s">
@@ -43553,8 +43553,8 @@
       <c r="J20" s="54"/>
     </row>
     <row r="21" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A21" s="476"/>
-      <c r="B21" s="477"/>
+      <c r="A21" s="484"/>
+      <c r="B21" s="485"/>
       <c r="C21" s="519"/>
       <c r="D21" s="73" t="s">
         <v>56</v>
@@ -43577,8 +43577,8 @@
       <c r="J21" s="54"/>
     </row>
     <row r="22" spans="1:138" ht="165" x14ac:dyDescent="0.2">
-      <c r="A22" s="476"/>
-      <c r="B22" s="477"/>
+      <c r="A22" s="484"/>
+      <c r="B22" s="485"/>
       <c r="C22" s="519"/>
       <c r="D22" s="73" t="s">
         <v>55</v>
@@ -43603,8 +43603,8 @@
       </c>
     </row>
     <row r="23" spans="1:138" s="47" customFormat="1" ht="165" x14ac:dyDescent="0.2">
-      <c r="A23" s="476"/>
-      <c r="B23" s="477"/>
+      <c r="A23" s="484"/>
+      <c r="B23" s="485"/>
       <c r="C23" s="519"/>
       <c r="D23" s="61" t="s">
         <v>114</v>
@@ -43757,8 +43757,8 @@
       <c r="EH23" s="36"/>
     </row>
     <row r="24" spans="1:138" s="47" customFormat="1" ht="165" x14ac:dyDescent="0.2">
-      <c r="A24" s="476"/>
-      <c r="B24" s="477"/>
+      <c r="A24" s="484"/>
+      <c r="B24" s="485"/>
       <c r="C24" s="519"/>
       <c r="D24" s="86" t="s">
         <v>92</v>
@@ -43909,8 +43909,8 @@
       <c r="EH24" s="36"/>
     </row>
     <row r="25" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="476"/>
-      <c r="B25" s="477"/>
+      <c r="A25" s="484"/>
+      <c r="B25" s="485"/>
       <c r="C25" s="520"/>
       <c r="D25" s="76" t="s">
         <v>94</v>
@@ -45416,26 +45416,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:138" s="31" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="527"/>
-      <c r="B1" s="527"/>
-      <c r="C1" s="527"/>
-      <c r="D1" s="527"/>
-      <c r="E1" s="527"/>
-      <c r="F1" s="527"/>
+      <c r="A1" s="528"/>
+      <c r="B1" s="528"/>
+      <c r="C1" s="528"/>
+      <c r="D1" s="528"/>
+      <c r="E1" s="528"/>
+      <c r="F1" s="528"/>
       <c r="G1" s="23"/>
       <c r="H1" s="24"/>
       <c r="I1" s="25"/>
       <c r="J1" s="25"/>
     </row>
     <row r="2" spans="1:138" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="527" t="s">
+      <c r="A2" s="528" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="527"/>
-      <c r="C2" s="527"/>
-      <c r="D2" s="527"/>
-      <c r="E2" s="527"/>
-      <c r="F2" s="527"/>
+      <c r="B2" s="528"/>
+      <c r="C2" s="528"/>
+      <c r="D2" s="528"/>
+      <c r="E2" s="528"/>
+      <c r="F2" s="528"/>
       <c r="G2" s="23"/>
       <c r="H2" s="24"/>
       <c r="I2" s="25"/>
@@ -45485,13 +45485,13 @@
       </c>
     </row>
     <row r="5" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="490">
+      <c r="A5" s="476">
         <v>1</v>
       </c>
-      <c r="B5" s="540" t="s">
+      <c r="B5" s="533" t="s">
         <v>399</v>
       </c>
-      <c r="C5" s="538" t="s">
+      <c r="C5" s="535" t="s">
         <v>440</v>
       </c>
       <c r="D5" s="32" t="s">
@@ -45513,9 +45513,9 @@
       <c r="J5" s="35"/>
     </row>
     <row r="6" spans="1:138" ht="72.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="491"/>
-      <c r="B6" s="541"/>
-      <c r="C6" s="542"/>
+      <c r="A6" s="477"/>
+      <c r="B6" s="534"/>
+      <c r="C6" s="536"/>
       <c r="D6" s="32" t="s">
         <v>56</v>
       </c>
@@ -45535,9 +45535,9 @@
       <c r="J6" s="35"/>
     </row>
     <row r="7" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A7" s="491"/>
-      <c r="B7" s="541"/>
-      <c r="C7" s="542"/>
+      <c r="A7" s="477"/>
+      <c r="B7" s="534"/>
+      <c r="C7" s="536"/>
       <c r="D7" s="32" t="s">
         <v>55</v>
       </c>
@@ -45557,9 +45557,9 @@
       <c r="J7" s="35"/>
     </row>
     <row r="8" spans="1:138" ht="120" x14ac:dyDescent="0.2">
-      <c r="A8" s="491"/>
-      <c r="B8" s="541"/>
-      <c r="C8" s="542"/>
+      <c r="A8" s="477"/>
+      <c r="B8" s="534"/>
+      <c r="C8" s="536"/>
       <c r="D8" s="32" t="s">
         <v>63</v>
       </c>
@@ -45580,9 +45580,9 @@
       <c r="K8" s="38"/>
     </row>
     <row r="9" spans="1:138" ht="105" x14ac:dyDescent="0.2">
-      <c r="A9" s="491"/>
-      <c r="B9" s="541"/>
-      <c r="C9" s="542"/>
+      <c r="A9" s="477"/>
+      <c r="B9" s="534"/>
+      <c r="C9" s="536"/>
       <c r="D9" s="32" t="s">
         <v>68</v>
       </c>
@@ -45602,9 +45602,9 @@
       <c r="J9" s="35"/>
     </row>
     <row r="10" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A10" s="491"/>
-      <c r="B10" s="541"/>
-      <c r="C10" s="542"/>
+      <c r="A10" s="477"/>
+      <c r="B10" s="534"/>
+      <c r="C10" s="536"/>
       <c r="D10" s="32" t="s">
         <v>72</v>
       </c>
@@ -45624,9 +45624,9 @@
       <c r="J10" s="35"/>
     </row>
     <row r="11" spans="1:138" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A11" s="491"/>
-      <c r="B11" s="541"/>
-      <c r="C11" s="542"/>
+      <c r="A11" s="477"/>
+      <c r="B11" s="534"/>
+      <c r="C11" s="536"/>
       <c r="D11" s="32" t="s">
         <v>86</v>
       </c>
@@ -45650,9 +45650,9 @@
       </c>
     </row>
     <row r="12" spans="1:138" s="42" customFormat="1" ht="347.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="491"/>
-      <c r="B12" s="541"/>
-      <c r="C12" s="542"/>
+      <c r="A12" s="477"/>
+      <c r="B12" s="534"/>
+      <c r="C12" s="536"/>
       <c r="D12" s="32" t="s">
         <v>92</v>
       </c>
@@ -45802,9 +45802,9 @@
       <c r="EH12" s="41"/>
     </row>
     <row r="13" spans="1:138" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="491"/>
-      <c r="B13" s="541"/>
-      <c r="C13" s="542"/>
+      <c r="A13" s="477"/>
+      <c r="B13" s="534"/>
+      <c r="C13" s="536"/>
       <c r="D13" s="32" t="s">
         <v>282</v>
       </c>
@@ -45824,13 +45824,13 @@
       </c>
     </row>
     <row r="14" spans="1:138" ht="60" x14ac:dyDescent="0.2">
-      <c r="A14" s="495">
+      <c r="A14" s="481">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B14" s="536" t="s">
+      <c r="B14" s="540" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="538" t="s">
+      <c r="C14" s="535" t="s">
         <v>441</v>
       </c>
       <c r="D14" s="32" t="s">
@@ -45854,9 +45854,9 @@
       <c r="J14" s="44"/>
     </row>
     <row r="15" spans="1:138" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="495"/>
-      <c r="B15" s="536"/>
-      <c r="C15" s="539"/>
+      <c r="A15" s="481"/>
+      <c r="B15" s="540"/>
+      <c r="C15" s="542"/>
       <c r="D15" s="32" t="s">
         <v>56</v>
       </c>
@@ -45878,9 +45878,9 @@
       <c r="J15" s="35"/>
     </row>
     <row r="16" spans="1:138" ht="140.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="495"/>
-      <c r="B16" s="536"/>
-      <c r="C16" s="539"/>
+      <c r="A16" s="481"/>
+      <c r="B16" s="540"/>
+      <c r="C16" s="542"/>
       <c r="D16" s="32" t="s">
         <v>55</v>
       </c>
@@ -45905,9 +45905,9 @@
       <c r="K16" s="38"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="126" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="495"/>
-      <c r="B17" s="536"/>
-      <c r="C17" s="539"/>
+      <c r="A17" s="481"/>
+      <c r="B17" s="540"/>
+      <c r="C17" s="542"/>
       <c r="D17" s="46" t="s">
         <v>106</v>
       </c>
@@ -46059,9 +46059,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" s="47" customFormat="1" ht="129.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="495"/>
-      <c r="B18" s="536"/>
-      <c r="C18" s="539"/>
+      <c r="A18" s="481"/>
+      <c r="B18" s="540"/>
+      <c r="C18" s="542"/>
       <c r="D18" s="46" t="s">
         <v>92</v>
       </c>
@@ -46209,9 +46209,9 @@
       <c r="EH18" s="36"/>
     </row>
     <row r="19" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A19" s="490"/>
-      <c r="B19" s="537"/>
-      <c r="C19" s="539"/>
+      <c r="A19" s="476"/>
+      <c r="B19" s="541"/>
+      <c r="C19" s="542"/>
       <c r="D19" s="49" t="s">
         <v>282</v>
       </c>
@@ -46231,13 +46231,13 @@
       </c>
     </row>
     <row r="20" spans="1:138" ht="45" x14ac:dyDescent="0.2">
-      <c r="A20" s="476">
+      <c r="A20" s="484">
         <v>2</v>
       </c>
-      <c r="B20" s="533" t="s">
+      <c r="B20" s="537" t="s">
         <v>442</v>
       </c>
-      <c r="C20" s="534" t="s">
+      <c r="C20" s="538" t="s">
         <v>443</v>
       </c>
       <c r="D20" s="32" t="s">
@@ -46259,9 +46259,9 @@
       <c r="J20" s="54"/>
     </row>
     <row r="21" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A21" s="476"/>
-      <c r="B21" s="533"/>
-      <c r="C21" s="535"/>
+      <c r="A21" s="484"/>
+      <c r="B21" s="537"/>
+      <c r="C21" s="539"/>
       <c r="D21" s="32" t="s">
         <v>56</v>
       </c>
@@ -46283,9 +46283,9 @@
       <c r="J21" s="54"/>
     </row>
     <row r="22" spans="1:138" ht="210" x14ac:dyDescent="0.2">
-      <c r="A22" s="476"/>
-      <c r="B22" s="533"/>
-      <c r="C22" s="535"/>
+      <c r="A22" s="484"/>
+      <c r="B22" s="537"/>
+      <c r="C22" s="539"/>
       <c r="D22" s="32" t="s">
         <v>55</v>
       </c>
@@ -46309,9 +46309,9 @@
       </c>
     </row>
     <row r="23" spans="1:138" s="47" customFormat="1" ht="210" x14ac:dyDescent="0.2">
-      <c r="A23" s="476"/>
-      <c r="B23" s="533"/>
-      <c r="C23" s="535"/>
+      <c r="A23" s="484"/>
+      <c r="B23" s="537"/>
+      <c r="C23" s="539"/>
       <c r="D23" s="52" t="s">
         <v>114</v>
       </c>
@@ -46463,9 +46463,9 @@
       <c r="EH23" s="36"/>
     </row>
     <row r="24" spans="1:138" s="47" customFormat="1" ht="210" x14ac:dyDescent="0.2">
-      <c r="A24" s="476"/>
-      <c r="B24" s="533"/>
-      <c r="C24" s="535"/>
+      <c r="A24" s="484"/>
+      <c r="B24" s="537"/>
+      <c r="C24" s="539"/>
       <c r="D24" s="52" t="s">
         <v>92</v>
       </c>
@@ -46615,9 +46615,9 @@
       <c r="EH24" s="36"/>
     </row>
     <row r="25" spans="1:138" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="476"/>
-      <c r="B25" s="533"/>
-      <c r="C25" s="535"/>
+      <c r="A25" s="484"/>
+      <c r="B25" s="537"/>
+      <c r="C25" s="539"/>
       <c r="D25" s="52" t="s">
         <v>94</v>
       </c>
@@ -47827,17 +47827,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A5:A13"/>
-    <mergeCell ref="B5:B13"/>
-    <mergeCell ref="C5:C13"/>
     <mergeCell ref="A20:A25"/>
     <mergeCell ref="B20:B25"/>
     <mergeCell ref="C20:C25"/>
     <mergeCell ref="A14:A19"/>
     <mergeCell ref="B14:B19"/>
     <mergeCell ref="C14:C19"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A5:A13"/>
+    <mergeCell ref="B5:B13"/>
+    <mergeCell ref="C5:C13"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J5:J7" xr:uid="{D5870D16-9B64-40FF-B604-4C6EAE214F81}"/>
@@ -47904,18 +47904,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:133" s="31" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="434" t="s">
+      <c r="A1" s="418" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="434"/>
-      <c r="C1" s="434"/>
-      <c r="D1" s="434"/>
-      <c r="E1" s="434"/>
-      <c r="F1" s="434"/>
-      <c r="G1" s="434"/>
+      <c r="B1" s="418"/>
+      <c r="C1" s="418"/>
+      <c r="D1" s="418"/>
+      <c r="E1" s="418"/>
+      <c r="F1" s="418"/>
+      <c r="G1" s="418"/>
       <c r="H1" s="334"/>
-      <c r="I1" s="422"/>
-      <c r="J1" s="422"/>
+      <c r="I1" s="402"/>
+      <c r="J1" s="402"/>
     </row>
     <row r="2" spans="1:133" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -48087,10 +48087,10 @@
       <c r="EC3" s="36"/>
     </row>
     <row r="4" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A4" s="423">
+      <c r="A4" s="403">
         <v>1</v>
       </c>
-      <c r="B4" s="425" t="s">
+      <c r="B4" s="405" t="s">
         <v>50</v>
       </c>
       <c r="C4" s="543" t="s">
@@ -48115,8 +48115,8 @@
       </c>
     </row>
     <row r="5" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A5" s="424"/>
-      <c r="B5" s="426"/>
+      <c r="A5" s="404"/>
+      <c r="B5" s="406"/>
       <c r="C5" s="544"/>
       <c r="D5" s="73" t="s">
         <v>56</v>
@@ -48137,8 +48137,8 @@
       </c>
     </row>
     <row r="6" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A6" s="424"/>
-      <c r="B6" s="426"/>
+      <c r="A6" s="404"/>
+      <c r="B6" s="406"/>
       <c r="C6" s="544"/>
       <c r="D6" s="73" t="s">
         <v>61</v>
@@ -48159,8 +48159,8 @@
       </c>
     </row>
     <row r="7" spans="1:133" ht="72" x14ac:dyDescent="0.2">
-      <c r="A7" s="424"/>
-      <c r="B7" s="426"/>
+      <c r="A7" s="404"/>
+      <c r="B7" s="406"/>
       <c r="C7" s="544"/>
       <c r="D7" s="73" t="s">
         <v>63</v>
@@ -48181,8 +48181,8 @@
       </c>
     </row>
     <row r="8" spans="1:133" ht="108" x14ac:dyDescent="0.2">
-      <c r="A8" s="424"/>
-      <c r="B8" s="426"/>
+      <c r="A8" s="404"/>
+      <c r="B8" s="406"/>
       <c r="C8" s="544"/>
       <c r="D8" s="73" t="s">
         <v>68</v>
@@ -48203,8 +48203,8 @@
       </c>
     </row>
     <row r="9" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A9" s="424"/>
-      <c r="B9" s="426"/>
+      <c r="A9" s="404"/>
+      <c r="B9" s="406"/>
       <c r="C9" s="544"/>
       <c r="D9" s="73" t="s">
         <v>72</v>
@@ -48225,8 +48225,8 @@
       </c>
     </row>
     <row r="10" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="424"/>
-      <c r="B10" s="426"/>
+      <c r="A10" s="404"/>
+      <c r="B10" s="406"/>
       <c r="C10" s="544"/>
       <c r="D10" s="73" t="s">
         <v>76</v>
@@ -48247,8 +48247,8 @@
       </c>
     </row>
     <row r="11" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A11" s="424"/>
-      <c r="B11" s="426"/>
+      <c r="A11" s="404"/>
+      <c r="B11" s="406"/>
       <c r="C11" s="544"/>
       <c r="D11" s="73" t="s">
         <v>79</v>
@@ -48271,8 +48271,8 @@
       </c>
     </row>
     <row r="12" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A12" s="424"/>
-      <c r="B12" s="426"/>
+      <c r="A12" s="404"/>
+      <c r="B12" s="406"/>
       <c r="C12" s="544"/>
       <c r="D12" s="73" t="s">
         <v>83</v>
@@ -48295,8 +48295,8 @@
       </c>
     </row>
     <row r="13" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A13" s="424"/>
-      <c r="B13" s="426"/>
+      <c r="A13" s="404"/>
+      <c r="B13" s="406"/>
       <c r="C13" s="544"/>
       <c r="D13" s="73" t="s">
         <v>86</v>
@@ -48319,8 +48319,8 @@
       </c>
     </row>
     <row r="14" spans="1:133" s="42" customFormat="1" ht="150" x14ac:dyDescent="0.2">
-      <c r="A14" s="424"/>
-      <c r="B14" s="426"/>
+      <c r="A14" s="404"/>
+      <c r="B14" s="406"/>
       <c r="C14" s="544"/>
       <c r="D14" s="73" t="s">
         <v>92</v>
@@ -48466,8 +48466,8 @@
       <c r="EC14" s="41"/>
     </row>
     <row r="15" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="424"/>
-      <c r="B15" s="426"/>
+      <c r="A15" s="404"/>
+      <c r="B15" s="406"/>
       <c r="C15" s="545"/>
       <c r="D15" s="73" t="s">
         <v>94</v>
@@ -48488,13 +48488,13 @@
       </c>
     </row>
     <row r="16" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A16" s="415" t="s">
+      <c r="A16" s="410" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="416" t="s">
+      <c r="B16" s="411" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="430" t="s">
+      <c r="C16" s="412" t="s">
         <v>99</v>
       </c>
       <c r="D16" s="73" t="s">
@@ -48516,9 +48516,9 @@
       </c>
     </row>
     <row r="17" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="415"/>
-      <c r="B17" s="416"/>
-      <c r="C17" s="431"/>
+      <c r="A17" s="410"/>
+      <c r="B17" s="411"/>
+      <c r="C17" s="413"/>
       <c r="D17" s="73" t="s">
         <v>56</v>
       </c>
@@ -48540,9 +48540,9 @@
       </c>
     </row>
     <row r="18" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A18" s="415"/>
-      <c r="B18" s="416"/>
-      <c r="C18" s="431"/>
+      <c r="A18" s="410"/>
+      <c r="B18" s="411"/>
+      <c r="C18" s="413"/>
       <c r="D18" s="73" t="s">
         <v>61</v>
       </c>
@@ -48562,13 +48562,13 @@
       </c>
     </row>
     <row r="19" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="415"/>
-      <c r="B19" s="416"/>
-      <c r="C19" s="431"/>
-      <c r="D19" s="430" t="s">
+      <c r="A19" s="410"/>
+      <c r="B19" s="411"/>
+      <c r="C19" s="413"/>
+      <c r="D19" s="412" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="446" t="s">
+      <c r="E19" s="444" t="s">
         <v>77</v>
       </c>
       <c r="F19" s="73" t="s">
@@ -48584,11 +48584,11 @@
       </c>
     </row>
     <row r="20" spans="1:133" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A20" s="415"/>
-      <c r="B20" s="416"/>
-      <c r="C20" s="431"/>
-      <c r="D20" s="445"/>
-      <c r="E20" s="447"/>
+      <c r="A20" s="410"/>
+      <c r="B20" s="411"/>
+      <c r="C20" s="413"/>
+      <c r="D20" s="443"/>
+      <c r="E20" s="445"/>
       <c r="F20" s="73" t="s">
         <v>103</v>
       </c>
@@ -48725,9 +48725,9 @@
       <c r="EC20" s="36"/>
     </row>
     <row r="21" spans="1:133" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A21" s="415"/>
-      <c r="B21" s="416"/>
-      <c r="C21" s="431"/>
+      <c r="A21" s="410"/>
+      <c r="B21" s="411"/>
+      <c r="C21" s="413"/>
       <c r="D21" s="73" t="s">
         <v>79</v>
       </c>
@@ -48872,9 +48872,9 @@
       <c r="EC21" s="36"/>
     </row>
     <row r="22" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A22" s="415"/>
-      <c r="B22" s="416"/>
-      <c r="C22" s="431"/>
+      <c r="A22" s="410"/>
+      <c r="B22" s="411"/>
+      <c r="C22" s="413"/>
       <c r="D22" s="73" t="s">
         <v>83</v>
       </c>
@@ -48896,9 +48896,9 @@
       </c>
     </row>
     <row r="23" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A23" s="415"/>
-      <c r="B23" s="416"/>
-      <c r="C23" s="431"/>
+      <c r="A23" s="410"/>
+      <c r="B23" s="411"/>
+      <c r="C23" s="413"/>
       <c r="D23" s="73" t="s">
         <v>106</v>
       </c>
@@ -48920,9 +48920,9 @@
       </c>
     </row>
     <row r="24" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A24" s="415"/>
-      <c r="B24" s="416"/>
-      <c r="C24" s="431"/>
+      <c r="A24" s="410"/>
+      <c r="B24" s="411"/>
+      <c r="C24" s="413"/>
       <c r="D24" s="73" t="s">
         <v>92</v>
       </c>
@@ -48944,9 +48944,9 @@
       </c>
     </row>
     <row r="25" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="423"/>
-      <c r="B25" s="425"/>
-      <c r="C25" s="431"/>
+      <c r="A25" s="403"/>
+      <c r="B25" s="405"/>
+      <c r="C25" s="413"/>
       <c r="D25" s="189" t="s">
         <v>94</v>
       </c>
@@ -48966,13 +48966,13 @@
       </c>
     </row>
     <row r="26" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A26" s="402" t="s">
+      <c r="A26" s="421" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="437" t="s">
+      <c r="B26" s="435" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="435" t="s">
+      <c r="C26" s="449" t="s">
         <v>110</v>
       </c>
       <c r="D26" s="73" t="s">
@@ -48994,9 +48994,9 @@
       </c>
     </row>
     <row r="27" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A27" s="403"/>
-      <c r="B27" s="438"/>
-      <c r="C27" s="435"/>
+      <c r="A27" s="422"/>
+      <c r="B27" s="436"/>
+      <c r="C27" s="449"/>
       <c r="D27" s="73" t="s">
         <v>56</v>
       </c>
@@ -49018,9 +49018,9 @@
       </c>
     </row>
     <row r="28" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A28" s="403"/>
-      <c r="B28" s="438"/>
-      <c r="C28" s="435"/>
+      <c r="A28" s="422"/>
+      <c r="B28" s="436"/>
+      <c r="C28" s="449"/>
       <c r="D28" s="73" t="s">
         <v>61</v>
       </c>
@@ -49042,13 +49042,13 @@
       </c>
     </row>
     <row r="29" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29" s="403"/>
-      <c r="B29" s="438"/>
-      <c r="C29" s="435"/>
-      <c r="D29" s="436" t="s">
+      <c r="A29" s="422"/>
+      <c r="B29" s="436"/>
+      <c r="C29" s="449"/>
+      <c r="D29" s="440" t="s">
         <v>76</v>
       </c>
-      <c r="E29" s="440" t="s">
+      <c r="E29" s="441" t="s">
         <v>77</v>
       </c>
       <c r="F29" s="73" t="s">
@@ -49064,11 +49064,11 @@
       </c>
     </row>
     <row r="30" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="403"/>
-      <c r="B30" s="438"/>
-      <c r="C30" s="435"/>
-      <c r="D30" s="436"/>
-      <c r="E30" s="441"/>
+      <c r="A30" s="422"/>
+      <c r="B30" s="436"/>
+      <c r="C30" s="449"/>
+      <c r="D30" s="440"/>
+      <c r="E30" s="442"/>
       <c r="F30" s="73" t="s">
         <v>113</v>
       </c>
@@ -49084,9 +49084,9 @@
       </c>
     </row>
     <row r="31" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A31" s="403"/>
-      <c r="B31" s="438"/>
-      <c r="C31" s="435"/>
+      <c r="A31" s="422"/>
+      <c r="B31" s="436"/>
+      <c r="C31" s="449"/>
       <c r="D31" s="73" t="s">
         <v>79</v>
       </c>
@@ -49108,9 +49108,9 @@
       </c>
     </row>
     <row r="32" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A32" s="403"/>
-      <c r="B32" s="438"/>
-      <c r="C32" s="435"/>
+      <c r="A32" s="422"/>
+      <c r="B32" s="436"/>
+      <c r="C32" s="449"/>
       <c r="D32" s="73" t="s">
         <v>83</v>
       </c>
@@ -49132,9 +49132,9 @@
       </c>
     </row>
     <row r="33" spans="1:133" s="47" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A33" s="403"/>
-      <c r="B33" s="438"/>
-      <c r="C33" s="435"/>
+      <c r="A33" s="422"/>
+      <c r="B33" s="436"/>
+      <c r="C33" s="449"/>
       <c r="D33" s="73" t="s">
         <v>114</v>
       </c>
@@ -49279,9 +49279,9 @@
       <c r="EC33" s="36"/>
     </row>
     <row r="34" spans="1:133" s="47" customFormat="1" ht="45" x14ac:dyDescent="0.2">
-      <c r="A34" s="403"/>
-      <c r="B34" s="438"/>
-      <c r="C34" s="435"/>
+      <c r="A34" s="422"/>
+      <c r="B34" s="436"/>
+      <c r="C34" s="449"/>
       <c r="D34" s="73" t="s">
         <v>92</v>
       </c>
@@ -49426,9 +49426,9 @@
       <c r="EC34" s="36"/>
     </row>
     <row r="35" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A35" s="404"/>
-      <c r="B35" s="439"/>
-      <c r="C35" s="435"/>
+      <c r="A35" s="423"/>
+      <c r="B35" s="437"/>
+      <c r="C35" s="449"/>
       <c r="D35" s="73" t="s">
         <v>94</v>
       </c>
@@ -49448,13 +49448,13 @@
       </c>
     </row>
     <row r="36" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A36" s="402" t="s">
+      <c r="A36" s="421" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="405" t="s">
+      <c r="B36" s="424" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="420" t="s">
+      <c r="C36" s="428" t="s">
         <v>117</v>
       </c>
       <c r="D36" s="206" t="s">
@@ -49478,9 +49478,9 @@
       </c>
     </row>
     <row r="37" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A37" s="403"/>
-      <c r="B37" s="406"/>
-      <c r="C37" s="420"/>
+      <c r="A37" s="422"/>
+      <c r="B37" s="425"/>
+      <c r="C37" s="428"/>
       <c r="D37" s="189" t="s">
         <v>122</v>
       </c>
@@ -49502,9 +49502,9 @@
       </c>
     </row>
     <row r="38" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A38" s="403"/>
-      <c r="B38" s="406"/>
-      <c r="C38" s="420"/>
+      <c r="A38" s="422"/>
+      <c r="B38" s="425"/>
+      <c r="C38" s="428"/>
       <c r="D38" s="73" t="s">
         <v>126</v>
       </c>
@@ -49526,9 +49526,9 @@
       </c>
     </row>
     <row r="39" spans="1:133" ht="84" x14ac:dyDescent="0.2">
-      <c r="A39" s="403"/>
-      <c r="B39" s="406"/>
-      <c r="C39" s="420"/>
+      <c r="A39" s="422"/>
+      <c r="B39" s="425"/>
+      <c r="C39" s="428"/>
       <c r="D39" s="73" t="s">
         <v>130</v>
       </c>
@@ -49550,9 +49550,9 @@
       </c>
     </row>
     <row r="40" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A40" s="403"/>
-      <c r="B40" s="406"/>
-      <c r="C40" s="420"/>
+      <c r="A40" s="422"/>
+      <c r="B40" s="425"/>
+      <c r="C40" s="428"/>
       <c r="D40" s="189" t="s">
         <v>134</v>
       </c>
@@ -49572,9 +49572,9 @@
       </c>
     </row>
     <row r="41" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A41" s="403"/>
-      <c r="B41" s="406"/>
-      <c r="C41" s="420"/>
+      <c r="A41" s="422"/>
+      <c r="B41" s="425"/>
+      <c r="C41" s="428"/>
       <c r="D41" s="73" t="s">
         <v>61</v>
       </c>
@@ -49596,9 +49596,9 @@
       </c>
     </row>
     <row r="42" spans="1:133" ht="72" x14ac:dyDescent="0.2">
-      <c r="A42" s="403"/>
-      <c r="B42" s="406"/>
-      <c r="C42" s="420"/>
+      <c r="A42" s="422"/>
+      <c r="B42" s="425"/>
+      <c r="C42" s="428"/>
       <c r="D42" s="73" t="s">
         <v>76</v>
       </c>
@@ -49620,9 +49620,9 @@
       </c>
     </row>
     <row r="43" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A43" s="403"/>
-      <c r="B43" s="406"/>
-      <c r="C43" s="420"/>
+      <c r="A43" s="422"/>
+      <c r="B43" s="425"/>
+      <c r="C43" s="428"/>
       <c r="D43" s="264" t="s">
         <v>114</v>
       </c>
@@ -49644,9 +49644,9 @@
       </c>
     </row>
     <row r="44" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A44" s="403"/>
-      <c r="B44" s="406"/>
-      <c r="C44" s="420"/>
+      <c r="A44" s="422"/>
+      <c r="B44" s="425"/>
+      <c r="C44" s="428"/>
       <c r="D44" s="332" t="s">
         <v>92</v>
       </c>
@@ -49668,9 +49668,9 @@
       </c>
     </row>
     <row r="45" spans="1:133" ht="45" x14ac:dyDescent="0.2">
-      <c r="A45" s="404"/>
-      <c r="B45" s="407"/>
-      <c r="C45" s="421"/>
+      <c r="A45" s="423"/>
+      <c r="B45" s="426"/>
+      <c r="C45" s="429"/>
       <c r="D45" s="73" t="s">
         <v>94</v>
       </c>
@@ -49706,13 +49706,13 @@
       <c r="J46" s="108"/>
     </row>
     <row r="47" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A47" s="415" t="s">
+      <c r="A47" s="410" t="s">
         <v>141</v>
       </c>
-      <c r="B47" s="416" t="s">
+      <c r="B47" s="411" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="435" t="s">
+      <c r="C47" s="449" t="s">
         <v>142</v>
       </c>
       <c r="D47" s="73" t="s">
@@ -49734,9 +49734,9 @@
       </c>
     </row>
     <row r="48" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A48" s="415"/>
-      <c r="B48" s="416"/>
-      <c r="C48" s="436"/>
+      <c r="A48" s="410"/>
+      <c r="B48" s="411"/>
+      <c r="C48" s="440"/>
       <c r="D48" s="73" t="s">
         <v>56</v>
       </c>
@@ -49756,9 +49756,9 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="24" x14ac:dyDescent="0.2">
-      <c r="A49" s="415"/>
-      <c r="B49" s="416"/>
-      <c r="C49" s="436"/>
+      <c r="A49" s="410"/>
+      <c r="B49" s="411"/>
+      <c r="C49" s="440"/>
       <c r="D49" s="73" t="s">
         <v>61</v>
       </c>
@@ -49778,9 +49778,9 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="117.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="415"/>
-      <c r="B50" s="416"/>
-      <c r="C50" s="436"/>
+      <c r="A50" s="410"/>
+      <c r="B50" s="411"/>
+      <c r="C50" s="440"/>
       <c r="D50" s="73" t="s">
         <v>63</v>
       </c>
@@ -49800,9 +49800,9 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="108" x14ac:dyDescent="0.2">
-      <c r="A51" s="415"/>
-      <c r="B51" s="416"/>
-      <c r="C51" s="436"/>
+      <c r="A51" s="410"/>
+      <c r="B51" s="411"/>
+      <c r="C51" s="440"/>
       <c r="D51" s="73" t="s">
         <v>68</v>
       </c>
@@ -49822,9 +49822,9 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A52" s="415"/>
-      <c r="B52" s="416"/>
-      <c r="C52" s="436"/>
+      <c r="A52" s="410"/>
+      <c r="B52" s="411"/>
+      <c r="C52" s="440"/>
       <c r="D52" s="73" t="s">
         <v>143</v>
       </c>
@@ -49844,9 +49844,9 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A53" s="415"/>
-      <c r="B53" s="416"/>
-      <c r="C53" s="436"/>
+      <c r="A53" s="410"/>
+      <c r="B53" s="411"/>
+      <c r="C53" s="440"/>
       <c r="D53" s="73" t="s">
         <v>76</v>
       </c>
@@ -49866,9 +49866,9 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="75" x14ac:dyDescent="0.2">
-      <c r="A54" s="415"/>
-      <c r="B54" s="416"/>
-      <c r="C54" s="436"/>
+      <c r="A54" s="410"/>
+      <c r="B54" s="411"/>
+      <c r="C54" s="440"/>
       <c r="D54" s="73" t="s">
         <v>79</v>
       </c>
@@ -49890,9 +49890,9 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A55" s="415"/>
-      <c r="B55" s="416"/>
-      <c r="C55" s="436"/>
+      <c r="A55" s="410"/>
+      <c r="B55" s="411"/>
+      <c r="C55" s="440"/>
       <c r="D55" s="73" t="s">
         <v>83</v>
       </c>
@@ -49914,9 +49914,9 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A56" s="415"/>
-      <c r="B56" s="416"/>
-      <c r="C56" s="436"/>
+      <c r="A56" s="410"/>
+      <c r="B56" s="411"/>
+      <c r="C56" s="440"/>
       <c r="D56" s="73" t="s">
         <v>106</v>
       </c>
@@ -49938,9 +49938,9 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A57" s="415"/>
-      <c r="B57" s="416"/>
-      <c r="C57" s="436"/>
+      <c r="A57" s="410"/>
+      <c r="B57" s="411"/>
+      <c r="C57" s="440"/>
       <c r="D57" s="73" t="s">
         <v>92</v>
       </c>
@@ -49962,9 +49962,9 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A58" s="415"/>
-      <c r="B58" s="416"/>
-      <c r="C58" s="436"/>
+      <c r="A58" s="410"/>
+      <c r="B58" s="411"/>
+      <c r="C58" s="440"/>
       <c r="D58" s="73" t="s">
         <v>94</v>
       </c>
@@ -49986,27 +49986,27 @@
   </sheetData>
   <autoFilter ref="A2:EC43" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="21">
+    <mergeCell ref="A16:A25"/>
+    <mergeCell ref="B16:B25"/>
+    <mergeCell ref="C16:C25"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A4:A15"/>
+    <mergeCell ref="B4:B15"/>
+    <mergeCell ref="C4:C15"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A36:A45"/>
+    <mergeCell ref="B36:B45"/>
+    <mergeCell ref="C36:C45"/>
     <mergeCell ref="A47:A58"/>
     <mergeCell ref="B47:B58"/>
     <mergeCell ref="C47:C58"/>
     <mergeCell ref="A26:A35"/>
     <mergeCell ref="B26:B35"/>
     <mergeCell ref="C26:C35"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A36:A45"/>
-    <mergeCell ref="B36:B45"/>
-    <mergeCell ref="C36:C45"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A4:A15"/>
-    <mergeCell ref="B4:B15"/>
-    <mergeCell ref="C4:C15"/>
-    <mergeCell ref="A16:A25"/>
-    <mergeCell ref="B16:B25"/>
-    <mergeCell ref="C16:C25"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -50312,18 +50312,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:133" s="31" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="434" t="s">
+      <c r="A1" s="418" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="434"/>
-      <c r="C1" s="434"/>
-      <c r="D1" s="434"/>
-      <c r="E1" s="434"/>
-      <c r="F1" s="434"/>
-      <c r="G1" s="434"/>
+      <c r="B1" s="418"/>
+      <c r="C1" s="418"/>
+      <c r="D1" s="418"/>
+      <c r="E1" s="418"/>
+      <c r="F1" s="418"/>
+      <c r="G1" s="418"/>
       <c r="H1" s="334"/>
-      <c r="I1" s="422"/>
-      <c r="J1" s="422"/>
+      <c r="I1" s="402"/>
+      <c r="J1" s="402"/>
     </row>
     <row r="2" spans="1:133" s="29" customFormat="1" ht="30" x14ac:dyDescent="0.2">
       <c r="A2" s="27" t="s">
@@ -50495,13 +50495,13 @@
       <c r="EC3" s="36"/>
     </row>
     <row r="4" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A4" s="423">
+      <c r="A4" s="403">
         <v>1</v>
       </c>
-      <c r="B4" s="425" t="s">
+      <c r="B4" s="405" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="442" t="s">
+      <c r="C4" s="446" t="s">
         <v>222</v>
       </c>
       <c r="D4" s="73" t="s">
@@ -50523,9 +50523,9 @@
       </c>
     </row>
     <row r="5" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A5" s="424"/>
-      <c r="B5" s="426"/>
-      <c r="C5" s="443"/>
+      <c r="A5" s="404"/>
+      <c r="B5" s="406"/>
+      <c r="C5" s="447"/>
       <c r="D5" s="73" t="s">
         <v>56</v>
       </c>
@@ -50545,9 +50545,9 @@
       </c>
     </row>
     <row r="6" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A6" s="424"/>
-      <c r="B6" s="426"/>
-      <c r="C6" s="443"/>
+      <c r="A6" s="404"/>
+      <c r="B6" s="406"/>
+      <c r="C6" s="447"/>
       <c r="D6" s="73" t="s">
         <v>61</v>
       </c>
@@ -50567,9 +50567,9 @@
       </c>
     </row>
     <row r="7" spans="1:133" ht="72" x14ac:dyDescent="0.2">
-      <c r="A7" s="424"/>
-      <c r="B7" s="426"/>
-      <c r="C7" s="443"/>
+      <c r="A7" s="404"/>
+      <c r="B7" s="406"/>
+      <c r="C7" s="447"/>
       <c r="D7" s="73" t="s">
         <v>63</v>
       </c>
@@ -50589,9 +50589,9 @@
       </c>
     </row>
     <row r="8" spans="1:133" ht="108" x14ac:dyDescent="0.2">
-      <c r="A8" s="424"/>
-      <c r="B8" s="426"/>
-      <c r="C8" s="443"/>
+      <c r="A8" s="404"/>
+      <c r="B8" s="406"/>
+      <c r="C8" s="447"/>
       <c r="D8" s="73" t="s">
         <v>68</v>
       </c>
@@ -50611,9 +50611,9 @@
       </c>
     </row>
     <row r="9" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A9" s="424"/>
-      <c r="B9" s="426"/>
-      <c r="C9" s="443"/>
+      <c r="A9" s="404"/>
+      <c r="B9" s="406"/>
+      <c r="C9" s="447"/>
       <c r="D9" s="73" t="s">
         <v>72</v>
       </c>
@@ -50633,9 +50633,9 @@
       </c>
     </row>
     <row r="10" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="424"/>
-      <c r="B10" s="426"/>
-      <c r="C10" s="443"/>
+      <c r="A10" s="404"/>
+      <c r="B10" s="406"/>
+      <c r="C10" s="447"/>
       <c r="D10" s="73" t="s">
         <v>76</v>
       </c>
@@ -50655,9 +50655,9 @@
       </c>
     </row>
     <row r="11" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A11" s="424"/>
-      <c r="B11" s="426"/>
-      <c r="C11" s="443"/>
+      <c r="A11" s="404"/>
+      <c r="B11" s="406"/>
+      <c r="C11" s="447"/>
       <c r="D11" s="73" t="s">
         <v>79</v>
       </c>
@@ -50679,9 +50679,9 @@
       </c>
     </row>
     <row r="12" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A12" s="424"/>
-      <c r="B12" s="426"/>
-      <c r="C12" s="443"/>
+      <c r="A12" s="404"/>
+      <c r="B12" s="406"/>
+      <c r="C12" s="447"/>
       <c r="D12" s="73" t="s">
         <v>83</v>
       </c>
@@ -50703,9 +50703,9 @@
       </c>
     </row>
     <row r="13" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A13" s="424"/>
-      <c r="B13" s="426"/>
-      <c r="C13" s="443"/>
+      <c r="A13" s="404"/>
+      <c r="B13" s="406"/>
+      <c r="C13" s="447"/>
       <c r="D13" s="73" t="s">
         <v>86</v>
       </c>
@@ -50727,9 +50727,9 @@
       </c>
     </row>
     <row r="14" spans="1:133" s="42" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A14" s="424"/>
-      <c r="B14" s="426"/>
-      <c r="C14" s="443"/>
+      <c r="A14" s="404"/>
+      <c r="B14" s="406"/>
+      <c r="C14" s="447"/>
       <c r="D14" s="73" t="s">
         <v>92</v>
       </c>
@@ -50874,9 +50874,9 @@
       <c r="EC14" s="41"/>
     </row>
     <row r="15" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="424"/>
-      <c r="B15" s="426"/>
-      <c r="C15" s="444"/>
+      <c r="A15" s="404"/>
+      <c r="B15" s="406"/>
+      <c r="C15" s="448"/>
       <c r="D15" s="73" t="s">
         <v>94</v>
       </c>
@@ -50896,13 +50896,13 @@
       </c>
     </row>
     <row r="16" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A16" s="415" t="s">
+      <c r="A16" s="410" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="416" t="s">
+      <c r="B16" s="411" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="430" t="s">
+      <c r="C16" s="412" t="s">
         <v>99</v>
       </c>
       <c r="D16" s="73" t="s">
@@ -50924,9 +50924,9 @@
       </c>
     </row>
     <row r="17" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A17" s="415"/>
-      <c r="B17" s="416"/>
-      <c r="C17" s="431"/>
+      <c r="A17" s="410"/>
+      <c r="B17" s="411"/>
+      <c r="C17" s="413"/>
       <c r="D17" s="73" t="s">
         <v>56</v>
       </c>
@@ -50948,9 +50948,9 @@
       </c>
     </row>
     <row r="18" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A18" s="415"/>
-      <c r="B18" s="416"/>
-      <c r="C18" s="431"/>
+      <c r="A18" s="410"/>
+      <c r="B18" s="411"/>
+      <c r="C18" s="413"/>
       <c r="D18" s="73" t="s">
         <v>61</v>
       </c>
@@ -50970,13 +50970,13 @@
       </c>
     </row>
     <row r="19" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="415"/>
-      <c r="B19" s="416"/>
-      <c r="C19" s="431"/>
-      <c r="D19" s="430" t="s">
+      <c r="A19" s="410"/>
+      <c r="B19" s="411"/>
+      <c r="C19" s="413"/>
+      <c r="D19" s="412" t="s">
         <v>76</v>
       </c>
-      <c r="E19" s="446" t="s">
+      <c r="E19" s="444" t="s">
         <v>77</v>
       </c>
       <c r="F19" s="73" t="s">
@@ -50992,11 +50992,11 @@
       </c>
     </row>
     <row r="20" spans="1:133" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A20" s="415"/>
-      <c r="B20" s="416"/>
-      <c r="C20" s="431"/>
-      <c r="D20" s="445"/>
-      <c r="E20" s="447"/>
+      <c r="A20" s="410"/>
+      <c r="B20" s="411"/>
+      <c r="C20" s="413"/>
+      <c r="D20" s="443"/>
+      <c r="E20" s="445"/>
       <c r="F20" s="73" t="s">
         <v>103</v>
       </c>
@@ -51133,9 +51133,9 @@
       <c r="EC20" s="36"/>
     </row>
     <row r="21" spans="1:133" s="47" customFormat="1" ht="75" x14ac:dyDescent="0.2">
-      <c r="A21" s="415"/>
-      <c r="B21" s="416"/>
-      <c r="C21" s="431"/>
+      <c r="A21" s="410"/>
+      <c r="B21" s="411"/>
+      <c r="C21" s="413"/>
       <c r="D21" s="73" t="s">
         <v>79</v>
       </c>
@@ -51280,9 +51280,9 @@
       <c r="EC21" s="36"/>
     </row>
     <row r="22" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A22" s="415"/>
-      <c r="B22" s="416"/>
-      <c r="C22" s="431"/>
+      <c r="A22" s="410"/>
+      <c r="B22" s="411"/>
+      <c r="C22" s="413"/>
       <c r="D22" s="73" t="s">
         <v>83</v>
       </c>
@@ -51304,9 +51304,9 @@
       </c>
     </row>
     <row r="23" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A23" s="415"/>
-      <c r="B23" s="416"/>
-      <c r="C23" s="431"/>
+      <c r="A23" s="410"/>
+      <c r="B23" s="411"/>
+      <c r="C23" s="413"/>
       <c r="D23" s="73" t="s">
         <v>106</v>
       </c>
@@ -51328,9 +51328,9 @@
       </c>
     </row>
     <row r="24" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A24" s="415"/>
-      <c r="B24" s="416"/>
-      <c r="C24" s="431"/>
+      <c r="A24" s="410"/>
+      <c r="B24" s="411"/>
+      <c r="C24" s="413"/>
       <c r="D24" s="73" t="s">
         <v>92</v>
       </c>
@@ -51352,9 +51352,9 @@
       </c>
     </row>
     <row r="25" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="423"/>
-      <c r="B25" s="425"/>
-      <c r="C25" s="431"/>
+      <c r="A25" s="403"/>
+      <c r="B25" s="405"/>
+      <c r="C25" s="413"/>
       <c r="D25" s="189" t="s">
         <v>94</v>
       </c>
@@ -51374,13 +51374,13 @@
       </c>
     </row>
     <row r="26" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A26" s="402" t="s">
+      <c r="A26" s="421" t="s">
         <v>108</v>
       </c>
-      <c r="B26" s="437" t="s">
+      <c r="B26" s="435" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="435" t="s">
+      <c r="C26" s="449" t="s">
         <v>110</v>
       </c>
       <c r="D26" s="73" t="s">
@@ -51402,9 +51402,9 @@
       </c>
     </row>
     <row r="27" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A27" s="403"/>
-      <c r="B27" s="438"/>
-      <c r="C27" s="435"/>
+      <c r="A27" s="422"/>
+      <c r="B27" s="436"/>
+      <c r="C27" s="449"/>
       <c r="D27" s="73" t="s">
         <v>56</v>
       </c>
@@ -51426,9 +51426,9 @@
       </c>
     </row>
     <row r="28" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A28" s="403"/>
-      <c r="B28" s="438"/>
-      <c r="C28" s="435"/>
+      <c r="A28" s="422"/>
+      <c r="B28" s="436"/>
+      <c r="C28" s="449"/>
       <c r="D28" s="73" t="s">
         <v>61</v>
       </c>
@@ -51450,13 +51450,13 @@
       </c>
     </row>
     <row r="29" spans="1:133" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29" s="403"/>
-      <c r="B29" s="438"/>
-      <c r="C29" s="435"/>
-      <c r="D29" s="436" t="s">
+      <c r="A29" s="422"/>
+      <c r="B29" s="436"/>
+      <c r="C29" s="449"/>
+      <c r="D29" s="440" t="s">
         <v>76</v>
       </c>
-      <c r="E29" s="440" t="s">
+      <c r="E29" s="441" t="s">
         <v>77</v>
       </c>
       <c r="F29" s="73" t="s">
@@ -51472,11 +51472,11 @@
       </c>
     </row>
     <row r="30" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="403"/>
-      <c r="B30" s="438"/>
-      <c r="C30" s="435"/>
-      <c r="D30" s="436"/>
-      <c r="E30" s="441"/>
+      <c r="A30" s="422"/>
+      <c r="B30" s="436"/>
+      <c r="C30" s="449"/>
+      <c r="D30" s="440"/>
+      <c r="E30" s="442"/>
       <c r="F30" s="73" t="s">
         <v>113</v>
       </c>
@@ -51492,9 +51492,9 @@
       </c>
     </row>
     <row r="31" spans="1:133" ht="75" x14ac:dyDescent="0.2">
-      <c r="A31" s="403"/>
-      <c r="B31" s="438"/>
-      <c r="C31" s="435"/>
+      <c r="A31" s="422"/>
+      <c r="B31" s="436"/>
+      <c r="C31" s="449"/>
       <c r="D31" s="73" t="s">
         <v>79</v>
       </c>
@@ -51516,9 +51516,9 @@
       </c>
     </row>
     <row r="32" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A32" s="403"/>
-      <c r="B32" s="438"/>
-      <c r="C32" s="435"/>
+      <c r="A32" s="422"/>
+      <c r="B32" s="436"/>
+      <c r="C32" s="449"/>
       <c r="D32" s="73" t="s">
         <v>83</v>
       </c>
@@ -51540,9 +51540,9 @@
       </c>
     </row>
     <row r="33" spans="1:133" s="47" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A33" s="403"/>
-      <c r="B33" s="438"/>
-      <c r="C33" s="435"/>
+      <c r="A33" s="422"/>
+      <c r="B33" s="436"/>
+      <c r="C33" s="449"/>
       <c r="D33" s="73" t="s">
         <v>114</v>
       </c>
@@ -51687,9 +51687,9 @@
       <c r="EC33" s="36"/>
     </row>
     <row r="34" spans="1:133" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A34" s="403"/>
-      <c r="B34" s="438"/>
-      <c r="C34" s="435"/>
+      <c r="A34" s="422"/>
+      <c r="B34" s="436"/>
+      <c r="C34" s="449"/>
       <c r="D34" s="73" t="s">
         <v>92</v>
       </c>
@@ -51834,9 +51834,9 @@
       <c r="EC34" s="36"/>
     </row>
     <row r="35" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A35" s="404"/>
-      <c r="B35" s="439"/>
-      <c r="C35" s="435"/>
+      <c r="A35" s="423"/>
+      <c r="B35" s="437"/>
+      <c r="C35" s="449"/>
       <c r="D35" s="73" t="s">
         <v>94</v>
       </c>
@@ -51856,13 +51856,13 @@
       </c>
     </row>
     <row r="36" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A36" s="402" t="s">
+      <c r="A36" s="421" t="s">
         <v>115</v>
       </c>
-      <c r="B36" s="405" t="s">
+      <c r="B36" s="424" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="420" t="s">
+      <c r="C36" s="428" t="s">
         <v>117</v>
       </c>
       <c r="D36" s="206" t="s">
@@ -51886,9 +51886,9 @@
       </c>
     </row>
     <row r="37" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A37" s="403"/>
-      <c r="B37" s="406"/>
-      <c r="C37" s="420"/>
+      <c r="A37" s="422"/>
+      <c r="B37" s="425"/>
+      <c r="C37" s="428"/>
       <c r="D37" s="189" t="s">
         <v>122</v>
       </c>
@@ -51910,9 +51910,9 @@
       </c>
     </row>
     <row r="38" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A38" s="403"/>
-      <c r="B38" s="406"/>
-      <c r="C38" s="420"/>
+      <c r="A38" s="422"/>
+      <c r="B38" s="425"/>
+      <c r="C38" s="428"/>
       <c r="D38" s="73" t="s">
         <v>126</v>
       </c>
@@ -51934,9 +51934,9 @@
       </c>
     </row>
     <row r="39" spans="1:133" ht="84" x14ac:dyDescent="0.2">
-      <c r="A39" s="403"/>
-      <c r="B39" s="406"/>
-      <c r="C39" s="420"/>
+      <c r="A39" s="422"/>
+      <c r="B39" s="425"/>
+      <c r="C39" s="428"/>
       <c r="D39" s="73" t="s">
         <v>130</v>
       </c>
@@ -51958,9 +51958,9 @@
       </c>
     </row>
     <row r="40" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A40" s="403"/>
-      <c r="B40" s="406"/>
-      <c r="C40" s="420"/>
+      <c r="A40" s="422"/>
+      <c r="B40" s="425"/>
+      <c r="C40" s="428"/>
       <c r="D40" s="189" t="s">
         <v>134</v>
       </c>
@@ -51980,9 +51980,9 @@
       </c>
     </row>
     <row r="41" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A41" s="403"/>
-      <c r="B41" s="406"/>
-      <c r="C41" s="420"/>
+      <c r="A41" s="422"/>
+      <c r="B41" s="425"/>
+      <c r="C41" s="428"/>
       <c r="D41" s="73" t="s">
         <v>61</v>
       </c>
@@ -52004,9 +52004,9 @@
       </c>
     </row>
     <row r="42" spans="1:133" ht="72" x14ac:dyDescent="0.2">
-      <c r="A42" s="403"/>
-      <c r="B42" s="406"/>
-      <c r="C42" s="420"/>
+      <c r="A42" s="422"/>
+      <c r="B42" s="425"/>
+      <c r="C42" s="428"/>
       <c r="D42" s="73" t="s">
         <v>76</v>
       </c>
@@ -52028,9 +52028,9 @@
       </c>
     </row>
     <row r="43" spans="1:133" ht="48" x14ac:dyDescent="0.2">
-      <c r="A43" s="403"/>
-      <c r="B43" s="406"/>
-      <c r="C43" s="420"/>
+      <c r="A43" s="422"/>
+      <c r="B43" s="425"/>
+      <c r="C43" s="428"/>
       <c r="D43" s="264" t="s">
         <v>114</v>
       </c>
@@ -52052,9 +52052,9 @@
       </c>
     </row>
     <row r="44" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A44" s="403"/>
-      <c r="B44" s="406"/>
-      <c r="C44" s="420"/>
+      <c r="A44" s="422"/>
+      <c r="B44" s="425"/>
+      <c r="C44" s="428"/>
       <c r="D44" s="332" t="s">
         <v>92</v>
       </c>
@@ -52076,9 +52076,9 @@
       </c>
     </row>
     <row r="45" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A45" s="404"/>
-      <c r="B45" s="407"/>
-      <c r="C45" s="421"/>
+      <c r="A45" s="423"/>
+      <c r="B45" s="426"/>
+      <c r="C45" s="429"/>
       <c r="D45" s="73" t="s">
         <v>94</v>
       </c>
@@ -52114,13 +52114,13 @@
       <c r="J46" s="108"/>
     </row>
     <row r="47" spans="1:133" ht="36" x14ac:dyDescent="0.2">
-      <c r="A47" s="415" t="s">
+      <c r="A47" s="410" t="s">
         <v>141</v>
       </c>
-      <c r="B47" s="416" t="s">
+      <c r="B47" s="411" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="435" t="s">
+      <c r="C47" s="449" t="s">
         <v>142</v>
       </c>
       <c r="D47" s="73" t="s">
@@ -52142,9 +52142,9 @@
       </c>
     </row>
     <row r="48" spans="1:133" ht="24" x14ac:dyDescent="0.2">
-      <c r="A48" s="415"/>
-      <c r="B48" s="416"/>
-      <c r="C48" s="436"/>
+      <c r="A48" s="410"/>
+      <c r="B48" s="411"/>
+      <c r="C48" s="440"/>
       <c r="D48" s="73" t="s">
         <v>56</v>
       </c>
@@ -52164,9 +52164,9 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="24" x14ac:dyDescent="0.2">
-      <c r="A49" s="415"/>
-      <c r="B49" s="416"/>
-      <c r="C49" s="436"/>
+      <c r="A49" s="410"/>
+      <c r="B49" s="411"/>
+      <c r="C49" s="440"/>
       <c r="D49" s="73" t="s">
         <v>61</v>
       </c>
@@ -52186,9 +52186,9 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="117.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="415"/>
-      <c r="B50" s="416"/>
-      <c r="C50" s="436"/>
+      <c r="A50" s="410"/>
+      <c r="B50" s="411"/>
+      <c r="C50" s="440"/>
       <c r="D50" s="73" t="s">
         <v>63</v>
       </c>
@@ -52208,9 +52208,9 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="108" x14ac:dyDescent="0.2">
-      <c r="A51" s="415"/>
-      <c r="B51" s="416"/>
-      <c r="C51" s="436"/>
+      <c r="A51" s="410"/>
+      <c r="B51" s="411"/>
+      <c r="C51" s="440"/>
       <c r="D51" s="73" t="s">
         <v>68</v>
       </c>
@@ -52230,9 +52230,9 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A52" s="415"/>
-      <c r="B52" s="416"/>
-      <c r="C52" s="436"/>
+      <c r="A52" s="410"/>
+      <c r="B52" s="411"/>
+      <c r="C52" s="440"/>
       <c r="D52" s="73" t="s">
         <v>143</v>
       </c>
@@ -52252,9 +52252,9 @@
       </c>
     </row>
     <row r="53" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A53" s="415"/>
-      <c r="B53" s="416"/>
-      <c r="C53" s="436"/>
+      <c r="A53" s="410"/>
+      <c r="B53" s="411"/>
+      <c r="C53" s="440"/>
       <c r="D53" s="73" t="s">
         <v>76</v>
       </c>
@@ -52274,9 +52274,9 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="75" x14ac:dyDescent="0.2">
-      <c r="A54" s="415"/>
-      <c r="B54" s="416"/>
-      <c r="C54" s="436"/>
+      <c r="A54" s="410"/>
+      <c r="B54" s="411"/>
+      <c r="C54" s="440"/>
       <c r="D54" s="73" t="s">
         <v>79</v>
       </c>
@@ -52298,9 +52298,9 @@
       </c>
     </row>
     <row r="55" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A55" s="415"/>
-      <c r="B55" s="416"/>
-      <c r="C55" s="436"/>
+      <c r="A55" s="410"/>
+      <c r="B55" s="411"/>
+      <c r="C55" s="440"/>
       <c r="D55" s="73" t="s">
         <v>83</v>
       </c>
@@ -52322,9 +52322,9 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A56" s="415"/>
-      <c r="B56" s="416"/>
-      <c r="C56" s="436"/>
+      <c r="A56" s="410"/>
+      <c r="B56" s="411"/>
+      <c r="C56" s="440"/>
       <c r="D56" s="73" t="s">
         <v>106</v>
       </c>
@@ -52346,9 +52346,9 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A57" s="415"/>
-      <c r="B57" s="416"/>
-      <c r="C57" s="436"/>
+      <c r="A57" s="410"/>
+      <c r="B57" s="411"/>
+      <c r="C57" s="440"/>
       <c r="D57" s="73" t="s">
         <v>92</v>
       </c>
@@ -52370,9 +52370,9 @@
       </c>
     </row>
     <row r="58" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A58" s="415"/>
-      <c r="B58" s="416"/>
-      <c r="C58" s="436"/>
+      <c r="A58" s="410"/>
+      <c r="B58" s="411"/>
+      <c r="C58" s="440"/>
       <c r="D58" s="73" t="s">
         <v>94</v>
       </c>
@@ -52392,13 +52392,13 @@
       </c>
     </row>
     <row r="59" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A59" s="402" t="s">
+      <c r="A59" s="421" t="s">
         <v>108</v>
       </c>
-      <c r="B59" s="437" t="s">
+      <c r="B59" s="435" t="s">
         <v>109</v>
       </c>
-      <c r="C59" s="448" t="s">
+      <c r="C59" s="438" t="s">
         <v>223</v>
       </c>
       <c r="D59" s="73" t="s">
@@ -52420,9 +52420,9 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A60" s="403"/>
-      <c r="B60" s="438"/>
-      <c r="C60" s="449"/>
+      <c r="A60" s="422"/>
+      <c r="B60" s="436"/>
+      <c r="C60" s="439"/>
       <c r="D60" s="73" t="s">
         <v>56</v>
       </c>
@@ -52444,9 +52444,9 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A61" s="403"/>
-      <c r="B61" s="438"/>
-      <c r="C61" s="449"/>
+      <c r="A61" s="422"/>
+      <c r="B61" s="436"/>
+      <c r="C61" s="439"/>
       <c r="D61" s="73" t="s">
         <v>61</v>
       </c>
@@ -52468,13 +52468,13 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="15" x14ac:dyDescent="0.2">
-      <c r="A62" s="403"/>
-      <c r="B62" s="438"/>
-      <c r="C62" s="449"/>
-      <c r="D62" s="436" t="s">
+      <c r="A62" s="422"/>
+      <c r="B62" s="436"/>
+      <c r="C62" s="439"/>
+      <c r="D62" s="440" t="s">
         <v>76</v>
       </c>
-      <c r="E62" s="440" t="s">
+      <c r="E62" s="441" t="s">
         <v>77</v>
       </c>
       <c r="F62" s="73" t="s">
@@ -52490,11 +52490,11 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A63" s="403"/>
-      <c r="B63" s="438"/>
-      <c r="C63" s="449"/>
-      <c r="D63" s="436"/>
-      <c r="E63" s="441"/>
+      <c r="A63" s="422"/>
+      <c r="B63" s="436"/>
+      <c r="C63" s="439"/>
+      <c r="D63" s="440"/>
+      <c r="E63" s="442"/>
       <c r="F63" s="73" t="s">
         <v>113</v>
       </c>
@@ -52510,9 +52510,9 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="75" x14ac:dyDescent="0.2">
-      <c r="A64" s="403"/>
-      <c r="B64" s="438"/>
-      <c r="C64" s="449"/>
+      <c r="A64" s="422"/>
+      <c r="B64" s="436"/>
+      <c r="C64" s="439"/>
       <c r="D64" s="73" t="s">
         <v>79</v>
       </c>
@@ -52534,9 +52534,9 @@
       </c>
     </row>
     <row r="65" spans="1:133" ht="60" x14ac:dyDescent="0.2">
-      <c r="A65" s="403"/>
-      <c r="B65" s="438"/>
-      <c r="C65" s="449"/>
+      <c r="A65" s="422"/>
+      <c r="B65" s="436"/>
+      <c r="C65" s="439"/>
       <c r="D65" s="73" t="s">
         <v>83</v>
       </c>
@@ -52558,9 +52558,9 @@
       </c>
     </row>
     <row r="66" spans="1:133" s="47" customFormat="1" ht="48" x14ac:dyDescent="0.2">
-      <c r="A66" s="403"/>
-      <c r="B66" s="438"/>
-      <c r="C66" s="449"/>
+      <c r="A66" s="422"/>
+      <c r="B66" s="436"/>
+      <c r="C66" s="439"/>
       <c r="D66" s="73" t="s">
         <v>114</v>
       </c>
@@ -52705,9 +52705,9 @@
       <c r="EC66" s="36"/>
     </row>
     <row r="67" spans="1:133" s="47" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A67" s="403"/>
-      <c r="B67" s="438"/>
-      <c r="C67" s="449"/>
+      <c r="A67" s="422"/>
+      <c r="B67" s="436"/>
+      <c r="C67" s="439"/>
       <c r="D67" s="73" t="s">
         <v>92</v>
       </c>
@@ -52852,9 +52852,9 @@
       <c r="EC67" s="36"/>
     </row>
     <row r="68" spans="1:133" ht="30" x14ac:dyDescent="0.2">
-      <c r="A68" s="404"/>
-      <c r="B68" s="439"/>
-      <c r="C68" s="449"/>
+      <c r="A68" s="423"/>
+      <c r="B68" s="437"/>
+      <c r="C68" s="439"/>
       <c r="D68" s="73" t="s">
         <v>94</v>
       </c>
@@ -52876,32 +52876,32 @@
   </sheetData>
   <autoFilter ref="A2:EC43" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="26">
-    <mergeCell ref="A59:A68"/>
-    <mergeCell ref="B59:B68"/>
-    <mergeCell ref="C59:C68"/>
-    <mergeCell ref="D62:D63"/>
-    <mergeCell ref="E62:E63"/>
-    <mergeCell ref="A16:A25"/>
-    <mergeCell ref="B16:B25"/>
-    <mergeCell ref="C16:C25"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="A4:A15"/>
-    <mergeCell ref="B4:B15"/>
-    <mergeCell ref="C4:C15"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="A36:A45"/>
-    <mergeCell ref="B36:B45"/>
-    <mergeCell ref="C36:C45"/>
     <mergeCell ref="A47:A58"/>
     <mergeCell ref="B47:B58"/>
     <mergeCell ref="C47:C58"/>
     <mergeCell ref="A26:A35"/>
     <mergeCell ref="B26:B35"/>
     <mergeCell ref="C26:C35"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="A36:A45"/>
+    <mergeCell ref="B36:B45"/>
+    <mergeCell ref="C36:C45"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="A4:A15"/>
+    <mergeCell ref="B4:B15"/>
+    <mergeCell ref="C4:C15"/>
+    <mergeCell ref="A16:A25"/>
+    <mergeCell ref="B16:B25"/>
+    <mergeCell ref="C16:C25"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="A59:A68"/>
+    <mergeCell ref="B59:B68"/>
+    <mergeCell ref="C59:C68"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="E62:E63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -53887,8 +53887,8 @@
       <c r="F1" s="188"/>
       <c r="G1" s="188"/>
       <c r="H1" s="105"/>
-      <c r="I1" s="422"/>
-      <c r="J1" s="422"/>
+      <c r="I1" s="402"/>
+      <c r="J1" s="402"/>
       <c r="L1" s="30"/>
       <c r="M1" s="30"/>
     </row>
@@ -54073,13 +54073,13 @@
       <c r="EH3" s="36"/>
     </row>
     <row r="4" spans="1:138" ht="44.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="423">
+      <c r="A4" s="403">
         <v>1</v>
       </c>
-      <c r="B4" s="425" t="s">
+      <c r="B4" s="405" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="427" t="s">
+      <c r="C4" s="407" t="s">
         <v>51</v>
       </c>
       <c r="D4" s="73" t="s">
@@ -54107,9 +54107,9 @@
       </c>
     </row>
     <row r="5" spans="1:138" ht="30" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="424"/>
-      <c r="B5" s="426"/>
-      <c r="C5" s="428"/>
+      <c r="A5" s="404"/>
+      <c r="B5" s="406"/>
+      <c r="C5" s="408"/>
       <c r="D5" s="73" t="s">
         <v>56</v>
       </c>
@@ -54131,9 +54131,9 @@
       <c r="M5" s="76"/>
     </row>
     <row r="6" spans="1:138" ht="48" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="424"/>
-      <c r="B6" s="426"/>
-      <c r="C6" s="428"/>
+      <c r="A6" s="404"/>
+      <c r="B6" s="406"/>
+      <c r="C6" s="408"/>
       <c r="D6" s="73" t="s">
         <v>55</v>
       </c>
@@ -54158,9 +54158,9 @@
       </c>
     </row>
     <row r="7" spans="1:138" ht="144" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="424"/>
-      <c r="B7" s="426"/>
-      <c r="C7" s="428"/>
+      <c r="A7" s="404"/>
+      <c r="B7" s="406"/>
+      <c r="C7" s="408"/>
       <c r="D7" s="73" t="s">
         <v>63</v>
       </c>
@@ -54183,9 +54183,9 @@
       <c r="M7" s="76"/>
     </row>
     <row r="8" spans="1:138" ht="108" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="424"/>
-      <c r="B8" s="426"/>
-      <c r="C8" s="428"/>
+      <c r="A8" s="404"/>
+      <c r="B8" s="406"/>
+      <c r="C8" s="408"/>
       <c r="D8" s="73" t="s">
         <v>68</v>
       </c>
@@ -54207,9 +54207,9 @@
       <c r="M8" s="76"/>
     </row>
     <row r="9" spans="1:138" ht="36" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="424"/>
-      <c r="B9" s="426"/>
-      <c r="C9" s="428"/>
+      <c r="A9" s="404"/>
+      <c r="B9" s="406"/>
+      <c r="C9" s="408"/>
       <c r="D9" s="73" t="s">
         <v>72</v>
       </c>
@@ -54231,9 +54231,9 @@
       <c r="M9" s="76"/>
     </row>
     <row r="10" spans="1:138" ht="48" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="424"/>
-      <c r="B10" s="426"/>
-      <c r="C10" s="428"/>
+      <c r="A10" s="404"/>
+      <c r="B10" s="406"/>
+      <c r="C10" s="408"/>
       <c r="D10" s="73" t="s">
         <v>86</v>
       </c>
@@ -54257,9 +54257,9 @@
       <c r="M10" s="76"/>
     </row>
     <row r="11" spans="1:138" s="42" customFormat="1" ht="30" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="424"/>
-      <c r="B11" s="426"/>
-      <c r="C11" s="428"/>
+      <c r="A11" s="404"/>
+      <c r="B11" s="406"/>
+      <c r="C11" s="408"/>
       <c r="D11" s="73" t="s">
         <v>92</v>
       </c>
@@ -54409,9 +54409,9 @@
       <c r="EH11" s="41"/>
     </row>
     <row r="12" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="424"/>
-      <c r="B12" s="426"/>
-      <c r="C12" s="429"/>
+      <c r="A12" s="404"/>
+      <c r="B12" s="406"/>
+      <c r="C12" s="409"/>
       <c r="D12" s="73" t="s">
         <v>282</v>
       </c>
@@ -54432,14 +54432,14 @@
       <c r="L12" s="76"/>
       <c r="M12" s="76"/>
     </row>
-    <row r="13" spans="1:138" ht="36" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="415">
+    <row r="13" spans="1:138" ht="45" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="410">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B13" s="416" t="s">
+      <c r="B13" s="411" t="s">
         <v>98</v>
       </c>
-      <c r="C13" s="430" t="s">
+      <c r="C13" s="412" t="s">
         <v>99</v>
       </c>
       <c r="D13" s="73" t="s">
@@ -54465,9 +54465,9 @@
       <c r="M13" s="76"/>
     </row>
     <row r="14" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="415"/>
-      <c r="B14" s="416"/>
-      <c r="C14" s="431"/>
+      <c r="A14" s="410"/>
+      <c r="B14" s="411"/>
+      <c r="C14" s="413"/>
       <c r="D14" s="73" t="s">
         <v>56</v>
       </c>
@@ -54493,9 +54493,9 @@
       <c r="M14" s="76"/>
     </row>
     <row r="15" spans="1:138" ht="409.6" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="415"/>
-      <c r="B15" s="416"/>
-      <c r="C15" s="431"/>
+      <c r="A15" s="410"/>
+      <c r="B15" s="411"/>
+      <c r="C15" s="413"/>
       <c r="D15" s="73" t="s">
         <v>284</v>
       </c>
@@ -54542,9 +54542,9 @@
       <c r="M15" s="76"/>
     </row>
     <row r="16" spans="1:138" ht="30" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="415"/>
-      <c r="B16" s="416"/>
-      <c r="C16" s="431"/>
+      <c r="A16" s="410"/>
+      <c r="B16" s="411"/>
+      <c r="C16" s="413"/>
       <c r="D16" s="73" t="s">
         <v>286</v>
       </c>
@@ -54563,9 +54563,9 @@
       <c r="M16" s="76"/>
     </row>
     <row r="17" spans="1:138" s="47" customFormat="1" ht="409.6" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="415"/>
-      <c r="B17" s="416"/>
-      <c r="C17" s="431"/>
+      <c r="A17" s="410"/>
+      <c r="B17" s="411"/>
+      <c r="C17" s="413"/>
       <c r="D17" s="73" t="s">
         <v>106</v>
       </c>
@@ -54726,9 +54726,9 @@
       <c r="EH17" s="36"/>
     </row>
     <row r="18" spans="1:138" s="47" customFormat="1" ht="409.6" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="415"/>
-      <c r="B18" s="416"/>
-      <c r="C18" s="431"/>
+      <c r="A18" s="410"/>
+      <c r="B18" s="411"/>
+      <c r="C18" s="413"/>
       <c r="D18" s="73" t="s">
         <v>92</v>
       </c>
@@ -54889,9 +54889,9 @@
       <c r="EH18" s="36"/>
     </row>
     <row r="19" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="423"/>
-      <c r="B19" s="425"/>
-      <c r="C19" s="431"/>
+      <c r="A19" s="403"/>
+      <c r="B19" s="405"/>
+      <c r="C19" s="413"/>
       <c r="D19" s="189" t="s">
         <v>282</v>
       </c>
@@ -54919,7 +54919,7 @@
       <c r="B20" s="468" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="470" t="s">
+      <c r="C20" s="469" t="s">
         <v>287</v>
       </c>
       <c r="D20" s="73" t="s">
@@ -54947,7 +54947,7 @@
     <row r="21" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A21" s="467"/>
       <c r="B21" s="468"/>
-      <c r="C21" s="470"/>
+      <c r="C21" s="469"/>
       <c r="D21" s="73" t="s">
         <v>56</v>
       </c>
@@ -54975,7 +54975,7 @@
     <row r="22" spans="1:138" ht="409.6" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A22" s="467"/>
       <c r="B22" s="468"/>
-      <c r="C22" s="470"/>
+      <c r="C22" s="469"/>
       <c r="D22" s="189" t="s">
         <v>284</v>
       </c>
@@ -55008,7 +55008,7 @@
     <row r="23" spans="1:138" ht="30" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A23" s="467"/>
       <c r="B23" s="468"/>
-      <c r="C23" s="471"/>
+      <c r="C23" s="470"/>
       <c r="D23" s="73" t="s">
         <v>286</v>
       </c>
@@ -55028,7 +55028,7 @@
     <row r="24" spans="1:138" s="47" customFormat="1" ht="409.6" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A24" s="467"/>
       <c r="B24" s="468"/>
-      <c r="C24" s="470"/>
+      <c r="C24" s="469"/>
       <c r="D24" s="271" t="s">
         <v>114</v>
       </c>
@@ -55187,7 +55187,7 @@
     <row r="25" spans="1:138" s="47" customFormat="1" ht="409.6" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A25" s="467"/>
       <c r="B25" s="468"/>
-      <c r="C25" s="470"/>
+      <c r="C25" s="469"/>
       <c r="D25" s="272" t="s">
         <v>92</v>
       </c>
@@ -55346,7 +55346,7 @@
     <row r="26" spans="1:138" ht="196.5" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A26" s="467"/>
       <c r="B26" s="468"/>
-      <c r="C26" s="471"/>
+      <c r="C26" s="470"/>
       <c r="D26" s="73" t="s">
         <v>94</v>
       </c>
@@ -55368,13 +55368,13 @@
       <c r="M26" s="76"/>
     </row>
     <row r="27" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="402">
+      <c r="A27" s="421">
         <v>2.1</v>
       </c>
-      <c r="B27" s="405" t="s">
+      <c r="B27" s="424" t="s">
         <v>116</v>
       </c>
-      <c r="C27" s="419" t="s">
+      <c r="C27" s="427" t="s">
         <v>117</v>
       </c>
       <c r="D27" s="73" t="s">
@@ -55400,9 +55400,9 @@
       <c r="M27" s="76"/>
     </row>
     <row r="28" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="403"/>
-      <c r="B28" s="406"/>
-      <c r="C28" s="420"/>
+      <c r="A28" s="422"/>
+      <c r="B28" s="425"/>
+      <c r="C28" s="428"/>
       <c r="D28" s="73" t="s">
         <v>122</v>
       </c>
@@ -55422,9 +55422,9 @@
       <c r="M28" s="76"/>
     </row>
     <row r="29" spans="1:138" ht="84" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="403"/>
-      <c r="B29" s="406"/>
-      <c r="C29" s="420"/>
+      <c r="A29" s="422"/>
+      <c r="B29" s="425"/>
+      <c r="C29" s="428"/>
       <c r="D29" s="73" t="s">
         <v>130</v>
       </c>
@@ -55448,9 +55448,9 @@
       <c r="M29" s="76"/>
     </row>
     <row r="30" spans="1:138" ht="60" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="403"/>
-      <c r="B30" s="406"/>
-      <c r="C30" s="420"/>
+      <c r="A30" s="422"/>
+      <c r="B30" s="425"/>
+      <c r="C30" s="428"/>
       <c r="D30" s="189" t="s">
         <v>55</v>
       </c>
@@ -55474,9 +55474,9 @@
       <c r="M30" s="76"/>
     </row>
     <row r="31" spans="1:138" ht="36" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="403"/>
-      <c r="B31" s="406"/>
-      <c r="C31" s="420"/>
+      <c r="A31" s="422"/>
+      <c r="B31" s="425"/>
+      <c r="C31" s="428"/>
       <c r="D31" s="73" t="s">
         <v>134</v>
       </c>
@@ -55500,9 +55500,9 @@
       </c>
     </row>
     <row r="32" spans="1:138" ht="48" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="403"/>
-      <c r="B32" s="406"/>
-      <c r="C32" s="420"/>
+      <c r="A32" s="422"/>
+      <c r="B32" s="425"/>
+      <c r="C32" s="428"/>
       <c r="D32" s="271" t="s">
         <v>114</v>
       </c>
@@ -55526,9 +55526,9 @@
       <c r="M32" s="76"/>
     </row>
     <row r="33" spans="1:13" ht="30" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="403"/>
-      <c r="B33" s="406"/>
-      <c r="C33" s="420"/>
+      <c r="A33" s="422"/>
+      <c r="B33" s="425"/>
+      <c r="C33" s="428"/>
       <c r="D33" s="272" t="s">
         <v>92</v>
       </c>
@@ -55552,9 +55552,9 @@
       <c r="M33" s="76"/>
     </row>
     <row r="34" spans="1:13" ht="45" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="404"/>
-      <c r="B34" s="407"/>
-      <c r="C34" s="421"/>
+      <c r="A34" s="423"/>
+      <c r="B34" s="426"/>
+      <c r="C34" s="429"/>
       <c r="D34" s="73" t="s">
         <v>94</v>
       </c>
@@ -55594,13 +55594,13 @@
       <c r="M35" s="76"/>
     </row>
     <row r="36" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="423">
+      <c r="A36" s="403">
         <v>1</v>
       </c>
-      <c r="B36" s="425" t="s">
+      <c r="B36" s="405" t="s">
         <v>50</v>
       </c>
-      <c r="C36" s="472" t="s">
+      <c r="C36" s="471" t="s">
         <v>296</v>
       </c>
       <c r="D36" s="73" t="s">
@@ -55622,9 +55622,9 @@
       </c>
     </row>
     <row r="37" spans="1:13" ht="30" x14ac:dyDescent="0.2">
-      <c r="A37" s="424"/>
-      <c r="B37" s="426"/>
-      <c r="C37" s="473"/>
+      <c r="A37" s="404"/>
+      <c r="B37" s="406"/>
+      <c r="C37" s="472"/>
       <c r="D37" s="73" t="s">
         <v>56</v>
       </c>
@@ -55644,9 +55644,9 @@
       </c>
     </row>
     <row r="38" spans="1:13" ht="48" x14ac:dyDescent="0.2">
-      <c r="A38" s="424"/>
-      <c r="B38" s="426"/>
-      <c r="C38" s="473"/>
+      <c r="A38" s="404"/>
+      <c r="B38" s="406"/>
+      <c r="C38" s="472"/>
       <c r="D38" s="73" t="s">
         <v>55</v>
       </c>
@@ -55666,9 +55666,9 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="144" x14ac:dyDescent="0.2">
-      <c r="A39" s="424"/>
-      <c r="B39" s="426"/>
-      <c r="C39" s="473"/>
+      <c r="A39" s="404"/>
+      <c r="B39" s="406"/>
+      <c r="C39" s="472"/>
       <c r="D39" s="73" t="s">
         <v>63</v>
       </c>
@@ -55688,9 +55688,9 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="108" x14ac:dyDescent="0.2">
-      <c r="A40" s="424"/>
-      <c r="B40" s="426"/>
-      <c r="C40" s="473"/>
+      <c r="A40" s="404"/>
+      <c r="B40" s="406"/>
+      <c r="C40" s="472"/>
       <c r="D40" s="73" t="s">
         <v>68</v>
       </c>
@@ -55710,9 +55710,9 @@
       </c>
     </row>
     <row r="41" spans="1:13" ht="36" x14ac:dyDescent="0.2">
-      <c r="A41" s="424"/>
-      <c r="B41" s="426"/>
-      <c r="C41" s="473"/>
+      <c r="A41" s="404"/>
+      <c r="B41" s="406"/>
+      <c r="C41" s="472"/>
       <c r="D41" s="73" t="s">
         <v>72</v>
       </c>
@@ -55732,9 +55732,9 @@
       </c>
     </row>
     <row r="42" spans="1:13" ht="48" x14ac:dyDescent="0.2">
-      <c r="A42" s="424"/>
-      <c r="B42" s="426"/>
-      <c r="C42" s="473"/>
+      <c r="A42" s="404"/>
+      <c r="B42" s="406"/>
+      <c r="C42" s="472"/>
       <c r="D42" s="73" t="s">
         <v>86</v>
       </c>
@@ -55756,9 +55756,9 @@
       </c>
     </row>
     <row r="43" spans="1:13" ht="30" x14ac:dyDescent="0.2">
-      <c r="A43" s="424"/>
-      <c r="B43" s="426"/>
-      <c r="C43" s="473"/>
+      <c r="A43" s="404"/>
+      <c r="B43" s="406"/>
+      <c r="C43" s="472"/>
       <c r="D43" s="73" t="s">
         <v>92</v>
       </c>
@@ -55780,9 +55780,9 @@
       </c>
     </row>
     <row r="44" spans="1:13" ht="60" x14ac:dyDescent="0.2">
-      <c r="A44" s="424"/>
-      <c r="B44" s="426"/>
-      <c r="C44" s="473"/>
+      <c r="A44" s="404"/>
+      <c r="B44" s="406"/>
+      <c r="C44" s="472"/>
       <c r="D44" s="73" t="s">
         <v>282</v>
       </c>
@@ -55802,13 +55802,13 @@
       </c>
     </row>
     <row r="45" spans="1:13" ht="36" x14ac:dyDescent="0.2">
-      <c r="A45" s="415">
+      <c r="A45" s="410">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B45" s="416" t="s">
+      <c r="B45" s="411" t="s">
         <v>98</v>
       </c>
-      <c r="C45" s="430" t="s">
+      <c r="C45" s="412" t="s">
         <v>99</v>
       </c>
       <c r="D45" s="73" t="s">
@@ -55830,9 +55830,9 @@
       </c>
     </row>
     <row r="46" spans="1:13" ht="30" x14ac:dyDescent="0.2">
-      <c r="A46" s="415"/>
-      <c r="B46" s="416"/>
-      <c r="C46" s="431"/>
+      <c r="A46" s="410"/>
+      <c r="B46" s="411"/>
+      <c r="C46" s="413"/>
       <c r="D46" s="73" t="s">
         <v>56</v>
       </c>
@@ -55854,9 +55854,9 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A47" s="415"/>
-      <c r="B47" s="416"/>
-      <c r="C47" s="431"/>
+      <c r="A47" s="410"/>
+      <c r="B47" s="411"/>
+      <c r="C47" s="413"/>
       <c r="D47" s="73" t="s">
         <v>284</v>
       </c>
@@ -55900,9 +55900,9 @@
       </c>
     </row>
     <row r="48" spans="1:13" ht="30" x14ac:dyDescent="0.2">
-      <c r="A48" s="415"/>
-      <c r="B48" s="416"/>
-      <c r="C48" s="431"/>
+      <c r="A48" s="410"/>
+      <c r="B48" s="411"/>
+      <c r="C48" s="413"/>
       <c r="D48" s="73" t="s">
         <v>286</v>
       </c>
@@ -55918,9 +55918,9 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A49" s="415"/>
-      <c r="B49" s="416"/>
-      <c r="C49" s="431"/>
+      <c r="A49" s="410"/>
+      <c r="B49" s="411"/>
+      <c r="C49" s="413"/>
       <c r="D49" s="73" t="s">
         <v>106</v>
       </c>
@@ -55953,9 +55953,9 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A50" s="415"/>
-      <c r="B50" s="416"/>
-      <c r="C50" s="431"/>
+      <c r="A50" s="410"/>
+      <c r="B50" s="411"/>
+      <c r="C50" s="413"/>
       <c r="D50" s="73" t="s">
         <v>92</v>
       </c>
@@ -55988,9 +55988,9 @@
       </c>
     </row>
     <row r="51" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A51" s="423"/>
-      <c r="B51" s="425"/>
-      <c r="C51" s="431"/>
+      <c r="A51" s="403"/>
+      <c r="B51" s="405"/>
+      <c r="C51" s="413"/>
       <c r="D51" s="189" t="s">
         <v>282</v>
       </c>
@@ -56016,7 +56016,7 @@
       <c r="B52" s="468" t="s">
         <v>109</v>
       </c>
-      <c r="C52" s="469" t="s">
+      <c r="C52" s="473" t="s">
         <v>297</v>
       </c>
       <c r="D52" s="73" t="s">
@@ -56040,7 +56040,7 @@
     <row r="53" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A53" s="467"/>
       <c r="B53" s="468"/>
-      <c r="C53" s="470"/>
+      <c r="C53" s="469"/>
       <c r="D53" s="37" t="s">
         <v>298</v>
       </c>
@@ -56071,7 +56071,7 @@
     <row r="54" spans="1:10" ht="30" x14ac:dyDescent="0.2">
       <c r="A54" s="467"/>
       <c r="B54" s="468"/>
-      <c r="C54" s="470"/>
+      <c r="C54" s="469"/>
       <c r="D54" s="37" t="s">
         <v>300</v>
       </c>
@@ -56093,7 +56093,7 @@
     <row r="55" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A55" s="467"/>
       <c r="B55" s="468"/>
-      <c r="C55" s="470"/>
+      <c r="C55" s="469"/>
       <c r="D55" s="189" t="s">
         <v>284</v>
       </c>
@@ -56124,7 +56124,7 @@
     <row r="56" spans="1:10" ht="30" x14ac:dyDescent="0.2">
       <c r="A56" s="467"/>
       <c r="B56" s="468"/>
-      <c r="C56" s="471"/>
+      <c r="C56" s="470"/>
       <c r="D56" s="73" t="s">
         <v>286</v>
       </c>
@@ -56142,7 +56142,7 @@
     <row r="57" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A57" s="467"/>
       <c r="B57" s="468"/>
-      <c r="C57" s="470"/>
+      <c r="C57" s="469"/>
       <c r="D57" s="271" t="s">
         <v>114</v>
       </c>
@@ -56173,7 +56173,7 @@
     <row r="58" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A58" s="467"/>
       <c r="B58" s="468"/>
-      <c r="C58" s="470"/>
+      <c r="C58" s="469"/>
       <c r="D58" s="272" t="s">
         <v>92</v>
       </c>
@@ -56204,7 +56204,7 @@
     <row r="59" spans="1:10" ht="45" x14ac:dyDescent="0.2">
       <c r="A59" s="467"/>
       <c r="B59" s="468"/>
-      <c r="C59" s="471"/>
+      <c r="C59" s="470"/>
       <c r="D59" s="73" t="s">
         <v>94</v>
       </c>
@@ -56224,13 +56224,13 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A60" s="402">
+      <c r="A60" s="421">
         <v>2.1</v>
       </c>
-      <c r="B60" s="405" t="s">
+      <c r="B60" s="424" t="s">
         <v>116</v>
       </c>
-      <c r="C60" s="419" t="s">
+      <c r="C60" s="427" t="s">
         <v>117</v>
       </c>
       <c r="D60" s="73" t="s">
@@ -56252,9 +56252,9 @@
       </c>
     </row>
     <row r="61" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A61" s="403"/>
-      <c r="B61" s="406"/>
-      <c r="C61" s="420"/>
+      <c r="A61" s="422"/>
+      <c r="B61" s="425"/>
+      <c r="C61" s="428"/>
       <c r="D61" s="73" t="s">
         <v>122</v>
       </c>
@@ -56272,9 +56272,9 @@
       </c>
     </row>
     <row r="62" spans="1:10" ht="84" x14ac:dyDescent="0.2">
-      <c r="A62" s="403"/>
-      <c r="B62" s="406"/>
-      <c r="C62" s="420"/>
+      <c r="A62" s="422"/>
+      <c r="B62" s="425"/>
+      <c r="C62" s="428"/>
       <c r="D62" s="73" t="s">
         <v>130</v>
       </c>
@@ -56294,9 +56294,9 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="60" x14ac:dyDescent="0.2">
-      <c r="A63" s="403"/>
-      <c r="B63" s="406"/>
-      <c r="C63" s="420"/>
+      <c r="A63" s="422"/>
+      <c r="B63" s="425"/>
+      <c r="C63" s="428"/>
       <c r="D63" s="189" t="s">
         <v>55</v>
       </c>
@@ -56318,9 +56318,9 @@
       </c>
     </row>
     <row r="64" spans="1:10" ht="36" x14ac:dyDescent="0.2">
-      <c r="A64" s="403"/>
-      <c r="B64" s="406"/>
-      <c r="C64" s="420"/>
+      <c r="A64" s="422"/>
+      <c r="B64" s="425"/>
+      <c r="C64" s="428"/>
       <c r="D64" s="73" t="s">
         <v>134</v>
       </c>
@@ -56338,9 +56338,9 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="48" x14ac:dyDescent="0.2">
-      <c r="A65" s="403"/>
-      <c r="B65" s="406"/>
-      <c r="C65" s="420"/>
+      <c r="A65" s="422"/>
+      <c r="B65" s="425"/>
+      <c r="C65" s="428"/>
       <c r="D65" s="271" t="s">
         <v>114</v>
       </c>
@@ -56362,9 +56362,9 @@
       </c>
     </row>
     <row r="66" spans="1:10" ht="30" x14ac:dyDescent="0.2">
-      <c r="A66" s="403"/>
-      <c r="B66" s="406"/>
-      <c r="C66" s="420"/>
+      <c r="A66" s="422"/>
+      <c r="B66" s="425"/>
+      <c r="C66" s="428"/>
       <c r="D66" s="272" t="s">
         <v>92</v>
       </c>
@@ -56386,9 +56386,9 @@
       </c>
     </row>
     <row r="67" spans="1:10" ht="45" x14ac:dyDescent="0.2">
-      <c r="A67" s="404"/>
-      <c r="B67" s="407"/>
-      <c r="C67" s="421"/>
+      <c r="A67" s="423"/>
+      <c r="B67" s="426"/>
+      <c r="C67" s="429"/>
       <c r="D67" s="73" t="s">
         <v>94</v>
       </c>
@@ -56410,6 +56410,24 @@
   </sheetData>
   <autoFilter ref="A2:EH34" xr:uid="{92218EDD-6442-41B5-9565-D949ECDDA5BC}"/>
   <mergeCells count="25">
+    <mergeCell ref="A52:A59"/>
+    <mergeCell ref="B52:B59"/>
+    <mergeCell ref="C52:C59"/>
+    <mergeCell ref="A60:A67"/>
+    <mergeCell ref="B60:B67"/>
+    <mergeCell ref="C60:C67"/>
+    <mergeCell ref="A36:A44"/>
+    <mergeCell ref="B36:B44"/>
+    <mergeCell ref="C36:C44"/>
+    <mergeCell ref="A45:A51"/>
+    <mergeCell ref="B45:B51"/>
+    <mergeCell ref="C45:C51"/>
+    <mergeCell ref="A20:A26"/>
+    <mergeCell ref="B20:B26"/>
+    <mergeCell ref="C20:C26"/>
+    <mergeCell ref="A27:A34"/>
+    <mergeCell ref="B27:B34"/>
+    <mergeCell ref="C27:C34"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="A4:A12"/>
     <mergeCell ref="B4:B12"/>
@@ -56417,24 +56435,6 @@
     <mergeCell ref="A13:A19"/>
     <mergeCell ref="B13:B19"/>
     <mergeCell ref="C13:C19"/>
-    <mergeCell ref="A20:A26"/>
-    <mergeCell ref="B20:B26"/>
-    <mergeCell ref="C20:C26"/>
-    <mergeCell ref="A27:A34"/>
-    <mergeCell ref="B27:B34"/>
-    <mergeCell ref="C27:C34"/>
-    <mergeCell ref="A36:A44"/>
-    <mergeCell ref="B36:B44"/>
-    <mergeCell ref="C36:C44"/>
-    <mergeCell ref="A45:A51"/>
-    <mergeCell ref="B45:B51"/>
-    <mergeCell ref="C45:C51"/>
-    <mergeCell ref="A52:A59"/>
-    <mergeCell ref="B52:B59"/>
-    <mergeCell ref="C52:C59"/>
-    <mergeCell ref="A60:A67"/>
-    <mergeCell ref="B60:B67"/>
-    <mergeCell ref="C60:C67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -57131,15 +57131,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F52F3FC1CD8EC649B3AFADF3835D38B7" ma:contentTypeVersion="0" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="585bd31a01b77638b6ff73c684db7301">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="500c6692915ba10984c0aabd49f31b22">
     <xsd:element name="properties">
@@ -57253,6 +57244,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -57260,14 +57260,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEA3B3A7-4C5B-4FB5-B9FC-8D6E6D28CE9F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38A554B1-B6E8-4F95-B069-71B18B767B61}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -57279,6 +57271,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEA3B3A7-4C5B-4FB5-B9FC-8D6E6D28CE9F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
